--- a/scenes.xlsx
+++ b/scenes.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K67"/>
+  <dimension ref="A1:K68"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="8.83203125" customWidth="1"/>
@@ -498,7 +498,7 @@
         <v>IMG_6266.jpg</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -551,11 +551,11 @@
       </c>
       <c r="J4">
         <f>J3+E3-0.7</f>
-        <v>11.6</v>
+        <v>11</v>
       </c>
       <c r="K4">
         <f>INT(J4*30+0.5)</f>
-        <v>348</v>
+        <v>330</v>
       </c>
     </row>
     <row r="5">
@@ -572,7 +572,7 @@
         <v>16.jpg</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -588,11 +588,11 @@
       </c>
       <c r="J5">
         <f>J4+E4-0.7</f>
-        <v>18.9</v>
+        <v>18.3</v>
       </c>
       <c r="K5">
         <f>INT(J5*30+0.5)</f>
-        <v>567</v>
+        <v>549</v>
       </c>
     </row>
     <row r="6">
@@ -609,7 +609,7 @@
         <v>3開院.jpg</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -625,11 +625,11 @@
       </c>
       <c r="J6">
         <f>J5+E5-0.7</f>
-        <v>23.2</v>
+        <v>22</v>
       </c>
       <c r="K6">
         <f>INT(J6*30+0.5)</f>
-        <v>696</v>
+        <v>660</v>
       </c>
     </row>
     <row r="7">
@@ -646,7 +646,7 @@
         <v>04-kono-hi-kara.jpg</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -662,11 +662,11 @@
       </c>
       <c r="J7">
         <f>J6+E6-0.7</f>
-        <v>27.5</v>
+        <v>25.7</v>
       </c>
       <c r="K7">
         <f>INT(J7*30+0.5)</f>
-        <v>825</v>
+        <v>771</v>
       </c>
     </row>
     <row r="8">
@@ -683,7 +683,7 @@
         <v>2015三月.jpg</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="F8">
         <v>1</v>
@@ -699,11 +699,11 @@
       </c>
       <c r="J8">
         <f>J7+E7-0.7</f>
-        <v>31.8</v>
+        <v>29.4</v>
       </c>
       <c r="K8">
         <f>INT(J8*30+0.5)</f>
-        <v>954</v>
+        <v>882</v>
       </c>
     </row>
     <row r="9">
@@ -720,7 +720,7 @@
         <v>03-kaiin-toji.jpg</v>
       </c>
       <c r="E9">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -736,11 +736,11 @@
       </c>
       <c r="J9">
         <f>J8+E8-0.7</f>
-        <v>36.1</v>
+        <v>33.1</v>
       </c>
       <c r="K9">
         <f>INT(J9*30+0.5)</f>
-        <v>1083</v>
+        <v>993</v>
       </c>
     </row>
     <row r="10">
@@ -757,7 +757,7 @@
         <v>2015年前期.jpg</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -773,11 +773,11 @@
       </c>
       <c r="J10">
         <f>J9+E9-0.7</f>
-        <v>40.4</v>
+        <v>36.8</v>
       </c>
       <c r="K10">
         <f>INT(J10*30+0.5)</f>
-        <v>1212</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="11">
@@ -810,11 +810,11 @@
       </c>
       <c r="J11">
         <f>J10+E10-0.7</f>
-        <v>44.7</v>
+        <v>40.5</v>
       </c>
       <c r="K11">
         <f>INT(J11*30+0.5)</f>
-        <v>1341</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="12">
@@ -831,7 +831,7 @@
         <v>9be842d9.jpg</v>
       </c>
       <c r="E12">
-        <v>5</v>
+        <v>4.49</v>
       </c>
       <c r="F12">
         <v>1</v>
@@ -847,11 +847,11 @@
       </c>
       <c r="J12">
         <f>J11+E11-0.7</f>
-        <v>52</v>
+        <v>47.8</v>
       </c>
       <c r="K12">
         <f>INT(J12*30+0.5)</f>
-        <v>1560</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="13">
@@ -884,11 +884,11 @@
       </c>
       <c r="J13">
         <f>J12+E12-0.7</f>
-        <v>56.3</v>
+        <v>51.59</v>
       </c>
       <c r="K13">
         <f>INT(J13*30+0.5)</f>
-        <v>1689</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="14">
@@ -921,11 +921,11 @@
       </c>
       <c r="J14">
         <f>J13+E13-0.7</f>
-        <v>60.6</v>
+        <v>55.89</v>
       </c>
       <c r="K14">
         <f>INT(J14*30+0.5)</f>
-        <v>1818</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="15">
@@ -958,11 +958,11 @@
       </c>
       <c r="J15">
         <f>J14+E14-0.7</f>
-        <v>64.9</v>
+        <v>60.19</v>
       </c>
       <c r="K15">
         <f>INT(J15*30+0.5)</f>
-        <v>1947</v>
+        <v>1806</v>
       </c>
     </row>
     <row r="16">
@@ -995,11 +995,11 @@
       </c>
       <c r="J16">
         <f>J15+E15-0.7</f>
-        <v>69.2</v>
+        <v>64.49</v>
       </c>
       <c r="K16">
         <f>INT(J16*30+0.5)</f>
-        <v>2076</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="17">
@@ -1032,11 +1032,11 @@
       </c>
       <c r="J17">
         <f>J16+E16-0.7</f>
-        <v>74.5</v>
+        <v>69.79</v>
       </c>
       <c r="K17">
         <f>INT(J17*30+0.5)</f>
-        <v>2235</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="18">
@@ -1069,11 +1069,11 @@
       </c>
       <c r="J18">
         <f>J17+E17-0.7</f>
-        <v>78.8</v>
+        <v>74.09</v>
       </c>
       <c r="K18">
         <f>INT(J18*30+0.5)</f>
-        <v>2364</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="19">
@@ -1106,11 +1106,11 @@
       </c>
       <c r="J19">
         <f>J18+E18-0.7</f>
-        <v>83.1</v>
+        <v>78.39</v>
       </c>
       <c r="K19">
         <f>INT(J19*30+0.5)</f>
-        <v>2493</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="20">
@@ -1143,11 +1143,11 @@
       </c>
       <c r="J20">
         <f>J19+E19-0.7</f>
-        <v>87.4</v>
+        <v>82.69</v>
       </c>
       <c r="K20">
         <f>INT(J20*30+0.5)</f>
-        <v>2622</v>
+        <v>2481</v>
       </c>
     </row>
     <row r="21">
@@ -1180,11 +1180,11 @@
       </c>
       <c r="J21">
         <f>J20+E20-0.7</f>
-        <v>92.7</v>
+        <v>87.99</v>
       </c>
       <c r="K21">
         <f>INT(J21*30+0.5)</f>
-        <v>2781</v>
+        <v>2640</v>
       </c>
     </row>
     <row r="22">
@@ -1217,11 +1217,11 @@
       </c>
       <c r="J22">
         <f>J21+E21-0.7</f>
-        <v>97</v>
+        <v>92.29</v>
       </c>
       <c r="K22">
         <f>INT(J22*30+0.5)</f>
-        <v>2910</v>
+        <v>2769</v>
       </c>
     </row>
     <row r="23">
@@ -1254,11 +1254,11 @@
       </c>
       <c r="J23">
         <f>J22+E22-0.7</f>
-        <v>101.3</v>
+        <v>96.59</v>
       </c>
       <c r="K23">
         <f>INT(J23*30+0.5)</f>
-        <v>3039</v>
+        <v>2898</v>
       </c>
     </row>
     <row r="24">
@@ -1291,11 +1291,11 @@
       </c>
       <c r="J24">
         <f>J23+E23-0.7</f>
-        <v>105.6</v>
+        <v>100.89</v>
       </c>
       <c r="K24">
         <f>INT(J24*30+0.5)</f>
-        <v>3168</v>
+        <v>3027</v>
       </c>
     </row>
     <row r="25">
@@ -1328,11 +1328,11 @@
       </c>
       <c r="J25">
         <f>J24+E24-0.7</f>
-        <v>109.9</v>
+        <v>105.19</v>
       </c>
       <c r="K25">
         <f>INT(J25*30+0.5)</f>
-        <v>3297</v>
+        <v>3156</v>
       </c>
     </row>
     <row r="26">
@@ -1365,11 +1365,11 @@
       </c>
       <c r="J26">
         <f>J25+E25-0.7</f>
-        <v>114.2</v>
+        <v>109.49</v>
       </c>
       <c r="K26">
         <f>INT(J26*30+0.5)</f>
-        <v>3426</v>
+        <v>3285</v>
       </c>
     </row>
     <row r="27">
@@ -1402,11 +1402,11 @@
       </c>
       <c r="J27">
         <f>J26+E26-0.7</f>
-        <v>118.5</v>
+        <v>113.79</v>
       </c>
       <c r="K27">
         <f>INT(J27*30+0.5)</f>
-        <v>3555</v>
+        <v>3414</v>
       </c>
     </row>
     <row r="28">
@@ -1439,11 +1439,11 @@
       </c>
       <c r="J28">
         <f>J27+E27-0.7</f>
-        <v>122.8</v>
+        <v>118.09</v>
       </c>
       <c r="K28">
         <f>INT(J28*30+0.5)</f>
-        <v>3684</v>
+        <v>3543</v>
       </c>
     </row>
     <row r="29">
@@ -1476,11 +1476,11 @@
       </c>
       <c r="J29">
         <f>J28+E28-0.7</f>
-        <v>127.1</v>
+        <v>122.39</v>
       </c>
       <c r="K29">
         <f>INT(J29*30+0.5)</f>
-        <v>3813</v>
+        <v>3672</v>
       </c>
     </row>
     <row r="30">
@@ -1513,11 +1513,11 @@
       </c>
       <c r="J30">
         <f>J29+E29-0.7</f>
-        <v>129.82</v>
+        <v>125.11</v>
       </c>
       <c r="K30">
         <f>INT(J30*30+0.5)</f>
-        <v>3895</v>
+        <v>3753</v>
       </c>
     </row>
     <row r="31">
@@ -1550,11 +1550,11 @@
       </c>
       <c r="J31">
         <f>J30+E30-0.7</f>
-        <v>134.12</v>
+        <v>129.41</v>
       </c>
       <c r="K31">
         <f>INT(J31*30+0.5)</f>
-        <v>4024</v>
+        <v>3882</v>
       </c>
     </row>
     <row r="32">
@@ -1587,11 +1587,11 @@
       </c>
       <c r="J32">
         <f>J31+E31-0.7</f>
-        <v>140.42</v>
+        <v>135.71</v>
       </c>
       <c r="K32">
         <f>INT(J32*30+0.5)</f>
-        <v>4213</v>
+        <v>4071</v>
       </c>
     </row>
     <row r="33">
@@ -1624,11 +1624,11 @@
       </c>
       <c r="J33">
         <f>J32+E32-0.7</f>
-        <v>144.72</v>
+        <v>140.01</v>
       </c>
       <c r="K33">
         <f>INT(J33*30+0.5)</f>
-        <v>4342</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="34">
@@ -1661,11 +1661,11 @@
       </c>
       <c r="J34">
         <f>J33+E33-0.7</f>
-        <v>150.02</v>
+        <v>145.31</v>
       </c>
       <c r="K34">
         <f>INT(J34*30+0.5)</f>
-        <v>4501</v>
+        <v>4359</v>
       </c>
     </row>
     <row r="35">
@@ -1698,11 +1698,11 @@
       </c>
       <c r="J35">
         <f>J34+E34-0.7</f>
-        <v>155.32</v>
+        <v>150.61</v>
       </c>
       <c r="K35">
         <f>INT(J35*30+0.5)</f>
-        <v>4660</v>
+        <v>4518</v>
       </c>
     </row>
     <row r="36">
@@ -1735,11 +1735,11 @@
       </c>
       <c r="J36">
         <f>J35+E35-0.7</f>
-        <v>159.42</v>
+        <v>154.71</v>
       </c>
       <c r="K36">
         <f>INT(J36*30+0.5)</f>
-        <v>4783</v>
+        <v>4641</v>
       </c>
     </row>
     <row r="37">
@@ -1772,11 +1772,11 @@
       </c>
       <c r="J37">
         <f>J36+E36-0.7</f>
-        <v>164.72</v>
+        <v>160.01</v>
       </c>
       <c r="K37">
         <f>INT(J37*30+0.5)</f>
-        <v>4942</v>
+        <v>4800</v>
       </c>
     </row>
     <row r="38">
@@ -1809,11 +1809,11 @@
       </c>
       <c r="J38">
         <f>J37+E37-0.7</f>
-        <v>170.02</v>
+        <v>165.31</v>
       </c>
       <c r="K38">
         <f>INT(J38*30+0.5)</f>
-        <v>5101</v>
+        <v>4959</v>
       </c>
     </row>
     <row r="39">
@@ -1846,11 +1846,11 @@
       </c>
       <c r="J39">
         <f>J38+E38-0.7</f>
-        <v>174.92</v>
+        <v>170.21</v>
       </c>
       <c r="K39">
         <f>INT(J39*30+0.5)</f>
-        <v>5248</v>
+        <v>5106</v>
       </c>
     </row>
     <row r="40">
@@ -1883,11 +1883,11 @@
       </c>
       <c r="J40">
         <f>J39+E39-0.7</f>
-        <v>178.82</v>
+        <v>174.11</v>
       </c>
       <c r="K40">
         <f>INT(J40*30+0.5)</f>
-        <v>5365</v>
+        <v>5223</v>
       </c>
     </row>
     <row r="41">
@@ -1920,11 +1920,11 @@
       </c>
       <c r="J41">
         <f>J40+E40-0.7</f>
-        <v>182.72</v>
+        <v>178.01</v>
       </c>
       <c r="K41">
         <f>INT(J41*30+0.5)</f>
-        <v>5482</v>
+        <v>5340</v>
       </c>
     </row>
     <row r="42">
@@ -1957,11 +1957,11 @@
       </c>
       <c r="J42">
         <f>J41+E41-0.7</f>
-        <v>186.62</v>
+        <v>181.91</v>
       </c>
       <c r="K42">
         <f>INT(J42*30+0.5)</f>
-        <v>5599</v>
+        <v>5457</v>
       </c>
     </row>
     <row r="43">
@@ -1994,11 +1994,11 @@
       </c>
       <c r="J43">
         <f>J42+E42-0.7</f>
-        <v>190.52</v>
+        <v>185.81</v>
       </c>
       <c r="K43">
         <f>INT(J43*30+0.5)</f>
-        <v>5716</v>
+        <v>5574</v>
       </c>
     </row>
     <row r="44">
@@ -2031,11 +2031,11 @@
       </c>
       <c r="J44">
         <f>J43+E43-0.7</f>
-        <v>194.42</v>
+        <v>189.71</v>
       </c>
       <c r="K44">
         <f>INT(J44*30+0.5)</f>
-        <v>5833</v>
+        <v>5691</v>
       </c>
     </row>
     <row r="45">
@@ -2068,11 +2068,11 @@
       </c>
       <c r="J45">
         <f>J44+E44-0.7</f>
-        <v>199.72</v>
+        <v>195.01</v>
       </c>
       <c r="K45">
         <f>INT(J45*30+0.5)</f>
-        <v>5992</v>
+        <v>5850</v>
       </c>
     </row>
     <row r="46">
@@ -2105,11 +2105,11 @@
       </c>
       <c r="J46">
         <f>J45+E45-0.7</f>
-        <v>203.62</v>
+        <v>198.91</v>
       </c>
       <c r="K46">
         <f>INT(J46*30+0.5)</f>
-        <v>6109</v>
+        <v>5967</v>
       </c>
     </row>
     <row r="47">
@@ -2142,11 +2142,11 @@
       </c>
       <c r="J47">
         <f>J46+E46-0.7</f>
-        <v>207.52</v>
+        <v>202.81</v>
       </c>
       <c r="K47">
         <f>INT(J47*30+0.5)</f>
-        <v>6226</v>
+        <v>6084</v>
       </c>
     </row>
     <row r="48">
@@ -2179,11 +2179,11 @@
       </c>
       <c r="J48">
         <f>J47+E47-0.7</f>
-        <v>211.42</v>
+        <v>206.71</v>
       </c>
       <c r="K48">
         <f>INT(J48*30+0.5)</f>
-        <v>6343</v>
+        <v>6201</v>
       </c>
     </row>
     <row r="49">
@@ -2216,11 +2216,11 @@
       </c>
       <c r="J49">
         <f>J48+E48-0.7</f>
-        <v>216.12</v>
+        <v>211.41</v>
       </c>
       <c r="K49">
         <f>INT(J49*30+0.5)</f>
-        <v>6484</v>
+        <v>6342</v>
       </c>
     </row>
     <row r="50">
@@ -2253,11 +2253,11 @@
       </c>
       <c r="J50">
         <f>J49+E49-0.7</f>
-        <v>220.82</v>
+        <v>216.11</v>
       </c>
       <c r="K50">
         <f>INT(J50*30+0.5)</f>
-        <v>6625</v>
+        <v>6483</v>
       </c>
     </row>
     <row r="51">
@@ -2290,11 +2290,11 @@
       </c>
       <c r="J51">
         <f>J50+E50-0.7</f>
-        <v>225.52</v>
+        <v>220.81</v>
       </c>
       <c r="K51">
         <f>INT(J51*30+0.5)</f>
-        <v>6766</v>
+        <v>6624</v>
       </c>
     </row>
     <row r="52">
@@ -2327,11 +2327,11 @@
       </c>
       <c r="J52">
         <f>J51+E51-0.7</f>
-        <v>230.22</v>
+        <v>225.51</v>
       </c>
       <c r="K52">
         <f>INT(J52*30+0.5)</f>
-        <v>6907</v>
+        <v>6765</v>
       </c>
     </row>
     <row r="53">
@@ -2364,11 +2364,11 @@
       </c>
       <c r="J53">
         <f>J52+E52-0.7</f>
-        <v>234.92</v>
+        <v>230.21</v>
       </c>
       <c r="K53">
         <f>INT(J53*30+0.5)</f>
-        <v>7048</v>
+        <v>6906</v>
       </c>
     </row>
     <row r="54">
@@ -2401,11 +2401,11 @@
       </c>
       <c r="J54">
         <f>J53+E53-0.7</f>
-        <v>239.62</v>
+        <v>234.91</v>
       </c>
       <c r="K54">
         <f>INT(J54*30+0.5)</f>
-        <v>7189</v>
+        <v>7047</v>
       </c>
     </row>
     <row r="55">
@@ -2438,11 +2438,11 @@
       </c>
       <c r="J55">
         <f>J54+E54-0.7</f>
-        <v>244.32</v>
+        <v>239.61</v>
       </c>
       <c r="K55">
         <f>INT(J55*30+0.5)</f>
-        <v>7330</v>
+        <v>7188</v>
       </c>
     </row>
     <row r="56">
@@ -2450,16 +2450,16 @@
         <v>55</v>
       </c>
       <c r="B56" t="str">
-        <v>photo</v>
+        <v>slide</v>
       </c>
       <c r="C56" t="str">
-        <v>group</v>
+        <v>add3</v>
       </c>
       <c r="D56" t="str">
-        <v>05755B0B-0A5B-49CD-BF06-8D1AF26BDFCB.jpg</v>
+        <v>cert_out1.jpg</v>
       </c>
       <c r="E56">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="F56" t="str">
         <v/>
@@ -2475,11 +2475,11 @@
       </c>
       <c r="J56">
         <f>J55+E55-0.7</f>
-        <v>249.02</v>
+        <v>244.31</v>
       </c>
       <c r="K56">
         <f>INT(J56*30+0.5)</f>
-        <v>7471</v>
+        <v>7329</v>
       </c>
     </row>
     <row r="57">
@@ -2493,7 +2493,7 @@
         <v>group</v>
       </c>
       <c r="D57" t="str">
-        <v>EDE4935B-45DB-4485-ACC1-455FE3959347.jpg</v>
+        <v>05755B0B-0A5B-49CD-BF06-8D1AF26BDFCB.jpg</v>
       </c>
       <c r="E57">
         <v>5.2</v>
@@ -2512,11 +2512,11 @@
       </c>
       <c r="J57">
         <f>J56+E56-0.7</f>
-        <v>253.52</v>
+        <v>249.01</v>
       </c>
       <c r="K57">
         <f>INT(J57*30+0.5)</f>
-        <v>7606</v>
+        <v>7470</v>
       </c>
     </row>
     <row r="58">
@@ -2527,10 +2527,10 @@
         <v>photo</v>
       </c>
       <c r="C58" t="str">
-        <v>bridge</v>
+        <v>group</v>
       </c>
       <c r="D58" t="str">
-        <v>120167_b19cd8fb0ec04df0aba8215e1acad532~mv2.jpg.jpg</v>
+        <v>EDE4935B-45DB-4485-ACC1-455FE3959347.jpg</v>
       </c>
       <c r="E58">
         <v>5.2</v>
@@ -2549,11 +2549,11 @@
       </c>
       <c r="J58">
         <f>J57+E57-0.7</f>
-        <v>258.02</v>
+        <v>253.51</v>
       </c>
       <c r="K58">
         <f>INT(J58*30+0.5)</f>
-        <v>7741</v>
+        <v>7605</v>
       </c>
     </row>
     <row r="59">
@@ -2564,10 +2564,10 @@
         <v>photo</v>
       </c>
       <c r="C59" t="str">
-        <v>group</v>
+        <v>bridge</v>
       </c>
       <c r="D59" t="str">
-        <v>IMG_1252.jpg</v>
+        <v>120167_b19cd8fb0ec04df0aba8215e1acad532~mv2.jpg.jpg</v>
       </c>
       <c r="E59">
         <v>5.2</v>
@@ -2586,11 +2586,11 @@
       </c>
       <c r="J59">
         <f>J58+E58-0.7</f>
-        <v>262.52</v>
+        <v>258.01</v>
       </c>
       <c r="K59">
         <f>INT(J59*30+0.5)</f>
-        <v>7876</v>
+        <v>7740</v>
       </c>
     </row>
     <row r="60">
@@ -2604,7 +2604,7 @@
         <v>group</v>
       </c>
       <c r="D60" t="str">
-        <v>IMG_3668.jpg</v>
+        <v>IMG_1252.jpg</v>
       </c>
       <c r="E60">
         <v>5.2</v>
@@ -2619,15 +2619,15 @@
         <v/>
       </c>
       <c r="I60" t="str">
-        <v>2024:09:13 13:17:03</v>
+        <v/>
       </c>
       <c r="J60">
         <f>J59+E59-0.7</f>
-        <v>267.02</v>
+        <v>262.51</v>
       </c>
       <c r="K60">
         <f>INT(J60*30+0.5)</f>
-        <v>8011</v>
+        <v>7875</v>
       </c>
     </row>
     <row r="61">
@@ -2641,7 +2641,7 @@
         <v>group</v>
       </c>
       <c r="D61" t="str">
-        <v>IMG_5027.jpg</v>
+        <v>IMG_3668.jpg</v>
       </c>
       <c r="E61">
         <v>5.2</v>
@@ -2656,15 +2656,15 @@
         <v/>
       </c>
       <c r="I61" t="str">
-        <v>2025:02:18 23:05:06</v>
+        <v>2024:09:13 13:17:03</v>
       </c>
       <c r="J61">
         <f>J60+E60-0.7</f>
-        <v>271.52</v>
+        <v>267.01</v>
       </c>
       <c r="K61">
         <f>INT(J61*30+0.5)</f>
-        <v>8146</v>
+        <v>8010</v>
       </c>
     </row>
     <row r="62">
@@ -2678,7 +2678,7 @@
         <v>group</v>
       </c>
       <c r="D62" t="str">
-        <v>IMG_9912.jpg</v>
+        <v>IMG_5027.jpg</v>
       </c>
       <c r="E62">
         <v>5.2</v>
@@ -2693,15 +2693,15 @@
         <v/>
       </c>
       <c r="I62" t="str">
-        <v>2023:06:29 16:33:20</v>
+        <v>2025:02:18 23:05:06</v>
       </c>
       <c r="J62">
         <f>J61+E61-0.7</f>
-        <v>276.02</v>
+        <v>271.51</v>
       </c>
       <c r="K62">
         <f>INT(J62*30+0.5)</f>
-        <v>8281</v>
+        <v>8145</v>
       </c>
     </row>
     <row r="63">
@@ -2709,16 +2709,16 @@
         <v>62</v>
       </c>
       <c r="B63" t="str">
-        <v>slide</v>
+        <v>photo</v>
       </c>
       <c r="C63" t="str">
-        <v>slides</v>
+        <v>group</v>
       </c>
       <c r="D63" t="str">
-        <v>09-legacy.jpg</v>
+        <v>IMG_9912.jpg</v>
       </c>
       <c r="E63">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="F63" t="str">
         <v/>
@@ -2727,18 +2727,18 @@
         <v/>
       </c>
       <c r="H63" t="str">
-        <v>時計</v>
+        <v/>
       </c>
       <c r="I63" t="str">
-        <v/>
+        <v>2023:06:29 16:33:20</v>
       </c>
       <c r="J63">
         <f>J62+E62-0.7</f>
-        <v>280.52</v>
+        <v>276.01</v>
       </c>
       <c r="K63">
         <f>INT(J63*30+0.5)</f>
-        <v>8416</v>
+        <v>8280</v>
       </c>
     </row>
     <row r="64">
@@ -2746,13 +2746,13 @@
         <v>63</v>
       </c>
       <c r="B64" t="str">
-        <v>photo</v>
+        <v>slide</v>
       </c>
       <c r="C64" t="str">
-        <v>bridge</v>
+        <v>slides</v>
       </c>
       <c r="D64" t="str">
-        <v>3FD3ABAF-3155-478F-88B2-BBE76A39CDBA.jpg</v>
+        <v>09-legacy.jpg</v>
       </c>
       <c r="E64">
         <v>6</v>
@@ -2764,18 +2764,18 @@
         <v/>
       </c>
       <c r="H64" t="str">
-        <v/>
+        <v>時計</v>
       </c>
       <c r="I64" t="str">
         <v/>
       </c>
       <c r="J64">
         <f>J63+E63-0.7</f>
-        <v>285.82</v>
+        <v>280.51</v>
       </c>
       <c r="K64">
         <f>INT(J64*30+0.5)</f>
-        <v>8575</v>
+        <v>8415</v>
       </c>
     </row>
     <row r="65">
@@ -2783,13 +2783,13 @@
         <v>64</v>
       </c>
       <c r="B65" t="str">
-        <v>slide</v>
+        <v>photo</v>
       </c>
       <c r="C65" t="str">
-        <v>slides</v>
+        <v>bridge</v>
       </c>
       <c r="D65" t="str">
-        <v>10-mirai.jpg</v>
+        <v>3FD3ABAF-3155-478F-88B2-BBE76A39CDBA.jpg</v>
       </c>
       <c r="E65">
         <v>6</v>
@@ -2801,18 +2801,18 @@
         <v/>
       </c>
       <c r="H65" t="str">
-        <v>めくり</v>
+        <v/>
       </c>
       <c r="I65" t="str">
         <v/>
       </c>
       <c r="J65">
         <f>J64+E64-0.7</f>
-        <v>291.12</v>
+        <v>285.81</v>
       </c>
       <c r="K65">
         <f>INT(J65*30+0.5)</f>
-        <v>8734</v>
+        <v>8574</v>
       </c>
     </row>
     <row r="66">
@@ -2820,16 +2820,16 @@
         <v>65</v>
       </c>
       <c r="B66" t="str">
-        <v>photo</v>
+        <v>slide</v>
       </c>
       <c r="C66" t="str">
-        <v>addition2</v>
+        <v>slides</v>
       </c>
       <c r="D66" t="str">
-        <v>IMG_9982.jpg</v>
+        <v>10-mirai.jpg</v>
       </c>
       <c r="E66">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F66" t="str">
         <v/>
@@ -2838,18 +2838,18 @@
         <v/>
       </c>
       <c r="H66" t="str">
-        <v/>
+        <v>めくり</v>
       </c>
       <c r="I66" t="str">
         <v/>
       </c>
       <c r="J66">
         <f>J65+E65-0.7</f>
-        <v>296.42</v>
+        <v>291.11</v>
       </c>
       <c r="K66">
         <f>INT(J66*30+0.5)</f>
-        <v>8893</v>
+        <v>8733</v>
       </c>
     </row>
     <row r="67">
@@ -2860,13 +2860,13 @@
         <v>photo</v>
       </c>
       <c r="C67" t="str">
-        <v>bridge</v>
+        <v>addition2</v>
       </c>
       <c r="D67" t="str">
-        <v>67021D6A-E5CC-4C5B-8908-07663F03DD2E.jpg</v>
+        <v>IMG_9982.jpg</v>
       </c>
       <c r="E67">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F67" t="str">
         <v/>
@@ -2882,23 +2882,60 @@
       </c>
       <c r="J67">
         <f>J66+E66-0.7</f>
-        <v>300.72</v>
+        <v>296.41</v>
       </c>
       <c r="K67">
         <f>INT(J67*30+0.5)</f>
-        <v>9022</v>
+        <v>8892</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="str">
+        <v>photo</v>
+      </c>
+      <c r="C68" t="str">
+        <v>bridge</v>
+      </c>
+      <c r="D68" t="str">
+        <v>67021D6A-E5CC-4C5B-8908-07663F03DD2E.jpg</v>
+      </c>
+      <c r="E68">
+        <v>6</v>
+      </c>
+      <c r="F68" t="str">
+        <v/>
+      </c>
+      <c r="G68" t="str">
+        <v/>
+      </c>
+      <c r="H68" t="str">
+        <v/>
+      </c>
+      <c r="I68" t="str">
+        <v/>
+      </c>
+      <c r="J68">
+        <f>J67+E67-0.7</f>
+        <v>300.71</v>
+      </c>
+      <c r="K68">
+        <f>INT(J68*30+0.5)</f>
+        <v>9021</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K67"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K68"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G401"/>
+  <dimension ref="A1:G404"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -3209,60 +3246,60 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>2</v>
+      <c r="A14" t="str">
+        <v/>
       </c>
       <c r="B14" t="str">
-        <v>addition2</v>
+        <v>add3</v>
       </c>
       <c r="C14" t="str">
-        <v>IMG_6266.jpg</v>
+        <v>1785404756977.jpg</v>
       </c>
       <c r="D14" t="str">
-        <v>2020:07:17 08:29:06</v>
+        <v/>
       </c>
       <c r="E14" t="str">
-        <v>1920</v>
+        <v>1108</v>
       </c>
       <c r="F14" t="str">
-        <v>1440</v>
+        <v>1477</v>
       </c>
       <c r="G14" t="str">
-        <v>横</v>
+        <v>縦</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>65</v>
+      <c r="A15" t="str">
+        <v/>
       </c>
       <c r="B15" t="str">
-        <v>addition2</v>
+        <v>add3</v>
       </c>
       <c r="C15" t="str">
-        <v>IMG_9982.jpg</v>
+        <v>IMG_1113.JPG</v>
       </c>
       <c r="D15" t="str">
         <v/>
       </c>
       <c r="E15" t="str">
-        <v>1440</v>
+        <v>1920</v>
       </c>
       <c r="F15" t="str">
-        <v>1920</v>
+        <v>1440</v>
       </c>
       <c r="G15" t="str">
-        <v>縦</v>
+        <v>横</v>
       </c>
     </row>
     <row r="16">
       <c r="A16">
-        <v>17</v>
+        <v>55</v>
       </c>
       <c r="B16" t="str">
-        <v>addition2</v>
+        <v>add3</v>
       </c>
       <c r="C16" t="str">
-        <v>スクリーンショット_2026-07-28_16.14.39.jpg</v>
+        <v>cert_out1.jpg</v>
       </c>
       <c r="D16" t="str">
         <v/>
@@ -3271,7 +3308,7 @@
         <v>1920</v>
       </c>
       <c r="F16" t="str">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="G16" t="str">
         <v>横</v>
@@ -3279,22 +3316,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>43</v>
+        <v>2</v>
       </c>
       <c r="B17" t="str">
         <v>addition2</v>
       </c>
       <c r="C17" t="str">
-        <v>スクリーンショット_2026-07-28_16.17.49.jpg</v>
+        <v>IMG_6266.jpg</v>
       </c>
       <c r="D17" t="str">
-        <v/>
+        <v>2020:07:17 08:29:06</v>
       </c>
       <c r="E17" t="str">
         <v>1920</v>
       </c>
       <c r="F17" t="str">
-        <v>1079</v>
+        <v>1440</v>
       </c>
       <c r="G17" t="str">
         <v>横</v>
@@ -3302,36 +3339,36 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="B18" t="str">
-        <v>bridge</v>
+        <v>addition2</v>
       </c>
       <c r="C18" t="str">
-        <v>120167_b19cd8fb0ec04df0aba8215e1acad532~mv2.jpg.jpg</v>
+        <v>IMG_9982.jpg</v>
       </c>
       <c r="D18" t="str">
         <v/>
       </c>
       <c r="E18" t="str">
-        <v>1920</v>
+        <v>1440</v>
       </c>
       <c r="F18" t="str">
-        <v>1416</v>
+        <v>1920</v>
       </c>
       <c r="G18" t="str">
-        <v>横</v>
+        <v>縦</v>
       </c>
     </row>
     <row r="19">
       <c r="A19">
-        <v>63</v>
+        <v>17</v>
       </c>
       <c r="B19" t="str">
-        <v>bridge</v>
+        <v>addition2</v>
       </c>
       <c r="C19" t="str">
-        <v>3FD3ABAF-3155-478F-88B2-BBE76A39CDBA.jpg</v>
+        <v>スクリーンショット_2026-07-28_16.14.39.jpg</v>
       </c>
       <c r="D19" t="str">
         <v/>
@@ -3340,7 +3377,7 @@
         <v>1920</v>
       </c>
       <c r="F19" t="str">
-        <v>1440</v>
+        <v>1078</v>
       </c>
       <c r="G19" t="str">
         <v>横</v>
@@ -3348,13 +3385,13 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="B20" t="str">
-        <v>bridge</v>
+        <v>addition2</v>
       </c>
       <c r="C20" t="str">
-        <v>67021D6A-E5CC-4C5B-8908-07663F03DD2E.jpg</v>
+        <v>スクリーンショット_2026-07-28_16.17.49.jpg</v>
       </c>
       <c r="D20" t="str">
         <v/>
@@ -3363,21 +3400,21 @@
         <v>1920</v>
       </c>
       <c r="F20" t="str">
-        <v>1440</v>
+        <v>1079</v>
       </c>
       <c r="G20" t="str">
         <v>横</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="str">
-        <v/>
+      <c r="A21">
+        <v>58</v>
       </c>
       <c r="B21" t="str">
         <v>bridge</v>
       </c>
       <c r="C21" t="str">
-        <v>7DC8739D-CF47-49D8-A351-2491438956F7.jpg</v>
+        <v>120167_b19cd8fb0ec04df0aba8215e1acad532~mv2.jpg.jpg</v>
       </c>
       <c r="D21" t="str">
         <v/>
@@ -3386,24 +3423,24 @@
         <v>1920</v>
       </c>
       <c r="F21" t="str">
-        <v>1440</v>
+        <v>1416</v>
       </c>
       <c r="G21" t="str">
         <v>横</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="str">
-        <v/>
+      <c r="A22">
+        <v>64</v>
       </c>
       <c r="B22" t="str">
         <v>bridge</v>
       </c>
       <c r="C22" t="str">
-        <v>IMG_0136.jpg</v>
+        <v>3FD3ABAF-3155-478F-88B2-BBE76A39CDBA.jpg</v>
       </c>
       <c r="D22" t="str">
-        <v>2014:01:10 08:57:01</v>
+        <v/>
       </c>
       <c r="E22" t="str">
         <v>1920</v>
@@ -3417,16 +3454,16 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="B23" t="str">
         <v>bridge</v>
       </c>
       <c r="C23" t="str">
-        <v>IMG_0305.jpg</v>
+        <v>67021D6A-E5CC-4C5B-8908-07663F03DD2E.jpg</v>
       </c>
       <c r="D23" t="str">
-        <v>2019:03:22 18:09:53</v>
+        <v/>
       </c>
       <c r="E23" t="str">
         <v>1920</v>
@@ -3446,10 +3483,10 @@
         <v>bridge</v>
       </c>
       <c r="C24" t="str">
-        <v>IMG_1133.jpg</v>
+        <v>7DC8739D-CF47-49D8-A351-2491438956F7.jpg</v>
       </c>
       <c r="D24" t="str">
-        <v>2021:08:11 18:55:02</v>
+        <v/>
       </c>
       <c r="E24" t="str">
         <v>1920</v>
@@ -3469,10 +3506,10 @@
         <v>bridge</v>
       </c>
       <c r="C25" t="str">
-        <v>IMG_1141.jpg</v>
+        <v>IMG_0136.jpg</v>
       </c>
       <c r="D25" t="str">
-        <v>2025:09:29 19:20:44</v>
+        <v>2014:01:10 08:57:01</v>
       </c>
       <c r="E25" t="str">
         <v>1920</v>
@@ -3485,17 +3522,17 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="str">
-        <v/>
+      <c r="A26">
+        <v>21</v>
       </c>
       <c r="B26" t="str">
         <v>bridge</v>
       </c>
       <c r="C26" t="str">
-        <v>IMG_3108.jpg</v>
+        <v>IMG_0305.jpg</v>
       </c>
       <c r="D26" t="str">
-        <v>2024:06:26 08:39:02</v>
+        <v>2019:03:22 18:09:53</v>
       </c>
       <c r="E26" t="str">
         <v>1920</v>
@@ -3515,10 +3552,10 @@
         <v>bridge</v>
       </c>
       <c r="C27" t="str">
-        <v>IMG_3110.jpg</v>
+        <v>IMG_1133.jpg</v>
       </c>
       <c r="D27" t="str">
-        <v>2024:06:26 08:39:28</v>
+        <v>2021:08:11 18:55:02</v>
       </c>
       <c r="E27" t="str">
         <v>1920</v>
@@ -3538,10 +3575,10 @@
         <v>bridge</v>
       </c>
       <c r="C28" t="str">
-        <v>IMG_3574.jpg</v>
+        <v>IMG_1141.jpg</v>
       </c>
       <c r="D28" t="str">
-        <v>2019:10:09 08:45:32</v>
+        <v>2025:09:29 19:20:44</v>
       </c>
       <c r="E28" t="str">
         <v>1920</v>
@@ -3561,10 +3598,10 @@
         <v>bridge</v>
       </c>
       <c r="C29" t="str">
-        <v>IMG_3869.jpg</v>
+        <v>IMG_3108.jpg</v>
       </c>
       <c r="D29" t="str">
-        <v>2024:10:11 18:03:33</v>
+        <v>2024:06:26 08:39:02</v>
       </c>
       <c r="E29" t="str">
         <v>1920</v>
@@ -3584,10 +3621,10 @@
         <v>bridge</v>
       </c>
       <c r="C30" t="str">
-        <v>IMG_3874.jpg</v>
+        <v>IMG_3110.jpg</v>
       </c>
       <c r="D30" t="str">
-        <v>2024:10:11 18:10:36</v>
+        <v>2024:06:26 08:39:28</v>
       </c>
       <c r="E30" t="str">
         <v>1920</v>
@@ -3607,16 +3644,16 @@
         <v>bridge</v>
       </c>
       <c r="C31" t="str">
-        <v>IMG_3900.jpg</v>
+        <v>IMG_3574.jpg</v>
       </c>
       <c r="D31" t="str">
-        <v/>
+        <v>2019:10:09 08:45:32</v>
       </c>
       <c r="E31" t="str">
         <v>1920</v>
       </c>
       <c r="F31" t="str">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="G31" t="str">
         <v>横</v>
@@ -3630,10 +3667,10 @@
         <v>bridge</v>
       </c>
       <c r="C32" t="str">
-        <v>IMG_6262.jpg</v>
+        <v>IMG_3869.jpg</v>
       </c>
       <c r="D32" t="str">
-        <v>2020:07:17 08:28:26</v>
+        <v>2024:10:11 18:03:33</v>
       </c>
       <c r="E32" t="str">
         <v>1920</v>
@@ -3653,10 +3690,10 @@
         <v>bridge</v>
       </c>
       <c r="C33" t="str">
-        <v>IMG_7685.jpg</v>
+        <v>IMG_3874.jpg</v>
       </c>
       <c r="D33" t="str">
-        <v>2023:04:07 19:02:58</v>
+        <v>2024:10:11 18:10:36</v>
       </c>
       <c r="E33" t="str">
         <v>1920</v>
@@ -3676,16 +3713,16 @@
         <v>bridge</v>
       </c>
       <c r="C34" t="str">
-        <v>IMG_9104.jpg</v>
+        <v>IMG_3900.jpg</v>
       </c>
       <c r="D34" t="str">
-        <v>2021:06:07 08:15:11</v>
+        <v/>
       </c>
       <c r="E34" t="str">
         <v>1920</v>
       </c>
       <c r="F34" t="str">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="G34" t="str">
         <v>横</v>
@@ -3696,13 +3733,13 @@
         <v/>
       </c>
       <c r="B35" t="str">
-        <v>byoto</v>
+        <v>bridge</v>
       </c>
       <c r="C35" t="str">
-        <v>IMG_1327.jpg</v>
+        <v>IMG_6262.jpg</v>
       </c>
       <c r="D35" t="str">
-        <v>2012:12:21 18:10:47</v>
+        <v>2020:07:17 08:28:26</v>
       </c>
       <c r="E35" t="str">
         <v>1920</v>
@@ -3719,88 +3756,88 @@
         <v/>
       </c>
       <c r="B36" t="str">
+        <v>bridge</v>
+      </c>
+      <c r="C36" t="str">
+        <v>IMG_7685.jpg</v>
+      </c>
+      <c r="D36" t="str">
+        <v>2023:04:07 19:02:58</v>
+      </c>
+      <c r="E36" t="str">
+        <v>1920</v>
+      </c>
+      <c r="F36" t="str">
+        <v>1440</v>
+      </c>
+      <c r="G36" t="str">
+        <v>横</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v/>
+      </c>
+      <c r="B37" t="str">
+        <v>bridge</v>
+      </c>
+      <c r="C37" t="str">
+        <v>IMG_9104.jpg</v>
+      </c>
+      <c r="D37" t="str">
+        <v>2021:06:07 08:15:11</v>
+      </c>
+      <c r="E37" t="str">
+        <v>1920</v>
+      </c>
+      <c r="F37" t="str">
+        <v>1440</v>
+      </c>
+      <c r="G37" t="str">
+        <v>横</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v/>
+      </c>
+      <c r="B38" t="str">
         <v>byoto</v>
       </c>
-      <c r="C36" t="str">
+      <c r="C38" t="str">
+        <v>IMG_1327.jpg</v>
+      </c>
+      <c r="D38" t="str">
+        <v>2012:12:21 18:10:47</v>
+      </c>
+      <c r="E38" t="str">
+        <v>1920</v>
+      </c>
+      <c r="F38" t="str">
+        <v>1440</v>
+      </c>
+      <c r="G38" t="str">
+        <v>横</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v/>
+      </c>
+      <c r="B39" t="str">
+        <v>byoto</v>
+      </c>
+      <c r="C39" t="str">
         <v>IMG_3149.jpg</v>
       </c>
-      <c r="D36" t="str">
+      <c r="D39" t="str">
         <v>2021:03:31 08:29:26</v>
       </c>
-      <c r="E36" t="str">
-        <v>1920</v>
-      </c>
-      <c r="F36" t="str">
-        <v>1440</v>
-      </c>
-      <c r="G36" t="str">
-        <v>横</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37">
-        <v>27</v>
-      </c>
-      <c r="B37" t="str">
-        <v>byoto</v>
-      </c>
-      <c r="C37" t="str">
-        <v>IMG_9875.jpg</v>
-      </c>
-      <c r="D37" t="str">
-        <v>2021:09:29 19:20:44</v>
-      </c>
-      <c r="E37" t="str">
-        <v>1920</v>
-      </c>
-      <c r="F37" t="str">
-        <v>1440</v>
-      </c>
-      <c r="G37" t="str">
-        <v>横</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38">
-        <v>14</v>
-      </c>
-      <c r="B38" t="str">
-        <v>collage</v>
-      </c>
-      <c r="C38" t="str">
-        <v>01.jpg</v>
-      </c>
-      <c r="D38" t="str">
-        <v/>
-      </c>
-      <c r="E38" t="str">
-        <v>1920</v>
-      </c>
-      <c r="F38" t="str">
-        <v>1088</v>
-      </c>
-      <c r="G38" t="str">
-        <v>横</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39">
-        <v>48</v>
-      </c>
-      <c r="B39" t="str">
-        <v>collage</v>
-      </c>
-      <c r="C39" t="str">
-        <v>02.jpg</v>
-      </c>
-      <c r="D39" t="str">
-        <v/>
-      </c>
       <c r="E39" t="str">
         <v>1920</v>
       </c>
       <c r="F39" t="str">
-        <v>1089</v>
+        <v>1440</v>
       </c>
       <c r="G39" t="str">
         <v>横</v>
@@ -3808,22 +3845,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="B40" t="str">
-        <v>collage</v>
+        <v>byoto</v>
       </c>
       <c r="C40" t="str">
-        <v>03.jpg</v>
+        <v>IMG_9875.jpg</v>
       </c>
       <c r="D40" t="str">
-        <v/>
+        <v>2021:09:29 19:20:44</v>
       </c>
       <c r="E40" t="str">
         <v>1920</v>
       </c>
       <c r="F40" t="str">
-        <v>1075</v>
+        <v>1440</v>
       </c>
       <c r="G40" t="str">
         <v>横</v>
@@ -3831,13 +3868,13 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="B41" t="str">
         <v>collage</v>
       </c>
       <c r="C41" t="str">
-        <v>04.jpg</v>
+        <v>01.jpg</v>
       </c>
       <c r="D41" t="str">
         <v/>
@@ -3846,7 +3883,7 @@
         <v>1920</v>
       </c>
       <c r="F41" t="str">
-        <v>1070</v>
+        <v>1088</v>
       </c>
       <c r="G41" t="str">
         <v>横</v>
@@ -3854,13 +3891,13 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B42" t="str">
         <v>collage</v>
       </c>
       <c r="C42" t="str">
-        <v>05.jpg</v>
+        <v>02.jpg</v>
       </c>
       <c r="D42" t="str">
         <v/>
@@ -3869,7 +3906,7 @@
         <v>1920</v>
       </c>
       <c r="F42" t="str">
-        <v>1076</v>
+        <v>1089</v>
       </c>
       <c r="G42" t="str">
         <v>横</v>
@@ -3877,13 +3914,13 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="B43" t="str">
         <v>collage</v>
       </c>
       <c r="C43" t="str">
-        <v>06.jpg</v>
+        <v>03.jpg</v>
       </c>
       <c r="D43" t="str">
         <v/>
@@ -3892,7 +3929,7 @@
         <v>1920</v>
       </c>
       <c r="F43" t="str">
-        <v>1023</v>
+        <v>1075</v>
       </c>
       <c r="G43" t="str">
         <v>横</v>
@@ -3900,13 +3937,13 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="B44" t="str">
         <v>collage</v>
       </c>
       <c r="C44" t="str">
-        <v>07.jpg</v>
+        <v>04.jpg</v>
       </c>
       <c r="D44" t="str">
         <v/>
@@ -3915,7 +3952,7 @@
         <v>1920</v>
       </c>
       <c r="F44" t="str">
-        <v>977</v>
+        <v>1070</v>
       </c>
       <c r="G44" t="str">
         <v>横</v>
@@ -3923,13 +3960,13 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B45" t="str">
         <v>collage</v>
       </c>
       <c r="C45" t="str">
-        <v>08.jpg</v>
+        <v>05.jpg</v>
       </c>
       <c r="D45" t="str">
         <v/>
@@ -3938,7 +3975,7 @@
         <v>1920</v>
       </c>
       <c r="F45" t="str">
-        <v>1066</v>
+        <v>1076</v>
       </c>
       <c r="G45" t="str">
         <v>横</v>
@@ -3946,13 +3983,13 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="B46" t="str">
         <v>collage</v>
       </c>
       <c r="C46" t="str">
-        <v>09.jpg</v>
+        <v>06.jpg</v>
       </c>
       <c r="D46" t="str">
         <v/>
@@ -3961,7 +3998,7 @@
         <v>1920</v>
       </c>
       <c r="F46" t="str">
-        <v>1075</v>
+        <v>1023</v>
       </c>
       <c r="G46" t="str">
         <v>横</v>
@@ -3969,13 +4006,13 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B47" t="str">
         <v>collage</v>
       </c>
       <c r="C47" t="str">
-        <v>10.jpg</v>
+        <v>07.jpg</v>
       </c>
       <c r="D47" t="str">
         <v/>
@@ -3984,7 +4021,7 @@
         <v>1920</v>
       </c>
       <c r="F47" t="str">
-        <v>1083</v>
+        <v>977</v>
       </c>
       <c r="G47" t="str">
         <v>横</v>
@@ -3992,13 +4029,13 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="B48" t="str">
         <v>collage</v>
       </c>
       <c r="C48" t="str">
-        <v>11.jpg</v>
+        <v>08.jpg</v>
       </c>
       <c r="D48" t="str">
         <v/>
@@ -4007,7 +4044,7 @@
         <v>1920</v>
       </c>
       <c r="F48" t="str">
-        <v>1081</v>
+        <v>1066</v>
       </c>
       <c r="G48" t="str">
         <v>横</v>
@@ -4015,13 +4052,13 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B49" t="str">
         <v>collage</v>
       </c>
       <c r="C49" t="str">
-        <v>12.jpg</v>
+        <v>09.jpg</v>
       </c>
       <c r="D49" t="str">
         <v/>
@@ -4030,7 +4067,7 @@
         <v>1920</v>
       </c>
       <c r="F49" t="str">
-        <v>1063</v>
+        <v>1075</v>
       </c>
       <c r="G49" t="str">
         <v>横</v>
@@ -4038,13 +4075,13 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="B50" t="str">
         <v>collage</v>
       </c>
       <c r="C50" t="str">
-        <v>13.jpg</v>
+        <v>10.jpg</v>
       </c>
       <c r="D50" t="str">
         <v/>
@@ -4053,7 +4090,7 @@
         <v>1920</v>
       </c>
       <c r="F50" t="str">
-        <v>1018</v>
+        <v>1083</v>
       </c>
       <c r="G50" t="str">
         <v>横</v>
@@ -4061,13 +4098,13 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B51" t="str">
         <v>collage</v>
       </c>
       <c r="C51" t="str">
-        <v>14.jpg</v>
+        <v>11.jpg</v>
       </c>
       <c r="D51" t="str">
         <v/>
@@ -4076,7 +4113,7 @@
         <v>1920</v>
       </c>
       <c r="F51" t="str">
-        <v>1072</v>
+        <v>1081</v>
       </c>
       <c r="G51" t="str">
         <v>横</v>
@@ -4084,13 +4121,13 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="B52" t="str">
         <v>collage</v>
       </c>
       <c r="C52" t="str">
-        <v>15.jpg</v>
+        <v>12.jpg</v>
       </c>
       <c r="D52" t="str">
         <v/>
@@ -4099,7 +4136,7 @@
         <v>1920</v>
       </c>
       <c r="F52" t="str">
-        <v>1075</v>
+        <v>1063</v>
       </c>
       <c r="G52" t="str">
         <v>横</v>
@@ -4107,91 +4144,91 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="B53" t="str">
         <v>collage</v>
       </c>
       <c r="C53" t="str">
+        <v>13.jpg</v>
+      </c>
+      <c r="D53" t="str">
+        <v/>
+      </c>
+      <c r="E53" t="str">
+        <v>1920</v>
+      </c>
+      <c r="F53" t="str">
+        <v>1018</v>
+      </c>
+      <c r="G53" t="str">
+        <v>横</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>54</v>
+      </c>
+      <c r="B54" t="str">
+        <v>collage</v>
+      </c>
+      <c r="C54" t="str">
+        <v>14.jpg</v>
+      </c>
+      <c r="D54" t="str">
+        <v/>
+      </c>
+      <c r="E54" t="str">
+        <v>1920</v>
+      </c>
+      <c r="F54" t="str">
+        <v>1072</v>
+      </c>
+      <c r="G54" t="str">
+        <v>横</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>18</v>
+      </c>
+      <c r="B55" t="str">
+        <v>collage</v>
+      </c>
+      <c r="C55" t="str">
+        <v>15.jpg</v>
+      </c>
+      <c r="D55" t="str">
+        <v/>
+      </c>
+      <c r="E55" t="str">
+        <v>1920</v>
+      </c>
+      <c r="F55" t="str">
+        <v>1075</v>
+      </c>
+      <c r="G55" t="str">
+        <v>横</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>4</v>
+      </c>
+      <c r="B56" t="str">
+        <v>collage</v>
+      </c>
+      <c r="C56" t="str">
         <v>16.jpg</v>
       </c>
-      <c r="D53" t="str">
-        <v/>
-      </c>
-      <c r="E53" t="str">
-        <v>1920</v>
-      </c>
-      <c r="F53" t="str">
+      <c r="D56" t="str">
+        <v/>
+      </c>
+      <c r="E56" t="str">
+        <v>1920</v>
+      </c>
+      <c r="F56" t="str">
         <v>1155</v>
-      </c>
-      <c r="G53" t="str">
-        <v>横</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="str">
-        <v/>
-      </c>
-      <c r="B54" t="str">
-        <v>conference</v>
-      </c>
-      <c r="C54" t="str">
-        <v>IMG_0475.jpg</v>
-      </c>
-      <c r="D54" t="str">
-        <v>2021:04:19 19:02:29</v>
-      </c>
-      <c r="E54" t="str">
-        <v>1920</v>
-      </c>
-      <c r="F54" t="str">
-        <v>1440</v>
-      </c>
-      <c r="G54" t="str">
-        <v>横</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="str">
-        <v/>
-      </c>
-      <c r="B55" t="str">
-        <v>conference</v>
-      </c>
-      <c r="C55" t="str">
-        <v>IMG_0763.jpg</v>
-      </c>
-      <c r="D55" t="str">
-        <v>2021:05:17 08:20:20</v>
-      </c>
-      <c r="E55" t="str">
-        <v>1920</v>
-      </c>
-      <c r="F55" t="str">
-        <v>1440</v>
-      </c>
-      <c r="G55" t="str">
-        <v>横</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="str">
-        <v/>
-      </c>
-      <c r="B56" t="str">
-        <v>conference</v>
-      </c>
-      <c r="C56" t="str">
-        <v>IMG_0807.jpg</v>
-      </c>
-      <c r="D56" t="str">
-        <v>2021:05:28 08:10:08</v>
-      </c>
-      <c r="E56" t="str">
-        <v>1920</v>
-      </c>
-      <c r="F56" t="str">
-        <v>1440</v>
       </c>
       <c r="G56" t="str">
         <v>横</v>
@@ -4205,10 +4242,10 @@
         <v>conference</v>
       </c>
       <c r="C57" t="str">
-        <v>IMG_0834.jpg</v>
+        <v>IMG_0475.jpg</v>
       </c>
       <c r="D57" t="str">
-        <v>2021:06:04 08:18:54</v>
+        <v>2021:04:19 19:02:29</v>
       </c>
       <c r="E57" t="str">
         <v>1920</v>
@@ -4228,10 +4265,10 @@
         <v>conference</v>
       </c>
       <c r="C58" t="str">
-        <v>IMG_0890.jpg</v>
+        <v>IMG_0763.jpg</v>
       </c>
       <c r="D58" t="str">
-        <v>2021:06:14 07:40:24</v>
+        <v>2021:05:17 08:20:20</v>
       </c>
       <c r="E58" t="str">
         <v>1920</v>
@@ -4251,10 +4288,10 @@
         <v>conference</v>
       </c>
       <c r="C59" t="str">
-        <v>IMG_1037.jpg</v>
+        <v>IMG_0807.jpg</v>
       </c>
       <c r="D59" t="str">
-        <v>2021:07:16 08:29:42</v>
+        <v>2021:05:28 08:10:08</v>
       </c>
       <c r="E59" t="str">
         <v>1920</v>
@@ -4274,10 +4311,10 @@
         <v>conference</v>
       </c>
       <c r="C60" t="str">
-        <v>IMG_8582.jpg</v>
+        <v>IMG_0834.jpg</v>
       </c>
       <c r="D60" t="str">
-        <v>2024:05:17 08:30:17</v>
+        <v>2021:06:04 08:18:54</v>
       </c>
       <c r="E60" t="str">
         <v>1920</v>
@@ -4297,10 +4334,10 @@
         <v>conference</v>
       </c>
       <c r="C61" t="str">
-        <v>IMG_8583.jpg</v>
+        <v>IMG_0890.jpg</v>
       </c>
       <c r="D61" t="str">
-        <v>2024:05:17 08:33:51</v>
+        <v>2021:06:14 07:40:24</v>
       </c>
       <c r="E61" t="str">
         <v>1920</v>
@@ -4320,10 +4357,10 @@
         <v>conference</v>
       </c>
       <c r="C62" t="str">
-        <v>IMG_8584.jpg</v>
+        <v>IMG_1037.jpg</v>
       </c>
       <c r="D62" t="str">
-        <v>2024:05:17 08:34:25</v>
+        <v>2021:07:16 08:29:42</v>
       </c>
       <c r="E62" t="str">
         <v>1920</v>
@@ -4343,10 +4380,10 @@
         <v>conference</v>
       </c>
       <c r="C63" t="str">
-        <v>IMG_8642.jpg</v>
+        <v>IMG_8582.jpg</v>
       </c>
       <c r="D63" t="str">
-        <v>2024:05:22 08:37:41</v>
+        <v>2024:05:17 08:30:17</v>
       </c>
       <c r="E63" t="str">
         <v>1920</v>
@@ -4366,10 +4403,10 @@
         <v>conference</v>
       </c>
       <c r="C64" t="str">
-        <v>IMG_8643.jpg</v>
+        <v>IMG_8583.jpg</v>
       </c>
       <c r="D64" t="str">
-        <v>2024:05:22 08:37:55</v>
+        <v>2024:05:17 08:33:51</v>
       </c>
       <c r="E64" t="str">
         <v>1920</v>
@@ -4389,10 +4426,10 @@
         <v>conference</v>
       </c>
       <c r="C65" t="str">
-        <v>IMG_8644.jpg</v>
+        <v>IMG_8584.jpg</v>
       </c>
       <c r="D65" t="str">
-        <v>2024:05:22 08:42:44</v>
+        <v>2024:05:17 08:34:25</v>
       </c>
       <c r="E65" t="str">
         <v>1920</v>
@@ -4412,10 +4449,10 @@
         <v>conference</v>
       </c>
       <c r="C66" t="str">
-        <v>IMG_8774.jpg</v>
+        <v>IMG_8642.jpg</v>
       </c>
       <c r="D66" t="str">
-        <v>2024:06:21 08:38:20</v>
+        <v>2024:05:22 08:37:41</v>
       </c>
       <c r="E66" t="str">
         <v>1920</v>
@@ -4435,10 +4472,10 @@
         <v>conference</v>
       </c>
       <c r="C67" t="str">
-        <v>IMG_8821.jpg</v>
+        <v>IMG_8643.jpg</v>
       </c>
       <c r="D67" t="str">
-        <v>2024:06:26 08:25:06</v>
+        <v>2024:05:22 08:37:55</v>
       </c>
       <c r="E67" t="str">
         <v>1920</v>
@@ -4458,16 +4495,16 @@
         <v>conference</v>
       </c>
       <c r="C68" t="str">
-        <v>IMG_9738.jpg</v>
+        <v>IMG_8644.jpg</v>
       </c>
       <c r="D68" t="str">
-        <v>2024:11:13 08:43:35</v>
+        <v>2024:05:22 08:42:44</v>
       </c>
       <c r="E68" t="str">
         <v>1920</v>
       </c>
       <c r="F68" t="str">
-        <v>1080</v>
+        <v>1440</v>
       </c>
       <c r="G68" t="str">
         <v>横</v>
@@ -4478,22 +4515,22 @@
         <v/>
       </c>
       <c r="B69" t="str">
-        <v>exterior</v>
+        <v>conference</v>
       </c>
       <c r="C69" t="str">
-        <v>images.jpg</v>
+        <v>IMG_8774.jpg</v>
       </c>
       <c r="D69" t="str">
-        <v/>
+        <v>2024:06:21 08:38:20</v>
       </c>
       <c r="E69" t="str">
-        <v>528</v>
+        <v>1920</v>
       </c>
       <c r="F69" t="str">
-        <v>1920</v>
+        <v>1440</v>
       </c>
       <c r="G69" t="str">
-        <v>縦</v>
+        <v>横</v>
       </c>
     </row>
     <row r="70">
@@ -4501,19 +4538,19 @@
         <v/>
       </c>
       <c r="B70" t="str">
-        <v>exterior</v>
+        <v>conference</v>
       </c>
       <c r="C70" t="str">
-        <v>images2.jpg</v>
+        <v>IMG_8821.jpg</v>
       </c>
       <c r="D70" t="str">
-        <v/>
+        <v>2024:06:26 08:25:06</v>
       </c>
       <c r="E70" t="str">
         <v>1920</v>
       </c>
       <c r="F70" t="str">
-        <v>1261</v>
+        <v>1440</v>
       </c>
       <c r="G70" t="str">
         <v>横</v>
@@ -4524,22 +4561,22 @@
         <v/>
       </c>
       <c r="B71" t="str">
-        <v>faces</v>
+        <v>conference</v>
       </c>
       <c r="C71" t="str">
-        <v>images4.jpg</v>
+        <v>IMG_9738.jpg</v>
       </c>
       <c r="D71" t="str">
-        <v/>
+        <v>2024:11:13 08:43:35</v>
       </c>
       <c r="E71" t="str">
-        <v>1686</v>
+        <v>1920</v>
       </c>
       <c r="F71" t="str">
-        <v>1920</v>
+        <v>1080</v>
       </c>
       <c r="G71" t="str">
-        <v>縦</v>
+        <v>横</v>
       </c>
     </row>
     <row r="72">
@@ -4547,16 +4584,16 @@
         <v/>
       </c>
       <c r="B72" t="str">
-        <v>faces</v>
+        <v>exterior</v>
       </c>
       <c r="C72" t="str">
-        <v>images5.jpg</v>
+        <v>images.jpg</v>
       </c>
       <c r="D72" t="str">
         <v/>
       </c>
       <c r="E72" t="str">
-        <v>1686</v>
+        <v>528</v>
       </c>
       <c r="F72" t="str">
         <v>1920</v>
@@ -4570,45 +4607,45 @@
         <v/>
       </c>
       <c r="B73" t="str">
+        <v>exterior</v>
+      </c>
+      <c r="C73" t="str">
+        <v>images2.jpg</v>
+      </c>
+      <c r="D73" t="str">
+        <v/>
+      </c>
+      <c r="E73" t="str">
+        <v>1920</v>
+      </c>
+      <c r="F73" t="str">
+        <v>1261</v>
+      </c>
+      <c r="G73" t="str">
+        <v>横</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v/>
+      </c>
+      <c r="B74" t="str">
         <v>faces</v>
       </c>
-      <c r="C73" t="str">
-        <v>images_furuko.jpg</v>
-      </c>
-      <c r="D73" t="str">
-        <v/>
-      </c>
-      <c r="E73" t="str">
-        <v>1180</v>
-      </c>
-      <c r="F73" t="str">
-        <v>1920</v>
-      </c>
-      <c r="G73" t="str">
+      <c r="C74" t="str">
+        <v>images4.jpg</v>
+      </c>
+      <c r="D74" t="str">
+        <v/>
+      </c>
+      <c r="E74" t="str">
+        <v>1686</v>
+      </c>
+      <c r="F74" t="str">
+        <v>1920</v>
+      </c>
+      <c r="G74" t="str">
         <v>縦</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74">
-        <v>34</v>
-      </c>
-      <c r="B74" t="str">
-        <v>fellows-intl</v>
-      </c>
-      <c r="C74" t="str">
-        <v>295b2717-e99e-4b5a-9a0f-f8de1ca5e74e.jpg</v>
-      </c>
-      <c r="D74" t="str">
-        <v/>
-      </c>
-      <c r="E74" t="str">
-        <v>1920</v>
-      </c>
-      <c r="F74" t="str">
-        <v>1440</v>
-      </c>
-      <c r="G74" t="str">
-        <v>横</v>
       </c>
     </row>
     <row r="75">
@@ -4616,22 +4653,22 @@
         <v/>
       </c>
       <c r="B75" t="str">
-        <v>fellows-intl</v>
+        <v>faces</v>
       </c>
       <c r="C75" t="str">
-        <v>2B6F956A-1587-47E9-AB64-ED9E3B8CE465.jpg</v>
+        <v>images5.jpg</v>
       </c>
       <c r="D75" t="str">
         <v/>
       </c>
       <c r="E75" t="str">
-        <v>1920</v>
+        <v>1686</v>
       </c>
       <c r="F75" t="str">
-        <v>1440</v>
+        <v>1920</v>
       </c>
       <c r="G75" t="str">
-        <v>横</v>
+        <v>縦</v>
       </c>
     </row>
     <row r="76">
@@ -4639,36 +4676,36 @@
         <v/>
       </c>
       <c r="B76" t="str">
-        <v>fellows-intl</v>
+        <v>faces</v>
       </c>
       <c r="C76" t="str">
-        <v>3753EF23-7AA7-48A1-9054-F7FC1C08F153.jpg</v>
+        <v>images_furuko.jpg</v>
       </c>
       <c r="D76" t="str">
         <v/>
       </c>
       <c r="E76" t="str">
-        <v>1920</v>
+        <v>1180</v>
       </c>
       <c r="F76" t="str">
-        <v>1440</v>
+        <v>1920</v>
       </c>
       <c r="G76" t="str">
-        <v>横</v>
+        <v>縦</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="str">
-        <v/>
+      <c r="A77">
+        <v>34</v>
       </c>
       <c r="B77" t="str">
         <v>fellows-intl</v>
       </c>
       <c r="C77" t="str">
-        <v>IMG_0232.jpg</v>
+        <v>295b2717-e99e-4b5a-9a0f-f8de1ca5e74e.jpg</v>
       </c>
       <c r="D77" t="str">
-        <v>2019:09:20 21:40:01</v>
+        <v/>
       </c>
       <c r="E77" t="str">
         <v>1920</v>
@@ -4688,7 +4725,7 @@
         <v>fellows-intl</v>
       </c>
       <c r="C78" t="str">
-        <v>IMG_0881.jpg</v>
+        <v>2B6F956A-1587-47E9-AB64-ED9E3B8CE465.jpg</v>
       </c>
       <c r="D78" t="str">
         <v/>
@@ -4697,7 +4734,7 @@
         <v>1920</v>
       </c>
       <c r="F78" t="str">
-        <v>1079</v>
+        <v>1440</v>
       </c>
       <c r="G78" t="str">
         <v>横</v>
@@ -4711,7 +4748,7 @@
         <v>fellows-intl</v>
       </c>
       <c r="C79" t="str">
-        <v>IMG_1245.jpg</v>
+        <v>3753EF23-7AA7-48A1-9054-F7FC1C08F153.jpg</v>
       </c>
       <c r="D79" t="str">
         <v/>
@@ -4720,7 +4757,7 @@
         <v>1920</v>
       </c>
       <c r="F79" t="str">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="G79" t="str">
         <v>横</v>
@@ -4734,10 +4771,10 @@
         <v>fellows-intl</v>
       </c>
       <c r="C80" t="str">
-        <v>IMG_1255.jpg</v>
+        <v>IMG_0232.jpg</v>
       </c>
       <c r="D80" t="str">
-        <v>2025:09:06 14:59:33</v>
+        <v>2019:09:20 21:40:01</v>
       </c>
       <c r="E80" t="str">
         <v>1920</v>
@@ -4757,16 +4794,16 @@
         <v>fellows-intl</v>
       </c>
       <c r="C81" t="str">
-        <v>IMG_1257.jpg</v>
+        <v>IMG_0881.jpg</v>
       </c>
       <c r="D81" t="str">
-        <v>2025:09:06 15:41:23</v>
+        <v/>
       </c>
       <c r="E81" t="str">
         <v>1920</v>
       </c>
       <c r="F81" t="str">
-        <v>1440</v>
+        <v>1079</v>
       </c>
       <c r="G81" t="str">
         <v>横</v>
@@ -4780,16 +4817,16 @@
         <v>fellows-intl</v>
       </c>
       <c r="C82" t="str">
-        <v>IMG_1258.jpg</v>
+        <v>IMG_1245.jpg</v>
       </c>
       <c r="D82" t="str">
-        <v>2025:09:06 16:19:01</v>
+        <v/>
       </c>
       <c r="E82" t="str">
         <v>1920</v>
       </c>
       <c r="F82" t="str">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="G82" t="str">
         <v>横</v>
@@ -4803,10 +4840,10 @@
         <v>fellows-intl</v>
       </c>
       <c r="C83" t="str">
-        <v>IMG_1259.jpg</v>
+        <v>IMG_1255.jpg</v>
       </c>
       <c r="D83" t="str">
-        <v>2025:09:06 17:21:50</v>
+        <v>2025:09:06 14:59:33</v>
       </c>
       <c r="E83" t="str">
         <v>1920</v>
@@ -4826,10 +4863,10 @@
         <v>fellows-intl</v>
       </c>
       <c r="C84" t="str">
-        <v>IMG_1265.jpg</v>
+        <v>IMG_1257.jpg</v>
       </c>
       <c r="D84" t="str">
-        <v>2025:09:06 17:22:51</v>
+        <v>2025:09:06 15:41:23</v>
       </c>
       <c r="E84" t="str">
         <v>1920</v>
@@ -4849,10 +4886,10 @@
         <v>fellows-intl</v>
       </c>
       <c r="C85" t="str">
-        <v>IMG_1275.jpg</v>
+        <v>IMG_1258.jpg</v>
       </c>
       <c r="D85" t="str">
-        <v>2023:12:22 23:02:45</v>
+        <v>2025:09:06 16:19:01</v>
       </c>
       <c r="E85" t="str">
         <v>1920</v>
@@ -4872,16 +4909,16 @@
         <v>fellows-intl</v>
       </c>
       <c r="C86" t="str">
-        <v>IMG_1553.jpg</v>
+        <v>IMG_1259.jpg</v>
       </c>
       <c r="D86" t="str">
-        <v/>
+        <v>2025:09:06 17:21:50</v>
       </c>
       <c r="E86" t="str">
         <v>1920</v>
       </c>
       <c r="F86" t="str">
-        <v>1080</v>
+        <v>1440</v>
       </c>
       <c r="G86" t="str">
         <v>横</v>
@@ -4895,10 +4932,10 @@
         <v>fellows-intl</v>
       </c>
       <c r="C87" t="str">
-        <v>IMG_2119.jpg</v>
+        <v>IMG_1265.jpg</v>
       </c>
       <c r="D87" t="str">
-        <v/>
+        <v>2025:09:06 17:22:51</v>
       </c>
       <c r="E87" t="str">
         <v>1920</v>
@@ -4918,10 +4955,10 @@
         <v>fellows-intl</v>
       </c>
       <c r="C88" t="str">
-        <v>IMG_2802.jpg</v>
+        <v>IMG_1275.jpg</v>
       </c>
       <c r="D88" t="str">
-        <v>2024:05:24 20:56:17</v>
+        <v>2023:12:22 23:02:45</v>
       </c>
       <c r="E88" t="str">
         <v>1920</v>
@@ -4941,16 +4978,16 @@
         <v>fellows-intl</v>
       </c>
       <c r="C89" t="str">
-        <v>IMG_2992.jpg</v>
+        <v>IMG_1553.jpg</v>
       </c>
       <c r="D89" t="str">
-        <v>2026:02:06 22:15:34</v>
+        <v/>
       </c>
       <c r="E89" t="str">
         <v>1920</v>
       </c>
       <c r="F89" t="str">
-        <v>1440</v>
+        <v>1080</v>
       </c>
       <c r="G89" t="str">
         <v>横</v>
@@ -4964,10 +5001,10 @@
         <v>fellows-intl</v>
       </c>
       <c r="C90" t="str">
-        <v>IMG_4245.jpg</v>
+        <v>IMG_2119.jpg</v>
       </c>
       <c r="D90" t="str">
-        <v>2022:10:07 20:03:25</v>
+        <v/>
       </c>
       <c r="E90" t="str">
         <v>1920</v>
@@ -4987,10 +5024,10 @@
         <v>fellows-intl</v>
       </c>
       <c r="C91" t="str">
-        <v>IMG_4431.jpg</v>
+        <v>IMG_2802.jpg</v>
       </c>
       <c r="D91" t="str">
-        <v>2024:12:16 22:33:10</v>
+        <v>2024:05:24 20:56:17</v>
       </c>
       <c r="E91" t="str">
         <v>1920</v>
@@ -5010,10 +5047,10 @@
         <v>fellows-intl</v>
       </c>
       <c r="C92" t="str">
-        <v>IMG_4632.jpg</v>
+        <v>IMG_2992.jpg</v>
       </c>
       <c r="D92" t="str">
-        <v>2025:10:27 19:27:28</v>
+        <v>2026:02:06 22:15:34</v>
       </c>
       <c r="E92" t="str">
         <v>1920</v>
@@ -5026,17 +5063,17 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93">
-        <v>38</v>
+      <c r="A93" t="str">
+        <v/>
       </c>
       <c r="B93" t="str">
         <v>fellows-intl</v>
       </c>
       <c r="C93" t="str">
-        <v>IMG_4707.jpg</v>
+        <v>IMG_4245.jpg</v>
       </c>
       <c r="D93" t="str">
-        <v>2025:10:29 21:00:18</v>
+        <v>2022:10:07 20:03:25</v>
       </c>
       <c r="E93" t="str">
         <v>1920</v>
@@ -5056,16 +5093,16 @@
         <v>fellows-intl</v>
       </c>
       <c r="C94" t="str">
-        <v>IMG_5409.jpg</v>
+        <v>IMG_4431.jpg</v>
       </c>
       <c r="D94" t="str">
-        <v/>
+        <v>2024:12:16 22:33:10</v>
       </c>
       <c r="E94" t="str">
         <v>1920</v>
       </c>
       <c r="F94" t="str">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="G94" t="str">
         <v>横</v>
@@ -5079,33 +5116,33 @@
         <v>fellows-intl</v>
       </c>
       <c r="C95" t="str">
-        <v>IMG_5552.jpg</v>
+        <v>IMG_4632.jpg</v>
       </c>
       <c r="D95" t="str">
-        <v>2026:01:19 21:18:43</v>
+        <v>2025:10:27 19:27:28</v>
       </c>
       <c r="E95" t="str">
         <v>1920</v>
       </c>
       <c r="F95" t="str">
-        <v>1080</v>
+        <v>1440</v>
       </c>
       <c r="G95" t="str">
         <v>横</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="str">
-        <v/>
+      <c r="A96">
+        <v>38</v>
       </c>
       <c r="B96" t="str">
         <v>fellows-intl</v>
       </c>
       <c r="C96" t="str">
-        <v>IMG_5645.jpg</v>
+        <v>IMG_4707.jpg</v>
       </c>
       <c r="D96" t="str">
-        <v>2025:05:12 19:31:17</v>
+        <v>2025:10:29 21:00:18</v>
       </c>
       <c r="E96" t="str">
         <v>1920</v>
@@ -5118,14 +5155,14 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97">
-        <v>40</v>
+      <c r="A97" t="str">
+        <v/>
       </c>
       <c r="B97" t="str">
         <v>fellows-intl</v>
       </c>
       <c r="C97" t="str">
-        <v>IMG_5714.jpg</v>
+        <v>IMG_5409.jpg</v>
       </c>
       <c r="D97" t="str">
         <v/>
@@ -5148,16 +5185,16 @@
         <v>fellows-intl</v>
       </c>
       <c r="C98" t="str">
-        <v>IMG_5862.jpg</v>
+        <v>IMG_5552.jpg</v>
       </c>
       <c r="D98" t="str">
-        <v/>
+        <v>2026:01:19 21:18:43</v>
       </c>
       <c r="E98" t="str">
         <v>1920</v>
       </c>
       <c r="F98" t="str">
-        <v>1439</v>
+        <v>1080</v>
       </c>
       <c r="G98" t="str">
         <v>横</v>
@@ -5171,10 +5208,10 @@
         <v>fellows-intl</v>
       </c>
       <c r="C99" t="str">
-        <v>IMG_5899.jpg</v>
+        <v>IMG_5645.jpg</v>
       </c>
       <c r="D99" t="str">
-        <v>2022:12:16 19:40:56</v>
+        <v>2025:05:12 19:31:17</v>
       </c>
       <c r="E99" t="str">
         <v>1920</v>
@@ -5187,14 +5224,14 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="str">
-        <v/>
+      <c r="A100">
+        <v>40</v>
       </c>
       <c r="B100" t="str">
         <v>fellows-intl</v>
       </c>
       <c r="C100" t="str">
-        <v>IMG_8021.jpg</v>
+        <v>IMG_5714.jpg</v>
       </c>
       <c r="D100" t="str">
         <v/>
@@ -5203,7 +5240,7 @@
         <v>1920</v>
       </c>
       <c r="F100" t="str">
-        <v>1079</v>
+        <v>1439</v>
       </c>
       <c r="G100" t="str">
         <v>横</v>
@@ -5217,16 +5254,16 @@
         <v>fellows-intl</v>
       </c>
       <c r="C101" t="str">
-        <v>IMG_8171.jpg</v>
+        <v>IMG_5862.jpg</v>
       </c>
       <c r="D101" t="str">
-        <v>2023:01:13 15:46:31</v>
+        <v/>
       </c>
       <c r="E101" t="str">
         <v>1920</v>
       </c>
       <c r="F101" t="str">
-        <v>1080</v>
+        <v>1439</v>
       </c>
       <c r="G101" t="str">
         <v>横</v>
@@ -5240,16 +5277,16 @@
         <v>fellows-intl</v>
       </c>
       <c r="C102" t="str">
-        <v>IMG_8333.jpg</v>
+        <v>IMG_5899.jpg</v>
       </c>
       <c r="D102" t="str">
-        <v>2023:02:22 08:44:22</v>
+        <v>2022:12:16 19:40:56</v>
       </c>
       <c r="E102" t="str">
         <v>1920</v>
       </c>
       <c r="F102" t="str">
-        <v>1080</v>
+        <v>1440</v>
       </c>
       <c r="G102" t="str">
         <v>横</v>
@@ -5263,7 +5300,7 @@
         <v>fellows-intl</v>
       </c>
       <c r="C103" t="str">
-        <v>IMG_8780.jpg</v>
+        <v>IMG_8021.jpg</v>
       </c>
       <c r="D103" t="str">
         <v/>
@@ -5272,7 +5309,7 @@
         <v>1920</v>
       </c>
       <c r="F103" t="str">
-        <v>1440</v>
+        <v>1079</v>
       </c>
       <c r="G103" t="str">
         <v>横</v>
@@ -5286,16 +5323,16 @@
         <v>fellows-intl</v>
       </c>
       <c r="C104" t="str">
-        <v>IMG_8786.jpg</v>
+        <v>IMG_8171.jpg</v>
       </c>
       <c r="D104" t="str">
-        <v/>
+        <v>2023:01:13 15:46:31</v>
       </c>
       <c r="E104" t="str">
         <v>1920</v>
       </c>
       <c r="F104" t="str">
-        <v>1440</v>
+        <v>1080</v>
       </c>
       <c r="G104" t="str">
         <v>横</v>
@@ -5309,16 +5346,16 @@
         <v>fellows-intl</v>
       </c>
       <c r="C105" t="str">
-        <v>IMG_8978.jpg</v>
+        <v>IMG_8333.jpg</v>
       </c>
       <c r="D105" t="str">
-        <v/>
+        <v>2023:02:22 08:44:22</v>
       </c>
       <c r="E105" t="str">
         <v>1920</v>
       </c>
       <c r="F105" t="str">
-        <v>1440</v>
+        <v>1080</v>
       </c>
       <c r="G105" t="str">
         <v>横</v>
@@ -5332,10 +5369,10 @@
         <v>fellows-intl</v>
       </c>
       <c r="C106" t="str">
-        <v>IMG_9613.jpg</v>
+        <v>IMG_8780.jpg</v>
       </c>
       <c r="D106" t="str">
-        <v>2026:03:23 21:16:22</v>
+        <v/>
       </c>
       <c r="E106" t="str">
         <v>1920</v>
@@ -5348,14 +5385,14 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107">
-        <v>41</v>
+      <c r="A107" t="str">
+        <v/>
       </c>
       <c r="B107" t="str">
         <v>fellows-intl</v>
       </c>
       <c r="C107" t="str">
-        <v>IMG_9625.jpg</v>
+        <v>IMG_8786.jpg</v>
       </c>
       <c r="D107" t="str">
         <v/>
@@ -5364,7 +5401,7 @@
         <v>1920</v>
       </c>
       <c r="F107" t="str">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="G107" t="str">
         <v>横</v>
@@ -5378,7 +5415,7 @@
         <v>fellows-intl</v>
       </c>
       <c r="C108" t="str">
-        <v>IMG_9688.jpg</v>
+        <v>IMG_8978.jpg</v>
       </c>
       <c r="D108" t="str">
         <v/>
@@ -5401,10 +5438,10 @@
         <v>fellows-intl</v>
       </c>
       <c r="C109" t="str">
-        <v>IMG_9848.jpg</v>
+        <v>IMG_9613.jpg</v>
       </c>
       <c r="D109" t="str">
-        <v>2024:12:25 22:07:54</v>
+        <v>2026:03:23 21:16:22</v>
       </c>
       <c r="E109" t="str">
         <v>1920</v>
@@ -5417,23 +5454,23 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="str">
-        <v/>
+      <c r="A110">
+        <v>41</v>
       </c>
       <c r="B110" t="str">
         <v>fellows-intl</v>
       </c>
       <c r="C110" t="str">
-        <v>IMG_9851.jpg</v>
+        <v>IMG_9625.jpg</v>
       </c>
       <c r="D110" t="str">
-        <v>2024:12:25 22:08:15</v>
+        <v/>
       </c>
       <c r="E110" t="str">
         <v>1920</v>
       </c>
       <c r="F110" t="str">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="G110" t="str">
         <v>横</v>
@@ -5447,10 +5484,10 @@
         <v>fellows-intl</v>
       </c>
       <c r="C111" t="str">
-        <v>IMG_9855.jpg</v>
+        <v>IMG_9688.jpg</v>
       </c>
       <c r="D111" t="str">
-        <v>2024:12:25 22:08:47</v>
+        <v/>
       </c>
       <c r="E111" t="str">
         <v>1920</v>
@@ -5467,19 +5504,19 @@
         <v/>
       </c>
       <c r="B112" t="str">
-        <v>fellows-jp</v>
+        <v>fellows-intl</v>
       </c>
       <c r="C112" t="str">
-        <v>IMG_0077.jpg</v>
+        <v>IMG_9848.jpg</v>
       </c>
       <c r="D112" t="str">
-        <v>2025:03:04 22:10:05</v>
+        <v>2024:12:25 22:07:54</v>
       </c>
       <c r="E112" t="str">
         <v>1920</v>
       </c>
       <c r="F112" t="str">
-        <v>1080</v>
+        <v>1440</v>
       </c>
       <c r="G112" t="str">
         <v>横</v>
@@ -5490,13 +5527,13 @@
         <v/>
       </c>
       <c r="B113" t="str">
-        <v>fellows-jp</v>
+        <v>fellows-intl</v>
       </c>
       <c r="C113" t="str">
-        <v>IMG_0084.jpg</v>
+        <v>IMG_9851.jpg</v>
       </c>
       <c r="D113" t="str">
-        <v/>
+        <v>2024:12:25 22:08:15</v>
       </c>
       <c r="E113" t="str">
         <v>1920</v>
@@ -5509,17 +5546,17 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114">
-        <v>44</v>
+      <c r="A114" t="str">
+        <v/>
       </c>
       <c r="B114" t="str">
-        <v>fellows-jp</v>
+        <v>fellows-intl</v>
       </c>
       <c r="C114" t="str">
-        <v>IMG_0088.jpg</v>
+        <v>IMG_9855.jpg</v>
       </c>
       <c r="D114" t="str">
-        <v>2025:03:05 10:25:27</v>
+        <v>2024:12:25 22:08:47</v>
       </c>
       <c r="E114" t="str">
         <v>1920</v>
@@ -5539,16 +5576,16 @@
         <v>fellows-jp</v>
       </c>
       <c r="C115" t="str">
-        <v>IMG_1537.jpg</v>
+        <v>IMG_0077.jpg</v>
       </c>
       <c r="D115" t="str">
-        <v/>
+        <v>2025:03:04 22:10:05</v>
       </c>
       <c r="E115" t="str">
         <v>1920</v>
       </c>
       <c r="F115" t="str">
-        <v>1440</v>
+        <v>1080</v>
       </c>
       <c r="G115" t="str">
         <v>横</v>
@@ -5562,10 +5599,10 @@
         <v>fellows-jp</v>
       </c>
       <c r="C116" t="str">
-        <v>IMG_2063.jpg</v>
+        <v>IMG_0084.jpg</v>
       </c>
       <c r="D116" t="str">
-        <v>2026:03:23 21:11:31</v>
+        <v/>
       </c>
       <c r="E116" t="str">
         <v>1920</v>
@@ -5579,16 +5616,16 @@
     </row>
     <row r="117">
       <c r="A117">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B117" t="str">
         <v>fellows-jp</v>
       </c>
       <c r="C117" t="str">
-        <v>IMG_2623.jpg</v>
+        <v>IMG_0088.jpg</v>
       </c>
       <c r="D117" t="str">
-        <v/>
+        <v>2025:03:05 10:25:27</v>
       </c>
       <c r="E117" t="str">
         <v>1920</v>
@@ -5608,10 +5645,10 @@
         <v>fellows-jp</v>
       </c>
       <c r="C118" t="str">
-        <v>IMG_9327.jpg</v>
+        <v>IMG_1537.jpg</v>
       </c>
       <c r="D118" t="str">
-        <v>2024:09:20 22:59:00</v>
+        <v/>
       </c>
       <c r="E118" t="str">
         <v>1920</v>
@@ -5631,10 +5668,10 @@
         <v>fellows-jp</v>
       </c>
       <c r="C119" t="str">
-        <v>IMG_9964.jpg</v>
+        <v>IMG_2063.jpg</v>
       </c>
       <c r="D119" t="str">
-        <v/>
+        <v>2026:03:23 21:11:31</v>
       </c>
       <c r="E119" t="str">
         <v>1920</v>
@@ -5648,16 +5685,16 @@
     </row>
     <row r="120">
       <c r="A120">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="B120" t="str">
-        <v>gairai</v>
+        <v>fellows-jp</v>
       </c>
       <c r="C120" t="str">
-        <v>IMG_0403.jpg</v>
+        <v>IMG_2623.jpg</v>
       </c>
       <c r="D120" t="str">
-        <v>2021:03:31 17:46:25</v>
+        <v/>
       </c>
       <c r="E120" t="str">
         <v>1920</v>
@@ -5674,13 +5711,13 @@
         <v/>
       </c>
       <c r="B121" t="str">
-        <v>gairai</v>
+        <v>fellows-jp</v>
       </c>
       <c r="C121" t="str">
-        <v>IMG_0409.jpg</v>
+        <v>IMG_9327.jpg</v>
       </c>
       <c r="D121" t="str">
-        <v>2021:03:31 17:48:51</v>
+        <v>2024:09:20 22:59:00</v>
       </c>
       <c r="E121" t="str">
         <v>1920</v>
@@ -5697,13 +5734,13 @@
         <v/>
       </c>
       <c r="B122" t="str">
-        <v>gairai</v>
+        <v>fellows-jp</v>
       </c>
       <c r="C122" t="str">
-        <v>IMG_0412.jpg</v>
+        <v>IMG_9964.jpg</v>
       </c>
       <c r="D122" t="str">
-        <v>2021:03:31 17:50:42</v>
+        <v/>
       </c>
       <c r="E122" t="str">
         <v>1920</v>
@@ -5716,17 +5753,17 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="str">
-        <v/>
+      <c r="A123">
+        <v>25</v>
       </c>
       <c r="B123" t="str">
         <v>gairai</v>
       </c>
       <c r="C123" t="str">
-        <v>IMG_3062.jpg</v>
+        <v>IMG_0403.jpg</v>
       </c>
       <c r="D123" t="str">
-        <v>2021:03:23 20:20:32</v>
+        <v>2021:03:31 17:46:25</v>
       </c>
       <c r="E123" t="str">
         <v>1920</v>
@@ -5739,17 +5776,17 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124">
-        <v>26</v>
+      <c r="A124" t="str">
+        <v/>
       </c>
       <c r="B124" t="str">
         <v>gairai</v>
       </c>
       <c r="C124" t="str">
-        <v>IMG_3154.jpg</v>
+        <v>IMG_0409.jpg</v>
       </c>
       <c r="D124" t="str">
-        <v>2021:03:31 17:57:42</v>
+        <v>2021:03:31 17:48:51</v>
       </c>
       <c r="E124" t="str">
         <v>1920</v>
@@ -5769,10 +5806,10 @@
         <v>gairai</v>
       </c>
       <c r="C125" t="str">
-        <v>IMG_3156.jpg</v>
+        <v>IMG_0412.jpg</v>
       </c>
       <c r="D125" t="str">
-        <v>2021:03:31 17:52:02</v>
+        <v>2021:03:31 17:50:42</v>
       </c>
       <c r="E125" t="str">
         <v>1920</v>
@@ -5792,10 +5829,10 @@
         <v>gairai</v>
       </c>
       <c r="C126" t="str">
-        <v>IMG_3157.jpg</v>
+        <v>IMG_3062.jpg</v>
       </c>
       <c r="D126" t="str">
-        <v>2021:03:31 17:49:31</v>
+        <v>2021:03:23 20:20:32</v>
       </c>
       <c r="E126" t="str">
         <v>1920</v>
@@ -5808,17 +5845,17 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="str">
-        <v/>
+      <c r="A127">
+        <v>26</v>
       </c>
       <c r="B127" t="str">
         <v>gairai</v>
       </c>
       <c r="C127" t="str">
-        <v>IMG_3245.jpg</v>
+        <v>IMG_3154.jpg</v>
       </c>
       <c r="D127" t="str">
-        <v>2022:08:09 13:16:57</v>
+        <v>2021:03:31 17:57:42</v>
       </c>
       <c r="E127" t="str">
         <v>1920</v>
@@ -5838,33 +5875,33 @@
         <v>gairai</v>
       </c>
       <c r="C128" t="str">
-        <v>IMG_9982.jpg</v>
+        <v>IMG_3156.jpg</v>
       </c>
       <c r="D128" t="str">
-        <v/>
+        <v>2021:03:31 17:52:02</v>
       </c>
       <c r="E128" t="str">
-        <v>1440</v>
+        <v>1920</v>
       </c>
       <c r="F128" t="str">
-        <v>1920</v>
+        <v>1440</v>
       </c>
       <c r="G128" t="str">
-        <v>縦</v>
+        <v>横</v>
       </c>
     </row>
     <row r="129">
-      <c r="A129">
-        <v>55</v>
+      <c r="A129" t="str">
+        <v/>
       </c>
       <c r="B129" t="str">
-        <v>group</v>
+        <v>gairai</v>
       </c>
       <c r="C129" t="str">
-        <v>05755B0B-0A5B-49CD-BF06-8D1AF26BDFCB.jpg</v>
+        <v>IMG_3157.jpg</v>
       </c>
       <c r="D129" t="str">
-        <v/>
+        <v>2021:03:31 17:49:31</v>
       </c>
       <c r="E129" t="str">
         <v>1920</v>
@@ -5881,13 +5918,13 @@
         <v/>
       </c>
       <c r="B130" t="str">
-        <v>group</v>
+        <v>gairai</v>
       </c>
       <c r="C130" t="str">
-        <v>10721352_779584428754417_1561167059_n.jpg</v>
+        <v>IMG_3245.jpg</v>
       </c>
       <c r="D130" t="str">
-        <v/>
+        <v>2022:08:09 13:16:57</v>
       </c>
       <c r="E130" t="str">
         <v>1920</v>
@@ -5904,22 +5941,22 @@
         <v/>
       </c>
       <c r="B131" t="str">
-        <v>group</v>
+        <v>gairai</v>
       </c>
       <c r="C131" t="str">
-        <v>30609613-B7C5-4C4B-A476-FADEEAC831F6.jpg</v>
+        <v>IMG_9982.jpg</v>
       </c>
       <c r="D131" t="str">
         <v/>
       </c>
       <c r="E131" t="str">
-        <v>1920</v>
+        <v>1440</v>
       </c>
       <c r="F131" t="str">
-        <v>1440</v>
+        <v>1920</v>
       </c>
       <c r="G131" t="str">
-        <v>横</v>
+        <v>縦</v>
       </c>
     </row>
     <row r="132">
@@ -5930,7 +5967,7 @@
         <v>group</v>
       </c>
       <c r="C132" t="str">
-        <v>EDE4935B-45DB-4485-ACC1-455FE3959347.jpg</v>
+        <v>05755B0B-0A5B-49CD-BF06-8D1AF26BDFCB.jpg</v>
       </c>
       <c r="D132" t="str">
         <v/>
@@ -5953,10 +5990,10 @@
         <v>group</v>
       </c>
       <c r="C133" t="str">
-        <v>IMG_0066.jpg</v>
+        <v>10721352_779584428754417_1561167059_n.jpg</v>
       </c>
       <c r="D133" t="str">
-        <v>2023:09:20 20:43:40</v>
+        <v/>
       </c>
       <c r="E133" t="str">
         <v>1920</v>
@@ -5976,7 +6013,7 @@
         <v>group</v>
       </c>
       <c r="C134" t="str">
-        <v>IMG_0154.jpg</v>
+        <v>30609613-B7C5-4C4B-A476-FADEEAC831F6.jpg</v>
       </c>
       <c r="D134" t="str">
         <v/>
@@ -5992,17 +6029,17 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="str">
-        <v/>
+      <c r="A135">
+        <v>57</v>
       </c>
       <c r="B135" t="str">
         <v>group</v>
       </c>
       <c r="C135" t="str">
-        <v>IMG_0269.jpg</v>
+        <v>EDE4935B-45DB-4485-ACC1-455FE3959347.jpg</v>
       </c>
       <c r="D135" t="str">
-        <v>2019:03:20 22:28:08</v>
+        <v/>
       </c>
       <c r="E135" t="str">
         <v>1920</v>
@@ -6022,10 +6059,10 @@
         <v>group</v>
       </c>
       <c r="C136" t="str">
-        <v>IMG_0711.jpg</v>
+        <v>IMG_0066.jpg</v>
       </c>
       <c r="D136" t="str">
-        <v>2023:10:11 22:07:03</v>
+        <v>2023:09:20 20:43:40</v>
       </c>
       <c r="E136" t="str">
         <v>1920</v>
@@ -6045,10 +6082,10 @@
         <v>group</v>
       </c>
       <c r="C137" t="str">
-        <v>IMG_1188-SMILE.jpg</v>
+        <v>IMG_0154.jpg</v>
       </c>
       <c r="D137" t="str">
-        <v>2012:12:07 21:23:47</v>
+        <v/>
       </c>
       <c r="E137" t="str">
         <v>1920</v>
@@ -6061,17 +6098,17 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138">
-        <v>58</v>
+      <c r="A138" t="str">
+        <v/>
       </c>
       <c r="B138" t="str">
         <v>group</v>
       </c>
       <c r="C138" t="str">
-        <v>IMG_1252.jpg</v>
+        <v>IMG_0269.jpg</v>
       </c>
       <c r="D138" t="str">
-        <v/>
+        <v>2019:03:20 22:28:08</v>
       </c>
       <c r="E138" t="str">
         <v>1920</v>
@@ -6091,10 +6128,10 @@
         <v>group</v>
       </c>
       <c r="C139" t="str">
-        <v>IMG_1362.jpg</v>
+        <v>IMG_0711.jpg</v>
       </c>
       <c r="D139" t="str">
-        <v>2012:12:28 00:08:10</v>
+        <v>2023:10:11 22:07:03</v>
       </c>
       <c r="E139" t="str">
         <v>1920</v>
@@ -6114,10 +6151,10 @@
         <v>group</v>
       </c>
       <c r="C140" t="str">
-        <v>IMG_1594.jpg</v>
+        <v>IMG_1188-SMILE.jpg</v>
       </c>
       <c r="D140" t="str">
-        <v>2013:02:09 12:26:17</v>
+        <v>2012:12:07 21:23:47</v>
       </c>
       <c r="E140" t="str">
         <v>1920</v>
@@ -6130,14 +6167,14 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="str">
-        <v/>
+      <c r="A141">
+        <v>59</v>
       </c>
       <c r="B141" t="str">
         <v>group</v>
       </c>
       <c r="C141" t="str">
-        <v>IMG_2617.jpg</v>
+        <v>IMG_1252.jpg</v>
       </c>
       <c r="D141" t="str">
         <v/>
@@ -6160,10 +6197,10 @@
         <v>group</v>
       </c>
       <c r="C142" t="str">
-        <v>IMG_2619.jpg</v>
+        <v>IMG_1362.jpg</v>
       </c>
       <c r="D142" t="str">
-        <v/>
+        <v>2012:12:28 00:08:10</v>
       </c>
       <c r="E142" t="str">
         <v>1920</v>
@@ -6183,10 +6220,10 @@
         <v>group</v>
       </c>
       <c r="C143" t="str">
-        <v>IMG_2620.jpg</v>
+        <v>IMG_1594.jpg</v>
       </c>
       <c r="D143" t="str">
-        <v/>
+        <v>2013:02:09 12:26:17</v>
       </c>
       <c r="E143" t="str">
         <v>1920</v>
@@ -6206,7 +6243,7 @@
         <v>group</v>
       </c>
       <c r="C144" t="str">
-        <v>IMG_2626.jpg</v>
+        <v>IMG_2617.jpg</v>
       </c>
       <c r="D144" t="str">
         <v/>
@@ -6215,7 +6252,7 @@
         <v>1920</v>
       </c>
       <c r="F144" t="str">
-        <v>1920</v>
+        <v>1440</v>
       </c>
       <c r="G144" t="str">
         <v>横</v>
@@ -6229,7 +6266,7 @@
         <v>group</v>
       </c>
       <c r="C145" t="str">
-        <v>IMG_2627.jpg</v>
+        <v>IMG_2619.jpg</v>
       </c>
       <c r="D145" t="str">
         <v/>
@@ -6238,7 +6275,7 @@
         <v>1920</v>
       </c>
       <c r="F145" t="str">
-        <v>1347</v>
+        <v>1440</v>
       </c>
       <c r="G145" t="str">
         <v>横</v>
@@ -6252,7 +6289,7 @@
         <v>group</v>
       </c>
       <c r="C146" t="str">
-        <v>IMG_2674.jpg</v>
+        <v>IMG_2620.jpg</v>
       </c>
       <c r="D146" t="str">
         <v/>
@@ -6261,7 +6298,7 @@
         <v>1920</v>
       </c>
       <c r="F146" t="str">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="G146" t="str">
         <v>横</v>
@@ -6275,39 +6312,39 @@
         <v>group</v>
       </c>
       <c r="C147" t="str">
-        <v>IMG_3580.jpg</v>
+        <v>IMG_2626.jpg</v>
       </c>
       <c r="D147" t="str">
-        <v>2019:10:09 08:46:50</v>
+        <v/>
       </c>
       <c r="E147" t="str">
         <v>1920</v>
       </c>
       <c r="F147" t="str">
-        <v>1440</v>
+        <v>1920</v>
       </c>
       <c r="G147" t="str">
         <v>横</v>
       </c>
     </row>
     <row r="148">
-      <c r="A148">
-        <v>59</v>
+      <c r="A148" t="str">
+        <v/>
       </c>
       <c r="B148" t="str">
         <v>group</v>
       </c>
       <c r="C148" t="str">
-        <v>IMG_3668.jpg</v>
+        <v>IMG_2627.jpg</v>
       </c>
       <c r="D148" t="str">
-        <v>2024:09:13 13:17:03</v>
+        <v/>
       </c>
       <c r="E148" t="str">
         <v>1920</v>
       </c>
       <c r="F148" t="str">
-        <v>1440</v>
+        <v>1347</v>
       </c>
       <c r="G148" t="str">
         <v>横</v>
@@ -6321,7 +6358,7 @@
         <v>group</v>
       </c>
       <c r="C149" t="str">
-        <v>IMG_4088.jpg</v>
+        <v>IMG_2674.jpg</v>
       </c>
       <c r="D149" t="str">
         <v/>
@@ -6330,7 +6367,7 @@
         <v>1920</v>
       </c>
       <c r="F149" t="str">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="G149" t="str">
         <v>横</v>
@@ -6344,33 +6381,33 @@
         <v>group</v>
       </c>
       <c r="C150" t="str">
-        <v>IMG_4699-SMILE.jpg</v>
+        <v>IMG_3580.jpg</v>
       </c>
       <c r="D150" t="str">
-        <v/>
+        <v>2019:10:09 08:46:50</v>
       </c>
       <c r="E150" t="str">
         <v>1920</v>
       </c>
       <c r="F150" t="str">
-        <v>1438</v>
+        <v>1440</v>
       </c>
       <c r="G150" t="str">
         <v>横</v>
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="str">
-        <v/>
+      <c r="A151">
+        <v>60</v>
       </c>
       <c r="B151" t="str">
         <v>group</v>
       </c>
       <c r="C151" t="str">
-        <v>IMG_4965.jpg</v>
+        <v>IMG_3668.jpg</v>
       </c>
       <c r="D151" t="str">
-        <v>2020:01:11 18:59:15</v>
+        <v>2024:09:13 13:17:03</v>
       </c>
       <c r="E151" t="str">
         <v>1920</v>
@@ -6383,17 +6420,17 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152">
-        <v>60</v>
+      <c r="A152" t="str">
+        <v/>
       </c>
       <c r="B152" t="str">
         <v>group</v>
       </c>
       <c r="C152" t="str">
-        <v>IMG_5027.jpg</v>
+        <v>IMG_4088.jpg</v>
       </c>
       <c r="D152" t="str">
-        <v>2025:02:18 23:05:06</v>
+        <v/>
       </c>
       <c r="E152" t="str">
         <v>1920</v>
@@ -6413,16 +6450,16 @@
         <v>group</v>
       </c>
       <c r="C153" t="str">
-        <v>IMG_5207-SMILE.jpg</v>
+        <v>IMG_4699-SMILE.jpg</v>
       </c>
       <c r="D153" t="str">
-        <v>2014:06:22 12:30:33</v>
+        <v/>
       </c>
       <c r="E153" t="str">
         <v>1920</v>
       </c>
       <c r="F153" t="str">
-        <v>1440</v>
+        <v>1438</v>
       </c>
       <c r="G153" t="str">
         <v>横</v>
@@ -6436,10 +6473,10 @@
         <v>group</v>
       </c>
       <c r="C154" t="str">
-        <v>IMG_5722.jpg</v>
+        <v>IMG_4965.jpg</v>
       </c>
       <c r="D154" t="str">
-        <v>2014:10:11 21:49:54</v>
+        <v>2020:01:11 18:59:15</v>
       </c>
       <c r="E154" t="str">
         <v>1920</v>
@@ -6452,17 +6489,17 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="str">
-        <v/>
+      <c r="A155">
+        <v>61</v>
       </c>
       <c r="B155" t="str">
         <v>group</v>
       </c>
       <c r="C155" t="str">
-        <v>IMG_6209.jpg</v>
+        <v>IMG_5027.jpg</v>
       </c>
       <c r="D155" t="str">
-        <v>2015:02:07 12:28:19</v>
+        <v>2025:02:18 23:05:06</v>
       </c>
       <c r="E155" t="str">
         <v>1920</v>
@@ -6482,16 +6519,16 @@
         <v>group</v>
       </c>
       <c r="C156" t="str">
-        <v>IMG_6257.jpg</v>
+        <v>IMG_5207-SMILE.jpg</v>
       </c>
       <c r="D156" t="str">
-        <v/>
+        <v>2014:06:22 12:30:33</v>
       </c>
       <c r="E156" t="str">
         <v>1920</v>
       </c>
       <c r="F156" t="str">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="G156" t="str">
         <v>横</v>
@@ -6505,10 +6542,10 @@
         <v>group</v>
       </c>
       <c r="C157" t="str">
-        <v>IMG_9209.jpg</v>
+        <v>IMG_5722.jpg</v>
       </c>
       <c r="D157" t="str">
-        <v>2019:01:11 22:59:53</v>
+        <v>2014:10:11 21:49:54</v>
       </c>
       <c r="E157" t="str">
         <v>1920</v>
@@ -6521,17 +6558,17 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158">
-        <v>61</v>
+      <c r="A158" t="str">
+        <v/>
       </c>
       <c r="B158" t="str">
         <v>group</v>
       </c>
       <c r="C158" t="str">
-        <v>IMG_9912.jpg</v>
+        <v>IMG_6209.jpg</v>
       </c>
       <c r="D158" t="str">
-        <v>2023:06:29 16:33:20</v>
+        <v>2015:02:07 12:28:19</v>
       </c>
       <c r="E158" t="str">
         <v>1920</v>
@@ -6551,16 +6588,16 @@
         <v>group</v>
       </c>
       <c r="C159" t="str">
-        <v>L1030853.jpg</v>
+        <v>IMG_6257.jpg</v>
       </c>
       <c r="D159" t="str">
-        <v>2020:06:10 08:57:07</v>
+        <v/>
       </c>
       <c r="E159" t="str">
         <v>1920</v>
       </c>
       <c r="F159" t="str">
-        <v>1280</v>
+        <v>1439</v>
       </c>
       <c r="G159" t="str">
         <v>横</v>
@@ -6574,10 +6611,10 @@
         <v>group</v>
       </c>
       <c r="C160" t="str">
-        <v>ab327393.jpg</v>
+        <v>IMG_9209.jpg</v>
       </c>
       <c r="D160" t="str">
-        <v/>
+        <v>2019:01:11 22:59:53</v>
       </c>
       <c r="E160" t="str">
         <v>1920</v>
@@ -6590,17 +6627,17 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="str">
-        <v/>
+      <c r="A161">
+        <v>62</v>
       </c>
       <c r="B161" t="str">
         <v>group</v>
       </c>
       <c r="C161" t="str">
-        <v>ed67a970-s.jpg</v>
+        <v>IMG_9912.jpg</v>
       </c>
       <c r="D161" t="str">
-        <v/>
+        <v>2023:06:29 16:33:20</v>
       </c>
       <c r="E161" t="str">
         <v>1920</v>
@@ -6617,19 +6654,19 @@
         <v/>
       </c>
       <c r="B162" t="str">
-        <v>history</v>
+        <v>group</v>
       </c>
       <c r="C162" t="str">
-        <v>19ca888e.jpg</v>
+        <v>L1030853.jpg</v>
       </c>
       <c r="D162" t="str">
-        <v/>
+        <v>2020:06:10 08:57:07</v>
       </c>
       <c r="E162" t="str">
         <v>1920</v>
       </c>
       <c r="F162" t="str">
-        <v>1440</v>
+        <v>1280</v>
       </c>
       <c r="G162" t="str">
         <v>横</v>
@@ -6640,10 +6677,10 @@
         <v/>
       </c>
       <c r="B163" t="str">
-        <v>history</v>
+        <v>group</v>
       </c>
       <c r="C163" t="str">
-        <v>1c7bcbfe.jpg</v>
+        <v>ab327393.jpg</v>
       </c>
       <c r="D163" t="str">
         <v/>
@@ -6663,10 +6700,10 @@
         <v/>
       </c>
       <c r="B164" t="str">
-        <v>history</v>
+        <v>group</v>
       </c>
       <c r="C164" t="str">
-        <v>62a2f21c.jpg</v>
+        <v>ed67a970-s.jpg</v>
       </c>
       <c r="D164" t="str">
         <v/>
@@ -6689,7 +6726,7 @@
         <v>history</v>
       </c>
       <c r="C165" t="str">
-        <v>969940de.jpg</v>
+        <v>19ca888e.jpg</v>
       </c>
       <c r="D165" t="str">
         <v/>
@@ -6705,14 +6742,14 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166">
-        <v>11</v>
+      <c r="A166" t="str">
+        <v/>
       </c>
       <c r="B166" t="str">
         <v>history</v>
       </c>
       <c r="C166" t="str">
-        <v>9be842d9.jpg</v>
+        <v>1c7bcbfe.jpg</v>
       </c>
       <c r="D166" t="str">
         <v/>
@@ -6735,7 +6772,7 @@
         <v>history</v>
       </c>
       <c r="C167" t="str">
-        <v>bcf3dfbd.jpg</v>
+        <v>62a2f21c.jpg</v>
       </c>
       <c r="D167" t="str">
         <v/>
@@ -6758,7 +6795,7 @@
         <v>history</v>
       </c>
       <c r="C168" t="str">
-        <v>f406f954.jpg</v>
+        <v>969940de.jpg</v>
       </c>
       <c r="D168" t="str">
         <v/>
@@ -6775,25 +6812,25 @@
     </row>
     <row r="169">
       <c r="A169">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="B169" t="str">
-        <v>ikyoku</v>
+        <v>history</v>
       </c>
       <c r="C169" t="str">
-        <v>IMG_0108.jpg</v>
+        <v>9be842d9.jpg</v>
       </c>
       <c r="D169" t="str">
         <v/>
       </c>
       <c r="E169" t="str">
-        <v>1440</v>
+        <v>1920</v>
       </c>
       <c r="F169" t="str">
-        <v>1920</v>
+        <v>1440</v>
       </c>
       <c r="G169" t="str">
-        <v>縦</v>
+        <v>横</v>
       </c>
     </row>
     <row r="170">
@@ -6801,13 +6838,13 @@
         <v/>
       </c>
       <c r="B170" t="str">
-        <v>ikyoku</v>
+        <v>history</v>
       </c>
       <c r="C170" t="str">
-        <v>IMG_0906.jpg</v>
+        <v>bcf3dfbd.jpg</v>
       </c>
       <c r="D170" t="str">
-        <v>2021:06:15 20:30:32</v>
+        <v/>
       </c>
       <c r="E170" t="str">
         <v>1920</v>
@@ -6824,45 +6861,45 @@
         <v/>
       </c>
       <c r="B171" t="str">
-        <v>ikyoku</v>
+        <v>history</v>
       </c>
       <c r="C171" t="str">
-        <v>IMG_1053.jpg</v>
+        <v>f406f954.jpg</v>
       </c>
       <c r="D171" t="str">
         <v/>
       </c>
       <c r="E171" t="str">
-        <v>1080</v>
+        <v>1920</v>
       </c>
       <c r="F171" t="str">
-        <v>1920</v>
+        <v>1440</v>
       </c>
       <c r="G171" t="str">
-        <v>縦</v>
+        <v>横</v>
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="str">
-        <v/>
+      <c r="A172">
+        <v>28</v>
       </c>
       <c r="B172" t="str">
         <v>ikyoku</v>
       </c>
       <c r="C172" t="str">
-        <v>IMG_1199.jpg</v>
+        <v>IMG_0108.jpg</v>
       </c>
       <c r="D172" t="str">
-        <v>2025:10:08 17:12:28</v>
+        <v/>
       </c>
       <c r="E172" t="str">
-        <v>1920</v>
+        <v>1440</v>
       </c>
       <c r="F172" t="str">
-        <v>1440</v>
+        <v>1920</v>
       </c>
       <c r="G172" t="str">
-        <v>横</v>
+        <v>縦</v>
       </c>
     </row>
     <row r="173">
@@ -6873,10 +6910,10 @@
         <v>ikyoku</v>
       </c>
       <c r="C173" t="str">
-        <v>IMG_1203.jpg</v>
+        <v>IMG_0906.jpg</v>
       </c>
       <c r="D173" t="str">
-        <v>2025:10:08 17:12:53</v>
+        <v>2021:06:15 20:30:32</v>
       </c>
       <c r="E173" t="str">
         <v>1920</v>
@@ -6896,19 +6933,19 @@
         <v>ikyoku</v>
       </c>
       <c r="C174" t="str">
-        <v>IMG_2247.jpg</v>
+        <v>IMG_1053.jpg</v>
       </c>
       <c r="D174" t="str">
-        <v>2020:10:09 20:12:13</v>
+        <v/>
       </c>
       <c r="E174" t="str">
-        <v>1920</v>
+        <v>1080</v>
       </c>
       <c r="F174" t="str">
-        <v>1440</v>
+        <v>1920</v>
       </c>
       <c r="G174" t="str">
-        <v>横</v>
+        <v>縦</v>
       </c>
     </row>
     <row r="175">
@@ -6919,10 +6956,10 @@
         <v>ikyoku</v>
       </c>
       <c r="C175" t="str">
-        <v>IMG_3586.jpg</v>
+        <v>IMG_1199.jpg</v>
       </c>
       <c r="D175" t="str">
-        <v>2019:10:09 19:56:18</v>
+        <v>2025:10:08 17:12:28</v>
       </c>
       <c r="E175" t="str">
         <v>1920</v>
@@ -6942,10 +6979,10 @@
         <v>ikyoku</v>
       </c>
       <c r="C176" t="str">
-        <v>IMG_8595.jpg</v>
+        <v>IMG_1203.jpg</v>
       </c>
       <c r="D176" t="str">
-        <v/>
+        <v>2025:10:08 17:12:53</v>
       </c>
       <c r="E176" t="str">
         <v>1920</v>
@@ -6965,10 +7002,10 @@
         <v>ikyoku</v>
       </c>
       <c r="C177" t="str">
-        <v>IMG_8735.jpg</v>
+        <v>IMG_2247.jpg</v>
       </c>
       <c r="D177" t="str">
-        <v>2024:06:07 10:50:01</v>
+        <v>2020:10:09 20:12:13</v>
       </c>
       <c r="E177" t="str">
         <v>1920</v>
@@ -6988,10 +7025,10 @@
         <v>ikyoku</v>
       </c>
       <c r="C178" t="str">
-        <v>IMG_8736.jpg</v>
+        <v>IMG_3586.jpg</v>
       </c>
       <c r="D178" t="str">
-        <v>2024:06:07 10:50:42</v>
+        <v>2019:10:09 19:56:18</v>
       </c>
       <c r="E178" t="str">
         <v>1920</v>
@@ -7011,10 +7048,10 @@
         <v>ikyoku</v>
       </c>
       <c r="C179" t="str">
-        <v>IMG_9973.jpg</v>
+        <v>IMG_8595.jpg</v>
       </c>
       <c r="D179" t="str">
-        <v>2021:10:08 21:02:46</v>
+        <v/>
       </c>
       <c r="E179" t="str">
         <v>1920</v>
@@ -7031,19 +7068,19 @@
         <v/>
       </c>
       <c r="B180" t="str">
-        <v>misc</v>
+        <v>ikyoku</v>
       </c>
       <c r="C180" t="str">
-        <v>IMG_0781.jpg</v>
+        <v>IMG_8735.jpg</v>
       </c>
       <c r="D180" t="str">
-        <v>2014:10:11 02:42:41</v>
+        <v>2024:06:07 10:50:01</v>
       </c>
       <c r="E180" t="str">
         <v>1920</v>
       </c>
       <c r="F180" t="str">
-        <v>1434</v>
+        <v>1440</v>
       </c>
       <c r="G180" t="str">
         <v>横</v>
@@ -7054,13 +7091,13 @@
         <v/>
       </c>
       <c r="B181" t="str">
-        <v>misc</v>
+        <v>ikyoku</v>
       </c>
       <c r="C181" t="str">
-        <v>IMG_1339.jpg</v>
+        <v>IMG_8736.jpg</v>
       </c>
       <c r="D181" t="str">
-        <v>2012:12:23 17:20:28</v>
+        <v>2024:06:07 10:50:42</v>
       </c>
       <c r="E181" t="str">
         <v>1920</v>
@@ -7077,13 +7114,13 @@
         <v/>
       </c>
       <c r="B182" t="str">
-        <v>misc</v>
+        <v>ikyoku</v>
       </c>
       <c r="C182" t="str">
-        <v>IMG_1474.jpg</v>
+        <v>IMG_9973.jpg</v>
       </c>
       <c r="D182" t="str">
-        <v/>
+        <v>2021:10:08 21:02:46</v>
       </c>
       <c r="E182" t="str">
         <v>1920</v>
@@ -7103,16 +7140,16 @@
         <v>misc</v>
       </c>
       <c r="C183" t="str">
-        <v>IMG_2468.jpg</v>
+        <v>IMG_0781.jpg</v>
       </c>
       <c r="D183" t="str">
-        <v>2020:02:09 10:32:30</v>
+        <v>2014:10:11 02:42:41</v>
       </c>
       <c r="E183" t="str">
         <v>1920</v>
       </c>
       <c r="F183" t="str">
-        <v>1440</v>
+        <v>1434</v>
       </c>
       <c r="G183" t="str">
         <v>横</v>
@@ -7126,10 +7163,10 @@
         <v>misc</v>
       </c>
       <c r="C184" t="str">
-        <v>IMG_2605.jpg</v>
+        <v>IMG_1339.jpg</v>
       </c>
       <c r="D184" t="str">
-        <v/>
+        <v>2012:12:23 17:20:28</v>
       </c>
       <c r="E184" t="str">
         <v>1920</v>
@@ -7149,10 +7186,10 @@
         <v>misc</v>
       </c>
       <c r="C185" t="str">
-        <v>IMG_2678.jpg</v>
+        <v>IMG_1474.jpg</v>
       </c>
       <c r="D185" t="str">
-        <v>2026:07:24 06:50:15</v>
+        <v/>
       </c>
       <c r="E185" t="str">
         <v>1920</v>
@@ -7172,10 +7209,10 @@
         <v>misc</v>
       </c>
       <c r="C186" t="str">
-        <v>IMG_3454.jpg</v>
+        <v>IMG_2468.jpg</v>
       </c>
       <c r="D186" t="str">
-        <v>2013:11:05 13:45:36</v>
+        <v>2020:02:09 10:32:30</v>
       </c>
       <c r="E186" t="str">
         <v>1920</v>
@@ -7195,10 +7232,10 @@
         <v>misc</v>
       </c>
       <c r="C187" t="str">
-        <v>IMG_3493.jpg</v>
+        <v>IMG_2605.jpg</v>
       </c>
       <c r="D187" t="str">
-        <v>2013:11:08 15:59:07</v>
+        <v/>
       </c>
       <c r="E187" t="str">
         <v>1920</v>
@@ -7218,10 +7255,10 @@
         <v>misc</v>
       </c>
       <c r="C188" t="str">
-        <v>IMG_3654.jpg</v>
+        <v>IMG_2678.jpg</v>
       </c>
       <c r="D188" t="str">
-        <v>2013:11:22 20:58:33</v>
+        <v>2026:07:24 06:50:15</v>
       </c>
       <c r="E188" t="str">
         <v>1920</v>
@@ -7241,10 +7278,10 @@
         <v>misc</v>
       </c>
       <c r="C189" t="str">
-        <v>IMG_3754.jpg</v>
+        <v>IMG_3454.jpg</v>
       </c>
       <c r="D189" t="str">
-        <v>2013:11:29 19:23:09</v>
+        <v>2013:11:05 13:45:36</v>
       </c>
       <c r="E189" t="str">
         <v>1920</v>
@@ -7264,10 +7301,10 @@
         <v>misc</v>
       </c>
       <c r="C190" t="str">
-        <v>IMG_4039.jpg</v>
+        <v>IMG_3493.jpg</v>
       </c>
       <c r="D190" t="str">
-        <v>2014:01:11 14:44:46</v>
+        <v>2013:11:08 15:59:07</v>
       </c>
       <c r="E190" t="str">
         <v>1920</v>
@@ -7287,10 +7324,10 @@
         <v>misc</v>
       </c>
       <c r="C191" t="str">
-        <v>IMG_4073.jpg</v>
+        <v>IMG_3654.jpg</v>
       </c>
       <c r="D191" t="str">
-        <v>2014:01:11 23:59:30</v>
+        <v>2013:11:22 20:58:33</v>
       </c>
       <c r="E191" t="str">
         <v>1920</v>
@@ -7310,10 +7347,10 @@
         <v>misc</v>
       </c>
       <c r="C192" t="str">
-        <v>IMG_4075.jpg</v>
+        <v>IMG_3754.jpg</v>
       </c>
       <c r="D192" t="str">
-        <v>2014:01:11 18:02:26</v>
+        <v>2013:11:29 19:23:09</v>
       </c>
       <c r="E192" t="str">
         <v>1920</v>
@@ -7333,10 +7370,10 @@
         <v>misc</v>
       </c>
       <c r="C193" t="str">
-        <v>IMG_4483.jpg</v>
+        <v>IMG_4039.jpg</v>
       </c>
       <c r="D193" t="str">
-        <v>2014:03:28 15:58:27</v>
+        <v>2014:01:11 14:44:46</v>
       </c>
       <c r="E193" t="str">
         <v>1920</v>
@@ -7356,10 +7393,10 @@
         <v>misc</v>
       </c>
       <c r="C194" t="str">
-        <v>IMG_4556.jpg</v>
+        <v>IMG_4073.jpg</v>
       </c>
       <c r="D194" t="str">
-        <v>2009:04:05 22:47:02</v>
+        <v>2014:01:11 23:59:30</v>
       </c>
       <c r="E194" t="str">
         <v>1920</v>
@@ -7379,10 +7416,10 @@
         <v>misc</v>
       </c>
       <c r="C195" t="str">
-        <v>IMG_4795.jpg</v>
+        <v>IMG_4075.jpg</v>
       </c>
       <c r="D195" t="str">
-        <v>2022:10:29 07:35:55</v>
+        <v>2014:01:11 18:02:26</v>
       </c>
       <c r="E195" t="str">
         <v>1920</v>
@@ -7402,10 +7439,10 @@
         <v>misc</v>
       </c>
       <c r="C196" t="str">
-        <v>IMG_4815.jpg</v>
+        <v>IMG_4483.jpg</v>
       </c>
       <c r="D196" t="str">
-        <v>2022:10:29 08:15:01</v>
+        <v>2014:03:28 15:58:27</v>
       </c>
       <c r="E196" t="str">
         <v>1920</v>
@@ -7425,10 +7462,10 @@
         <v>misc</v>
       </c>
       <c r="C197" t="str">
-        <v>IMG_4862.jpg</v>
+        <v>IMG_4556.jpg</v>
       </c>
       <c r="D197" t="str">
-        <v>2014:05:08 06:19:05</v>
+        <v>2009:04:05 22:47:02</v>
       </c>
       <c r="E197" t="str">
         <v>1920</v>
@@ -7448,10 +7485,10 @@
         <v>misc</v>
       </c>
       <c r="C198" t="str">
-        <v>IMG_4869.jpg</v>
+        <v>IMG_4795.jpg</v>
       </c>
       <c r="D198" t="str">
-        <v>2014:05:09 08:22:13</v>
+        <v>2022:10:29 07:35:55</v>
       </c>
       <c r="E198" t="str">
         <v>1920</v>
@@ -7471,10 +7508,10 @@
         <v>misc</v>
       </c>
       <c r="C199" t="str">
-        <v>IMG_4926.jpg</v>
+        <v>IMG_4815.jpg</v>
       </c>
       <c r="D199" t="str">
-        <v>2020:01:10 12:10:43</v>
+        <v>2022:10:29 08:15:01</v>
       </c>
       <c r="E199" t="str">
         <v>1920</v>
@@ -7494,10 +7531,10 @@
         <v>misc</v>
       </c>
       <c r="C200" t="str">
-        <v>IMG_5203.jpg</v>
+        <v>IMG_4862.jpg</v>
       </c>
       <c r="D200" t="str">
-        <v>2014:06:22 07:18:21</v>
+        <v>2014:05:08 06:19:05</v>
       </c>
       <c r="E200" t="str">
         <v>1920</v>
@@ -7517,10 +7554,10 @@
         <v>misc</v>
       </c>
       <c r="C201" t="str">
-        <v>IMG_5289.jpg</v>
+        <v>IMG_4869.jpg</v>
       </c>
       <c r="D201" t="str">
-        <v>2014:07:12 20:42:11</v>
+        <v>2014:05:09 08:22:13</v>
       </c>
       <c r="E201" t="str">
         <v>1920</v>
@@ -7540,10 +7577,10 @@
         <v>misc</v>
       </c>
       <c r="C202" t="str">
-        <v>IMG_5404.jpg</v>
+        <v>IMG_4926.jpg</v>
       </c>
       <c r="D202" t="str">
-        <v>2014:08:07 08:16:01</v>
+        <v>2020:01:10 12:10:43</v>
       </c>
       <c r="E202" t="str">
         <v>1920</v>
@@ -7563,10 +7600,10 @@
         <v>misc</v>
       </c>
       <c r="C203" t="str">
-        <v>IMG_5692.jpg</v>
+        <v>IMG_5203.jpg</v>
       </c>
       <c r="D203" t="str">
-        <v>2014:10:09 18:55:52</v>
+        <v>2014:06:22 07:18:21</v>
       </c>
       <c r="E203" t="str">
         <v>1920</v>
@@ -7586,16 +7623,16 @@
         <v>misc</v>
       </c>
       <c r="C204" t="str">
-        <v>IMG_5833.jpg</v>
+        <v>IMG_5289.jpg</v>
       </c>
       <c r="D204" t="str">
-        <v/>
+        <v>2014:07:12 20:42:11</v>
       </c>
       <c r="E204" t="str">
         <v>1920</v>
       </c>
       <c r="F204" t="str">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="G204" t="str">
         <v>横</v>
@@ -7609,10 +7646,10 @@
         <v>misc</v>
       </c>
       <c r="C205" t="str">
-        <v>IMG_6094.jpg</v>
+        <v>IMG_5404.jpg</v>
       </c>
       <c r="D205" t="str">
-        <v/>
+        <v>2014:08:07 08:16:01</v>
       </c>
       <c r="E205" t="str">
         <v>1920</v>
@@ -7632,10 +7669,10 @@
         <v>misc</v>
       </c>
       <c r="C206" t="str">
-        <v>P8070283.jpg</v>
+        <v>IMG_5692.jpg</v>
       </c>
       <c r="D206" t="str">
-        <v>2014:08:07 22:19:06</v>
+        <v>2014:10:09 18:55:52</v>
       </c>
       <c r="E206" t="str">
         <v>1920</v>
@@ -7655,16 +7692,16 @@
         <v>misc</v>
       </c>
       <c r="C207" t="str">
-        <v>P8070294.jpg</v>
+        <v>IMG_5833.jpg</v>
       </c>
       <c r="D207" t="str">
-        <v>2014:08:07 23:28:46</v>
+        <v/>
       </c>
       <c r="E207" t="str">
         <v>1920</v>
       </c>
       <c r="F207" t="str">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="G207" t="str">
         <v>横</v>
@@ -7678,10 +7715,10 @@
         <v>misc</v>
       </c>
       <c r="C208" t="str">
-        <v>写真-5-ACTION.jpg</v>
+        <v>IMG_6094.jpg</v>
       </c>
       <c r="D208" t="str">
-        <v>2014:01:11 20:37:34</v>
+        <v/>
       </c>
       <c r="E208" t="str">
         <v>1920</v>
@@ -7701,10 +7738,10 @@
         <v>misc</v>
       </c>
       <c r="C209" t="str">
-        <v>写真-9.jpg</v>
+        <v>P8070283.jpg</v>
       </c>
       <c r="D209" t="str">
-        <v>2014:01:11 20:25:03</v>
+        <v>2014:08:07 22:19:06</v>
       </c>
       <c r="E209" t="str">
         <v>1920</v>
@@ -7721,13 +7758,13 @@
         <v/>
       </c>
       <c r="B210" t="str">
-        <v>misc6</v>
+        <v>misc</v>
       </c>
       <c r="C210" t="str">
-        <v>11C3740C-0171-4ED7-9FE7-9540EAC991CE.jpg</v>
+        <v>P8070294.jpg</v>
       </c>
       <c r="D210" t="str">
-        <v/>
+        <v>2014:08:07 23:28:46</v>
       </c>
       <c r="E210" t="str">
         <v>1920</v>
@@ -7744,13 +7781,13 @@
         <v/>
       </c>
       <c r="B211" t="str">
-        <v>misc6</v>
+        <v>misc</v>
       </c>
       <c r="C211" t="str">
-        <v>IMG_0231.jpg</v>
+        <v>写真-5-ACTION.jpg</v>
       </c>
       <c r="D211" t="str">
-        <v>2019:03:20 21:16:05</v>
+        <v>2014:01:11 20:37:34</v>
       </c>
       <c r="E211" t="str">
         <v>1920</v>
@@ -7767,13 +7804,13 @@
         <v/>
       </c>
       <c r="B212" t="str">
-        <v>misc6</v>
+        <v>misc</v>
       </c>
       <c r="C212" t="str">
-        <v>IMG_0236.jpg</v>
+        <v>写真-9.jpg</v>
       </c>
       <c r="D212" t="str">
-        <v>2019:03:20 21:20:23</v>
+        <v>2014:01:11 20:25:03</v>
       </c>
       <c r="E212" t="str">
         <v>1920</v>
@@ -7793,16 +7830,16 @@
         <v>misc6</v>
       </c>
       <c r="C213" t="str">
-        <v>IMG_0237.jpg</v>
+        <v>11C3740C-0171-4ED7-9FE7-9540EAC991CE.jpg</v>
       </c>
       <c r="D213" t="str">
-        <v>2019:09:25 22:53:40</v>
+        <v/>
       </c>
       <c r="E213" t="str">
         <v>1920</v>
       </c>
       <c r="F213" t="str">
-        <v>1080</v>
+        <v>1440</v>
       </c>
       <c r="G213" t="str">
         <v>横</v>
@@ -7816,16 +7853,16 @@
         <v>misc6</v>
       </c>
       <c r="C214" t="str">
-        <v>IMG_0241.jpg</v>
+        <v>IMG_0231.jpg</v>
       </c>
       <c r="D214" t="str">
-        <v>2019:09:25 22:59:21</v>
+        <v>2019:03:20 21:16:05</v>
       </c>
       <c r="E214" t="str">
         <v>1920</v>
       </c>
       <c r="F214" t="str">
-        <v>1080</v>
+        <v>1440</v>
       </c>
       <c r="G214" t="str">
         <v>横</v>
@@ -7839,10 +7876,10 @@
         <v>misc6</v>
       </c>
       <c r="C215" t="str">
-        <v>IMG_0245.jpg</v>
+        <v>IMG_0236.jpg</v>
       </c>
       <c r="D215" t="str">
-        <v>2019:03:20 21:31:54</v>
+        <v>2019:03:20 21:20:23</v>
       </c>
       <c r="E215" t="str">
         <v>1920</v>
@@ -7862,16 +7899,16 @@
         <v>misc6</v>
       </c>
       <c r="C216" t="str">
-        <v>IMG_0248.jpg</v>
+        <v>IMG_0237.jpg</v>
       </c>
       <c r="D216" t="str">
-        <v>2019:03:20 21:47:26</v>
+        <v>2019:09:25 22:53:40</v>
       </c>
       <c r="E216" t="str">
         <v>1920</v>
       </c>
       <c r="F216" t="str">
-        <v>1440</v>
+        <v>1080</v>
       </c>
       <c r="G216" t="str">
         <v>横</v>
@@ -7885,16 +7922,16 @@
         <v>misc6</v>
       </c>
       <c r="C217" t="str">
-        <v>IMG_0262.jpg</v>
+        <v>IMG_0241.jpg</v>
       </c>
       <c r="D217" t="str">
-        <v>2019:03:20 21:53:43</v>
+        <v>2019:09:25 22:59:21</v>
       </c>
       <c r="E217" t="str">
         <v>1920</v>
       </c>
       <c r="F217" t="str">
-        <v>1440</v>
+        <v>1080</v>
       </c>
       <c r="G217" t="str">
         <v>横</v>
@@ -7908,10 +7945,10 @@
         <v>misc6</v>
       </c>
       <c r="C218" t="str">
-        <v>IMG_0396.jpg</v>
+        <v>IMG_0245.jpg</v>
       </c>
       <c r="D218" t="str">
-        <v>2019:03:29 19:59:44</v>
+        <v>2019:03:20 21:31:54</v>
       </c>
       <c r="E218" t="str">
         <v>1920</v>
@@ -7931,10 +7968,10 @@
         <v>misc6</v>
       </c>
       <c r="C219" t="str">
-        <v>IMG_0686.jpg</v>
+        <v>IMG_0248.jpg</v>
       </c>
       <c r="D219" t="str">
-        <v/>
+        <v>2019:03:20 21:47:26</v>
       </c>
       <c r="E219" t="str">
         <v>1920</v>
@@ -7954,10 +7991,10 @@
         <v>misc6</v>
       </c>
       <c r="C220" t="str">
-        <v>IMG_0710.jpg</v>
+        <v>IMG_0262.jpg</v>
       </c>
       <c r="D220" t="str">
-        <v>2020:02:11 00:03:11</v>
+        <v>2019:03:20 21:53:43</v>
       </c>
       <c r="E220" t="str">
         <v>1920</v>
@@ -7977,10 +8014,10 @@
         <v>misc6</v>
       </c>
       <c r="C221" t="str">
-        <v>IMG_0776.jpg</v>
+        <v>IMG_0396.jpg</v>
       </c>
       <c r="D221" t="str">
-        <v>2019:04:14 20:50:09</v>
+        <v>2019:03:29 19:59:44</v>
       </c>
       <c r="E221" t="str">
         <v>1920</v>
@@ -8000,10 +8037,10 @@
         <v>misc6</v>
       </c>
       <c r="C222" t="str">
-        <v>IMG_0791.jpg</v>
+        <v>IMG_0686.jpg</v>
       </c>
       <c r="D222" t="str">
-        <v>2023:10:11 21:51:35</v>
+        <v/>
       </c>
       <c r="E222" t="str">
         <v>1920</v>
@@ -8023,10 +8060,10 @@
         <v>misc6</v>
       </c>
       <c r="C223" t="str">
-        <v>IMG_0862.jpg</v>
+        <v>IMG_0710.jpg</v>
       </c>
       <c r="D223" t="str">
-        <v/>
+        <v>2020:02:11 00:03:11</v>
       </c>
       <c r="E223" t="str">
         <v>1920</v>
@@ -8046,10 +8083,10 @@
         <v>misc6</v>
       </c>
       <c r="C224" t="str">
-        <v>IMG_0930.jpg</v>
+        <v>IMG_0776.jpg</v>
       </c>
       <c r="D224" t="str">
-        <v>2020:03:17 22:02:24</v>
+        <v>2019:04:14 20:50:09</v>
       </c>
       <c r="E224" t="str">
         <v>1920</v>
@@ -8069,10 +8106,10 @@
         <v>misc6</v>
       </c>
       <c r="C225" t="str">
-        <v>IMG_0998.jpg</v>
+        <v>IMG_0791.jpg</v>
       </c>
       <c r="D225" t="str">
-        <v>2018:08:24 23:26:01</v>
+        <v>2023:10:11 21:51:35</v>
       </c>
       <c r="E225" t="str">
         <v>1920</v>
@@ -8092,10 +8129,10 @@
         <v>misc6</v>
       </c>
       <c r="C226" t="str">
-        <v>IMG_1148.jpg</v>
+        <v>IMG_0862.jpg</v>
       </c>
       <c r="D226" t="str">
-        <v>2018:09:01 17:41:33</v>
+        <v/>
       </c>
       <c r="E226" t="str">
         <v>1920</v>
@@ -8115,10 +8152,10 @@
         <v>misc6</v>
       </c>
       <c r="C227" t="str">
-        <v>IMG_1200.jpg</v>
+        <v>IMG_0930.jpg</v>
       </c>
       <c r="D227" t="str">
-        <v>2025:10:08 17:12:29</v>
+        <v>2020:03:17 22:02:24</v>
       </c>
       <c r="E227" t="str">
         <v>1920</v>
@@ -8138,10 +8175,10 @@
         <v>misc6</v>
       </c>
       <c r="C228" t="str">
-        <v>IMG_1267.jpg</v>
+        <v>IMG_0998.jpg</v>
       </c>
       <c r="D228" t="str">
-        <v>2019:05:11 16:41:27</v>
+        <v>2018:08:24 23:26:01</v>
       </c>
       <c r="E228" t="str">
         <v>1920</v>
@@ -8161,10 +8198,10 @@
         <v>misc6</v>
       </c>
       <c r="C229" t="str">
-        <v>IMG_1269.jpg</v>
+        <v>IMG_1148.jpg</v>
       </c>
       <c r="D229" t="str">
-        <v>2019:05:11 16:41:47</v>
+        <v>2018:09:01 17:41:33</v>
       </c>
       <c r="E229" t="str">
         <v>1920</v>
@@ -8184,10 +8221,10 @@
         <v>misc6</v>
       </c>
       <c r="C230" t="str">
-        <v>IMG_1272.jpg</v>
+        <v>IMG_1200.jpg</v>
       </c>
       <c r="D230" t="str">
-        <v>2023:12:22 23:02:30</v>
+        <v>2025:10:08 17:12:29</v>
       </c>
       <c r="E230" t="str">
         <v>1920</v>
@@ -8207,16 +8244,16 @@
         <v>misc6</v>
       </c>
       <c r="C231" t="str">
-        <v>IMG_1277.jpg</v>
+        <v>IMG_1267.jpg</v>
       </c>
       <c r="D231" t="str">
-        <v/>
+        <v>2019:05:11 16:41:27</v>
       </c>
       <c r="E231" t="str">
         <v>1920</v>
       </c>
       <c r="F231" t="str">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="G231" t="str">
         <v>横</v>
@@ -8230,10 +8267,10 @@
         <v>misc6</v>
       </c>
       <c r="C232" t="str">
-        <v>IMG_1280.jpg</v>
+        <v>IMG_1269.jpg</v>
       </c>
       <c r="D232" t="str">
-        <v>2023:12:22 23:11:19</v>
+        <v>2019:05:11 16:41:47</v>
       </c>
       <c r="E232" t="str">
         <v>1920</v>
@@ -8253,10 +8290,10 @@
         <v>misc6</v>
       </c>
       <c r="C233" t="str">
-        <v>IMG_1366.jpg</v>
+        <v>IMG_1272.jpg</v>
       </c>
       <c r="D233" t="str">
-        <v>2019:05:12 14:03:30</v>
+        <v>2023:12:22 23:02:30</v>
       </c>
       <c r="E233" t="str">
         <v>1920</v>
@@ -8276,16 +8313,16 @@
         <v>misc6</v>
       </c>
       <c r="C234" t="str">
-        <v>IMG_1375.jpg</v>
+        <v>IMG_1277.jpg</v>
       </c>
       <c r="D234" t="str">
-        <v>2019:05:12 14:09:34</v>
+        <v/>
       </c>
       <c r="E234" t="str">
         <v>1920</v>
       </c>
       <c r="F234" t="str">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="G234" t="str">
         <v>横</v>
@@ -8299,19 +8336,19 @@
         <v>misc6</v>
       </c>
       <c r="C235" t="str">
-        <v>IMG_1391.jpg</v>
+        <v>IMG_1280.jpg</v>
       </c>
       <c r="D235" t="str">
-        <v>2019:05:12 14:11:12</v>
+        <v>2023:12:22 23:11:19</v>
       </c>
       <c r="E235" t="str">
-        <v>1440</v>
+        <v>1920</v>
       </c>
       <c r="F235" t="str">
-        <v>1920</v>
+        <v>1440</v>
       </c>
       <c r="G235" t="str">
-        <v>縦</v>
+        <v>横</v>
       </c>
     </row>
     <row r="236">
@@ -8322,19 +8359,19 @@
         <v>misc6</v>
       </c>
       <c r="C236" t="str">
-        <v>IMG_1393.jpg</v>
+        <v>IMG_1366.jpg</v>
       </c>
       <c r="D236" t="str">
-        <v>2019:05:12 14:11:56</v>
+        <v>2019:05:12 14:03:30</v>
       </c>
       <c r="E236" t="str">
-        <v>1440</v>
+        <v>1920</v>
       </c>
       <c r="F236" t="str">
-        <v>1920</v>
+        <v>1440</v>
       </c>
       <c r="G236" t="str">
-        <v>縦</v>
+        <v>横</v>
       </c>
     </row>
     <row r="237">
@@ -8345,16 +8382,16 @@
         <v>misc6</v>
       </c>
       <c r="C237" t="str">
-        <v>IMG_1403.jpg</v>
+        <v>IMG_1375.jpg</v>
       </c>
       <c r="D237" t="str">
-        <v>2019:05:12 14:12:46</v>
+        <v>2019:05:12 14:09:34</v>
       </c>
       <c r="E237" t="str">
         <v>1920</v>
       </c>
       <c r="F237" t="str">
-        <v>1083</v>
+        <v>1440</v>
       </c>
       <c r="G237" t="str">
         <v>横</v>
@@ -8368,19 +8405,19 @@
         <v>misc6</v>
       </c>
       <c r="C238" t="str">
-        <v>IMG_1438.jpg</v>
+        <v>IMG_1391.jpg</v>
       </c>
       <c r="D238" t="str">
-        <v>2019:05:12 15:15:55</v>
+        <v>2019:05:12 14:11:12</v>
       </c>
       <c r="E238" t="str">
-        <v>1920</v>
+        <v>1440</v>
       </c>
       <c r="F238" t="str">
-        <v>1440</v>
+        <v>1920</v>
       </c>
       <c r="G238" t="str">
-        <v>横</v>
+        <v>縦</v>
       </c>
     </row>
     <row r="239">
@@ -8391,19 +8428,19 @@
         <v>misc6</v>
       </c>
       <c r="C239" t="str">
-        <v>IMG_1449.jpg</v>
+        <v>IMG_1393.jpg</v>
       </c>
       <c r="D239" t="str">
-        <v>2019:05:12 15:27:58</v>
+        <v>2019:05:12 14:11:56</v>
       </c>
       <c r="E239" t="str">
-        <v>1920</v>
+        <v>1440</v>
       </c>
       <c r="F239" t="str">
-        <v>1440</v>
+        <v>1920</v>
       </c>
       <c r="G239" t="str">
-        <v>横</v>
+        <v>縦</v>
       </c>
     </row>
     <row r="240">
@@ -8414,16 +8451,16 @@
         <v>misc6</v>
       </c>
       <c r="C240" t="str">
-        <v>IMG_1490.jpg</v>
+        <v>IMG_1403.jpg</v>
       </c>
       <c r="D240" t="str">
-        <v/>
+        <v>2019:05:12 14:12:46</v>
       </c>
       <c r="E240" t="str">
         <v>1920</v>
       </c>
       <c r="F240" t="str">
-        <v>1440</v>
+        <v>1083</v>
       </c>
       <c r="G240" t="str">
         <v>横</v>
@@ -8437,10 +8474,10 @@
         <v>misc6</v>
       </c>
       <c r="C241" t="str">
-        <v>IMG_1494.jpg</v>
+        <v>IMG_1438.jpg</v>
       </c>
       <c r="D241" t="str">
-        <v/>
+        <v>2019:05:12 15:15:55</v>
       </c>
       <c r="E241" t="str">
         <v>1920</v>
@@ -8460,10 +8497,10 @@
         <v>misc6</v>
       </c>
       <c r="C242" t="str">
-        <v>IMG_1496.jpg</v>
+        <v>IMG_1449.jpg</v>
       </c>
       <c r="D242" t="str">
-        <v>2018:09:28 22:21:16</v>
+        <v>2019:05:12 15:27:58</v>
       </c>
       <c r="E242" t="str">
         <v>1920</v>
@@ -8483,10 +8520,10 @@
         <v>misc6</v>
       </c>
       <c r="C243" t="str">
-        <v>IMG_1539.jpg</v>
+        <v>IMG_1490.jpg</v>
       </c>
       <c r="D243" t="str">
-        <v>2019:05:14 22:24:42</v>
+        <v/>
       </c>
       <c r="E243" t="str">
         <v>1920</v>
@@ -8506,10 +8543,10 @@
         <v>misc6</v>
       </c>
       <c r="C244" t="str">
-        <v>IMG_1585.jpg</v>
+        <v>IMG_1494.jpg</v>
       </c>
       <c r="D244" t="str">
-        <v>2020:06:19 17:53:10</v>
+        <v/>
       </c>
       <c r="E244" t="str">
         <v>1920</v>
@@ -8529,10 +8566,10 @@
         <v>misc6</v>
       </c>
       <c r="C245" t="str">
-        <v>IMG_1623.jpg</v>
+        <v>IMG_1496.jpg</v>
       </c>
       <c r="D245" t="str">
-        <v>2024:02:03 21:25:46</v>
+        <v>2018:09:28 22:21:16</v>
       </c>
       <c r="E245" t="str">
         <v>1920</v>
@@ -8552,10 +8589,10 @@
         <v>misc6</v>
       </c>
       <c r="C246" t="str">
-        <v>IMG_1868.jpg</v>
+        <v>IMG_1539.jpg</v>
       </c>
       <c r="D246" t="str">
-        <v>2018:12:26 23:09:35</v>
+        <v>2019:05:14 22:24:42</v>
       </c>
       <c r="E246" t="str">
         <v>1920</v>
@@ -8575,10 +8612,10 @@
         <v>misc6</v>
       </c>
       <c r="C247" t="str">
-        <v>IMG_1992.jpg</v>
+        <v>IMG_1585.jpg</v>
       </c>
       <c r="D247" t="str">
-        <v>2022:03:29 19:46:36</v>
+        <v>2020:06:19 17:53:10</v>
       </c>
       <c r="E247" t="str">
         <v>1920</v>
@@ -8598,10 +8635,10 @@
         <v>misc6</v>
       </c>
       <c r="C248" t="str">
-        <v>IMG_1994.jpg</v>
+        <v>IMG_1623.jpg</v>
       </c>
       <c r="D248" t="str">
-        <v>2022:03:29 19:46:57</v>
+        <v>2024:02:03 21:25:46</v>
       </c>
       <c r="E248" t="str">
         <v>1920</v>
@@ -8621,10 +8658,10 @@
         <v>misc6</v>
       </c>
       <c r="C249" t="str">
-        <v>IMG_2011.jpg</v>
+        <v>IMG_1868.jpg</v>
       </c>
       <c r="D249" t="str">
-        <v>2022:03:29 22:18:21</v>
+        <v>2018:12:26 23:09:35</v>
       </c>
       <c r="E249" t="str">
         <v>1920</v>
@@ -8644,10 +8681,10 @@
         <v>misc6</v>
       </c>
       <c r="C250" t="str">
-        <v>IMG_2077.jpg</v>
+        <v>IMG_1992.jpg</v>
       </c>
       <c r="D250" t="str">
-        <v>2019:06:14 21:08:12</v>
+        <v>2022:03:29 19:46:36</v>
       </c>
       <c r="E250" t="str">
         <v>1920</v>
@@ -8667,10 +8704,10 @@
         <v>misc6</v>
       </c>
       <c r="C251" t="str">
-        <v>IMG_2083.jpg</v>
+        <v>IMG_1994.jpg</v>
       </c>
       <c r="D251" t="str">
-        <v>2019:06:15 12:12:43</v>
+        <v>2022:03:29 19:46:57</v>
       </c>
       <c r="E251" t="str">
         <v>1920</v>
@@ -8690,10 +8727,10 @@
         <v>misc6</v>
       </c>
       <c r="C252" t="str">
-        <v>IMG_2259.jpg</v>
+        <v>IMG_2011.jpg</v>
       </c>
       <c r="D252" t="str">
-        <v>2020:02:21 22:05:25</v>
+        <v>2022:03:29 22:18:21</v>
       </c>
       <c r="E252" t="str">
         <v>1920</v>
@@ -8713,16 +8750,16 @@
         <v>misc6</v>
       </c>
       <c r="C253" t="str">
-        <v>IMG_2555.jpg</v>
+        <v>IMG_2077.jpg</v>
       </c>
       <c r="D253" t="str">
-        <v>2022:05:20 22:18:02</v>
+        <v>2019:06:14 21:08:12</v>
       </c>
       <c r="E253" t="str">
         <v>1920</v>
       </c>
       <c r="F253" t="str">
-        <v>1080</v>
+        <v>1440</v>
       </c>
       <c r="G253" t="str">
         <v>横</v>
@@ -8736,10 +8773,10 @@
         <v>misc6</v>
       </c>
       <c r="C254" t="str">
-        <v>IMG_3369.jpg</v>
+        <v>IMG_2083.jpg</v>
       </c>
       <c r="D254" t="str">
-        <v>2024:08:06 21:59:33</v>
+        <v>2019:06:15 12:12:43</v>
       </c>
       <c r="E254" t="str">
         <v>1920</v>
@@ -8759,19 +8796,19 @@
         <v>misc6</v>
       </c>
       <c r="C255" t="str">
-        <v>IMG_3678.jpg</v>
+        <v>IMG_2259.jpg</v>
       </c>
       <c r="D255" t="str">
-        <v/>
+        <v>2020:02:21 22:05:25</v>
       </c>
       <c r="E255" t="str">
-        <v>1440</v>
+        <v>1920</v>
       </c>
       <c r="F255" t="str">
-        <v>1920</v>
+        <v>1440</v>
       </c>
       <c r="G255" t="str">
-        <v>縦</v>
+        <v>横</v>
       </c>
     </row>
     <row r="256">
@@ -8782,10 +8819,10 @@
         <v>misc6</v>
       </c>
       <c r="C256" t="str">
-        <v>IMG_3721.jpg</v>
+        <v>IMG_2555.jpg</v>
       </c>
       <c r="D256" t="str">
-        <v>2024:09:25 21:39:09</v>
+        <v>2022:05:20 22:18:02</v>
       </c>
       <c r="E256" t="str">
         <v>1920</v>
@@ -8805,10 +8842,10 @@
         <v>misc6</v>
       </c>
       <c r="C257" t="str">
-        <v>IMG_3850.jpg</v>
+        <v>IMG_3369.jpg</v>
       </c>
       <c r="D257" t="str">
-        <v>2024:10:07 22:07:38</v>
+        <v>2024:08:06 21:59:33</v>
       </c>
       <c r="E257" t="str">
         <v>1920</v>
@@ -8828,19 +8865,19 @@
         <v>misc6</v>
       </c>
       <c r="C258" t="str">
-        <v>IMG_3860.jpg</v>
+        <v>IMG_3678.jpg</v>
       </c>
       <c r="D258" t="str">
-        <v>2021:08:06 22:10:40</v>
+        <v/>
       </c>
       <c r="E258" t="str">
-        <v>1920</v>
+        <v>1440</v>
       </c>
       <c r="F258" t="str">
-        <v>1440</v>
+        <v>1920</v>
       </c>
       <c r="G258" t="str">
-        <v>横</v>
+        <v>縦</v>
       </c>
     </row>
     <row r="259">
@@ -8851,16 +8888,16 @@
         <v>misc6</v>
       </c>
       <c r="C259" t="str">
-        <v>IMG_3871.jpg</v>
+        <v>IMG_3721.jpg</v>
       </c>
       <c r="D259" t="str">
-        <v>2024:10:11 18:03:36</v>
+        <v>2024:09:25 21:39:09</v>
       </c>
       <c r="E259" t="str">
         <v>1920</v>
       </c>
       <c r="F259" t="str">
-        <v>1440</v>
+        <v>1080</v>
       </c>
       <c r="G259" t="str">
         <v>横</v>
@@ -8874,10 +8911,10 @@
         <v>misc6</v>
       </c>
       <c r="C260" t="str">
-        <v>IMG_4090.jpg</v>
+        <v>IMG_3850.jpg</v>
       </c>
       <c r="D260" t="str">
-        <v/>
+        <v>2024:10:07 22:07:38</v>
       </c>
       <c r="E260" t="str">
         <v>1920</v>
@@ -8897,10 +8934,10 @@
         <v>misc6</v>
       </c>
       <c r="C261" t="str">
-        <v>IMG_4095.jpg</v>
+        <v>IMG_3860.jpg</v>
       </c>
       <c r="D261" t="str">
-        <v/>
+        <v>2021:08:06 22:10:40</v>
       </c>
       <c r="E261" t="str">
         <v>1920</v>
@@ -8920,10 +8957,10 @@
         <v>misc6</v>
       </c>
       <c r="C262" t="str">
-        <v>IMG_4308.jpg</v>
+        <v>IMG_3871.jpg</v>
       </c>
       <c r="D262" t="str">
-        <v>2019:10:28 21:48:03</v>
+        <v>2024:10:11 18:03:36</v>
       </c>
       <c r="E262" t="str">
         <v>1920</v>
@@ -8943,10 +8980,10 @@
         <v>misc6</v>
       </c>
       <c r="C263" t="str">
-        <v>IMG_4316.jpg</v>
+        <v>IMG_4090.jpg</v>
       </c>
       <c r="D263" t="str">
-        <v>2019:10:29 23:04:43</v>
+        <v/>
       </c>
       <c r="E263" t="str">
         <v>1920</v>
@@ -8966,10 +9003,10 @@
         <v>misc6</v>
       </c>
       <c r="C264" t="str">
-        <v>IMG_4664.jpg</v>
+        <v>IMG_4095.jpg</v>
       </c>
       <c r="D264" t="str">
-        <v>2019:12:25 21:52:29</v>
+        <v/>
       </c>
       <c r="E264" t="str">
         <v>1920</v>
@@ -8989,10 +9026,10 @@
         <v>misc6</v>
       </c>
       <c r="C265" t="str">
-        <v>IMG_4665.jpg</v>
+        <v>IMG_4308.jpg</v>
       </c>
       <c r="D265" t="str">
-        <v>2021:11:05 22:44:13</v>
+        <v>2019:10:28 21:48:03</v>
       </c>
       <c r="E265" t="str">
         <v>1920</v>
@@ -9012,10 +9049,10 @@
         <v>misc6</v>
       </c>
       <c r="C266" t="str">
-        <v>IMG_4860.jpg</v>
+        <v>IMG_4316.jpg</v>
       </c>
       <c r="D266" t="str">
-        <v>2024:05:03 16:19:25</v>
+        <v>2019:10:29 23:04:43</v>
       </c>
       <c r="E266" t="str">
         <v>1920</v>
@@ -9035,10 +9072,10 @@
         <v>misc6</v>
       </c>
       <c r="C267" t="str">
-        <v>IMG_4862.jpg</v>
+        <v>IMG_4664.jpg</v>
       </c>
       <c r="D267" t="str">
-        <v>2024:05:03 16:22:46</v>
+        <v>2019:12:25 21:52:29</v>
       </c>
       <c r="E267" t="str">
         <v>1920</v>
@@ -9058,10 +9095,10 @@
         <v>misc6</v>
       </c>
       <c r="C268" t="str">
-        <v>IMG_4865.jpg</v>
+        <v>IMG_4665.jpg</v>
       </c>
       <c r="D268" t="str">
-        <v>2021:12:11 21:38:51</v>
+        <v>2021:11:05 22:44:13</v>
       </c>
       <c r="E268" t="str">
         <v>1920</v>
@@ -9081,16 +9118,16 @@
         <v>misc6</v>
       </c>
       <c r="C269" t="str">
-        <v>IMG_4950.jpg</v>
+        <v>IMG_4860.jpg</v>
       </c>
       <c r="D269" t="str">
-        <v/>
+        <v>2024:05:03 16:19:25</v>
       </c>
       <c r="E269" t="str">
         <v>1920</v>
       </c>
       <c r="F269" t="str">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="G269" t="str">
         <v>横</v>
@@ -9104,16 +9141,16 @@
         <v>misc6</v>
       </c>
       <c r="C270" t="str">
-        <v>IMG_4977.jpg</v>
+        <v>IMG_4862.jpg</v>
       </c>
       <c r="D270" t="str">
-        <v>2021:12:24 22:18:23</v>
+        <v>2024:05:03 16:22:46</v>
       </c>
       <c r="E270" t="str">
         <v>1920</v>
       </c>
       <c r="F270" t="str">
-        <v>1080</v>
+        <v>1440</v>
       </c>
       <c r="G270" t="str">
         <v>横</v>
@@ -9127,10 +9164,10 @@
         <v>misc6</v>
       </c>
       <c r="C271" t="str">
-        <v>IMG_5126.jpg</v>
+        <v>IMG_4865.jpg</v>
       </c>
       <c r="D271" t="str">
-        <v>2025:03:04 22:44:46</v>
+        <v>2021:12:11 21:38:51</v>
       </c>
       <c r="E271" t="str">
         <v>1920</v>
@@ -9150,16 +9187,16 @@
         <v>misc6</v>
       </c>
       <c r="C272" t="str">
-        <v>IMG_5135.jpg</v>
+        <v>IMG_4950.jpg</v>
       </c>
       <c r="D272" t="str">
-        <v>2022:11:12 09:38:40</v>
+        <v/>
       </c>
       <c r="E272" t="str">
         <v>1920</v>
       </c>
       <c r="F272" t="str">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="G272" t="str">
         <v>横</v>
@@ -9173,16 +9210,16 @@
         <v>misc6</v>
       </c>
       <c r="C273" t="str">
-        <v>IMG_5222.jpg</v>
+        <v>IMG_4977.jpg</v>
       </c>
       <c r="D273" t="str">
-        <v>2020:02:11 15:26:09</v>
+        <v>2021:12:24 22:18:23</v>
       </c>
       <c r="E273" t="str">
         <v>1920</v>
       </c>
       <c r="F273" t="str">
-        <v>1440</v>
+        <v>1080</v>
       </c>
       <c r="G273" t="str">
         <v>横</v>
@@ -9196,10 +9233,10 @@
         <v>misc6</v>
       </c>
       <c r="C274" t="str">
-        <v>IMG_5230.jpg</v>
+        <v>IMG_5126.jpg</v>
       </c>
       <c r="D274" t="str">
-        <v/>
+        <v>2025:03:04 22:44:46</v>
       </c>
       <c r="E274" t="str">
         <v>1920</v>
@@ -9219,10 +9256,10 @@
         <v>misc6</v>
       </c>
       <c r="C275" t="str">
-        <v>IMG_5256.jpg</v>
+        <v>IMG_5135.jpg</v>
       </c>
       <c r="D275" t="str">
-        <v>2020:02:21 22:29:48</v>
+        <v>2022:11:12 09:38:40</v>
       </c>
       <c r="E275" t="str">
         <v>1920</v>
@@ -9242,10 +9279,10 @@
         <v>misc6</v>
       </c>
       <c r="C276" t="str">
-        <v>IMG_5406.jpg</v>
+        <v>IMG_5222.jpg</v>
       </c>
       <c r="D276" t="str">
-        <v>2020:03:10 21:53:00</v>
+        <v>2020:02:11 15:26:09</v>
       </c>
       <c r="E276" t="str">
         <v>1920</v>
@@ -9265,10 +9302,10 @@
         <v>misc6</v>
       </c>
       <c r="C277" t="str">
-        <v>IMG_5410.jpg</v>
+        <v>IMG_5230.jpg</v>
       </c>
       <c r="D277" t="str">
-        <v>2020:03:10 21:54:14</v>
+        <v/>
       </c>
       <c r="E277" t="str">
         <v>1920</v>
@@ -9288,16 +9325,16 @@
         <v>misc6</v>
       </c>
       <c r="C278" t="str">
-        <v>IMG_5426.jpg</v>
+        <v>IMG_5256.jpg</v>
       </c>
       <c r="D278" t="str">
-        <v/>
+        <v>2020:02:21 22:29:48</v>
       </c>
       <c r="E278" t="str">
         <v>1920</v>
       </c>
       <c r="F278" t="str">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="G278" t="str">
         <v>横</v>
@@ -9311,10 +9348,10 @@
         <v>misc6</v>
       </c>
       <c r="C279" t="str">
-        <v>IMG_5503.jpg</v>
+        <v>IMG_5406.jpg</v>
       </c>
       <c r="D279" t="str">
-        <v>2020:03:17 22:18:08</v>
+        <v>2020:03:10 21:53:00</v>
       </c>
       <c r="E279" t="str">
         <v>1920</v>
@@ -9334,10 +9371,10 @@
         <v>misc6</v>
       </c>
       <c r="C280" t="str">
-        <v>IMG_5657.jpg</v>
+        <v>IMG_5410.jpg</v>
       </c>
       <c r="D280" t="str">
-        <v>2025:05:13 22:11:10</v>
+        <v>2020:03:10 21:54:14</v>
       </c>
       <c r="E280" t="str">
         <v>1920</v>
@@ -9357,16 +9394,16 @@
         <v>misc6</v>
       </c>
       <c r="C281" t="str">
-        <v>IMG_5699.jpg</v>
+        <v>IMG_5426.jpg</v>
       </c>
       <c r="D281" t="str">
-        <v>2020:04:05 15:16:39</v>
+        <v/>
       </c>
       <c r="E281" t="str">
         <v>1920</v>
       </c>
       <c r="F281" t="str">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="G281" t="str">
         <v>横</v>
@@ -9380,16 +9417,16 @@
         <v>misc6</v>
       </c>
       <c r="C282" t="str">
-        <v>IMG_5769.jpg</v>
+        <v>IMG_5503.jpg</v>
       </c>
       <c r="D282" t="str">
-        <v/>
+        <v>2020:03:17 22:18:08</v>
       </c>
       <c r="E282" t="str">
         <v>1920</v>
       </c>
       <c r="F282" t="str">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="G282" t="str">
         <v>横</v>
@@ -9403,10 +9440,10 @@
         <v>misc6</v>
       </c>
       <c r="C283" t="str">
-        <v>IMG_6188.jpg</v>
+        <v>IMG_5657.jpg</v>
       </c>
       <c r="D283" t="str">
-        <v>2024:05:03 15:06:19</v>
+        <v>2025:05:13 22:11:10</v>
       </c>
       <c r="E283" t="str">
         <v>1920</v>
@@ -9426,16 +9463,16 @@
         <v>misc6</v>
       </c>
       <c r="C284" t="str">
-        <v>IMG_6252.jpg</v>
+        <v>IMG_5699.jpg</v>
       </c>
       <c r="D284" t="str">
-        <v/>
+        <v>2020:04:05 15:16:39</v>
       </c>
       <c r="E284" t="str">
         <v>1920</v>
       </c>
       <c r="F284" t="str">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="G284" t="str">
         <v>横</v>
@@ -9449,16 +9486,16 @@
         <v>misc6</v>
       </c>
       <c r="C285" t="str">
-        <v>IMG_6266.jpg</v>
+        <v>IMG_5769.jpg</v>
       </c>
       <c r="D285" t="str">
-        <v>2020:07:17 08:29:06</v>
+        <v/>
       </c>
       <c r="E285" t="str">
         <v>1920</v>
       </c>
       <c r="F285" t="str">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="G285" t="str">
         <v>横</v>
@@ -9472,10 +9509,10 @@
         <v>misc6</v>
       </c>
       <c r="C286" t="str">
-        <v>IMG_6275.jpg</v>
+        <v>IMG_6188.jpg</v>
       </c>
       <c r="D286" t="str">
-        <v>2022:06:29 08:37:51</v>
+        <v>2024:05:03 15:06:19</v>
       </c>
       <c r="E286" t="str">
         <v>1920</v>
@@ -9495,7 +9532,7 @@
         <v>misc6</v>
       </c>
       <c r="C287" t="str">
-        <v>IMG_6284.jpg</v>
+        <v>IMG_6252.jpg</v>
       </c>
       <c r="D287" t="str">
         <v/>
@@ -9518,16 +9555,16 @@
         <v>misc6</v>
       </c>
       <c r="C288" t="str">
-        <v>IMG_6289.jpg</v>
+        <v>IMG_6266.jpg</v>
       </c>
       <c r="D288" t="str">
-        <v/>
+        <v>2020:07:17 08:29:06</v>
       </c>
       <c r="E288" t="str">
         <v>1920</v>
       </c>
       <c r="F288" t="str">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="G288" t="str">
         <v>横</v>
@@ -9541,16 +9578,16 @@
         <v>misc6</v>
       </c>
       <c r="C289" t="str">
-        <v>IMG_6731.jpg</v>
+        <v>IMG_6275.jpg</v>
       </c>
       <c r="D289" t="str">
-        <v>2025:09:05 19:04:42</v>
+        <v>2022:06:29 08:37:51</v>
       </c>
       <c r="E289" t="str">
         <v>1920</v>
       </c>
       <c r="F289" t="str">
-        <v>1080</v>
+        <v>1440</v>
       </c>
       <c r="G289" t="str">
         <v>横</v>
@@ -9564,16 +9601,16 @@
         <v>misc6</v>
       </c>
       <c r="C290" t="str">
-        <v>IMG_7091-EDIT.jpg</v>
+        <v>IMG_6284.jpg</v>
       </c>
       <c r="D290" t="str">
-        <v>2023:03:20 13:17:22</v>
+        <v/>
       </c>
       <c r="E290" t="str">
         <v>1920</v>
       </c>
       <c r="F290" t="str">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="G290" t="str">
         <v>横</v>
@@ -9587,7 +9624,7 @@
         <v>misc6</v>
       </c>
       <c r="C291" t="str">
-        <v>IMG_7221.jpg</v>
+        <v>IMG_6289.jpg</v>
       </c>
       <c r="D291" t="str">
         <v/>
@@ -9610,16 +9647,16 @@
         <v>misc6</v>
       </c>
       <c r="C292" t="str">
-        <v>IMG_7328.jpg</v>
+        <v>IMG_6731.jpg</v>
       </c>
       <c r="D292" t="str">
-        <v>2023:03:28 22:45:04</v>
+        <v>2025:09:05 19:04:42</v>
       </c>
       <c r="E292" t="str">
         <v>1920</v>
       </c>
       <c r="F292" t="str">
-        <v>1440</v>
+        <v>1080</v>
       </c>
       <c r="G292" t="str">
         <v>横</v>
@@ -9633,10 +9670,10 @@
         <v>misc6</v>
       </c>
       <c r="C293" t="str">
-        <v>IMG_7333.jpg</v>
+        <v>IMG_7091-EDIT.jpg</v>
       </c>
       <c r="D293" t="str">
-        <v>2023:03:28 22:54:42</v>
+        <v>2023:03:20 13:17:22</v>
       </c>
       <c r="E293" t="str">
         <v>1920</v>
@@ -9656,19 +9693,19 @@
         <v>misc6</v>
       </c>
       <c r="C294" t="str">
-        <v>IMG_7586.jpg</v>
+        <v>IMG_7221.jpg</v>
       </c>
       <c r="D294" t="str">
         <v/>
       </c>
       <c r="E294" t="str">
+        <v>1920</v>
+      </c>
+      <c r="F294" t="str">
         <v>1439</v>
       </c>
-      <c r="F294" t="str">
-        <v>1920</v>
-      </c>
       <c r="G294" t="str">
-        <v>縦</v>
+        <v>横</v>
       </c>
     </row>
     <row r="295">
@@ -9679,10 +9716,10 @@
         <v>misc6</v>
       </c>
       <c r="C295" t="str">
-        <v>IMG_7605.jpg</v>
+        <v>IMG_7328.jpg</v>
       </c>
       <c r="D295" t="str">
-        <v>2025:11:19 22:10:10</v>
+        <v>2023:03:28 22:45:04</v>
       </c>
       <c r="E295" t="str">
         <v>1920</v>
@@ -9702,16 +9739,16 @@
         <v>misc6</v>
       </c>
       <c r="C296" t="str">
-        <v>IMG_7642.jpg</v>
+        <v>IMG_7333.jpg</v>
       </c>
       <c r="D296" t="str">
-        <v/>
+        <v>2023:03:28 22:54:42</v>
       </c>
       <c r="E296" t="str">
         <v>1920</v>
       </c>
       <c r="F296" t="str">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="G296" t="str">
         <v>横</v>
@@ -9725,19 +9762,19 @@
         <v>misc6</v>
       </c>
       <c r="C297" t="str">
-        <v>IMG_7643.jpg</v>
+        <v>IMG_7586.jpg</v>
       </c>
       <c r="D297" t="str">
         <v/>
       </c>
       <c r="E297" t="str">
-        <v>1920</v>
+        <v>1439</v>
       </c>
       <c r="F297" t="str">
-        <v>1439</v>
+        <v>1920</v>
       </c>
       <c r="G297" t="str">
-        <v>横</v>
+        <v>縦</v>
       </c>
     </row>
     <row r="298">
@@ -9748,16 +9785,16 @@
         <v>misc6</v>
       </c>
       <c r="C298" t="str">
-        <v>IMG_7647.jpg</v>
+        <v>IMG_7605.jpg</v>
       </c>
       <c r="D298" t="str">
-        <v/>
+        <v>2025:11:19 22:10:10</v>
       </c>
       <c r="E298" t="str">
         <v>1920</v>
       </c>
       <c r="F298" t="str">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="G298" t="str">
         <v>横</v>
@@ -9771,7 +9808,7 @@
         <v>misc6</v>
       </c>
       <c r="C299" t="str">
-        <v>IMG_7649.jpg</v>
+        <v>IMG_7642.jpg</v>
       </c>
       <c r="D299" t="str">
         <v/>
@@ -9794,19 +9831,19 @@
         <v>misc6</v>
       </c>
       <c r="C300" t="str">
-        <v>IMG_7658.jpg</v>
+        <v>IMG_7643.jpg</v>
       </c>
       <c r="D300" t="str">
         <v/>
       </c>
       <c r="E300" t="str">
+        <v>1920</v>
+      </c>
+      <c r="F300" t="str">
         <v>1439</v>
       </c>
-      <c r="F300" t="str">
-        <v>1920</v>
-      </c>
       <c r="G300" t="str">
-        <v>縦</v>
+        <v>横</v>
       </c>
     </row>
     <row r="301">
@@ -9817,16 +9854,16 @@
         <v>misc6</v>
       </c>
       <c r="C301" t="str">
-        <v>IMG_7688.jpg</v>
+        <v>IMG_7647.jpg</v>
       </c>
       <c r="D301" t="str">
-        <v>2023:04:07 19:04:44</v>
+        <v/>
       </c>
       <c r="E301" t="str">
         <v>1920</v>
       </c>
       <c r="F301" t="str">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="G301" t="str">
         <v>横</v>
@@ -9840,16 +9877,16 @@
         <v>misc6</v>
       </c>
       <c r="C302" t="str">
-        <v>IMG_7693.jpg</v>
+        <v>IMG_7649.jpg</v>
       </c>
       <c r="D302" t="str">
-        <v>2023:04:07 19:06:28</v>
+        <v/>
       </c>
       <c r="E302" t="str">
         <v>1920</v>
       </c>
       <c r="F302" t="str">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="G302" t="str">
         <v>横</v>
@@ -9863,7 +9900,7 @@
         <v>misc6</v>
       </c>
       <c r="C303" t="str">
-        <v>IMG_8037.jpg</v>
+        <v>IMG_7658.jpg</v>
       </c>
       <c r="D303" t="str">
         <v/>
@@ -9886,16 +9923,16 @@
         <v>misc6</v>
       </c>
       <c r="C304" t="str">
-        <v>IMG_8274.jpg</v>
+        <v>IMG_7688.jpg</v>
       </c>
       <c r="D304" t="str">
-        <v/>
+        <v>2023:04:07 19:04:44</v>
       </c>
       <c r="E304" t="str">
         <v>1920</v>
       </c>
       <c r="F304" t="str">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="G304" t="str">
         <v>横</v>
@@ -9909,16 +9946,16 @@
         <v>misc6</v>
       </c>
       <c r="C305" t="str">
-        <v>IMG_8277.jpg</v>
+        <v>IMG_7693.jpg</v>
       </c>
       <c r="D305" t="str">
-        <v/>
+        <v>2023:04:07 19:06:28</v>
       </c>
       <c r="E305" t="str">
         <v>1920</v>
       </c>
       <c r="F305" t="str">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="G305" t="str">
         <v>横</v>
@@ -9932,19 +9969,19 @@
         <v>misc6</v>
       </c>
       <c r="C306" t="str">
-        <v>IMG_8346.jpg</v>
+        <v>IMG_8037.jpg</v>
       </c>
       <c r="D306" t="str">
-        <v>2023:02:23 01:10:15</v>
+        <v/>
       </c>
       <c r="E306" t="str">
-        <v>1920</v>
+        <v>1439</v>
       </c>
       <c r="F306" t="str">
-        <v>1080</v>
+        <v>1920</v>
       </c>
       <c r="G306" t="str">
-        <v>横</v>
+        <v>縦</v>
       </c>
     </row>
     <row r="307">
@@ -9955,16 +9992,16 @@
         <v>misc6</v>
       </c>
       <c r="C307" t="str">
-        <v>IMG_8348.jpg</v>
+        <v>IMG_8274.jpg</v>
       </c>
       <c r="D307" t="str">
-        <v>2023:02:23 01:17:34</v>
+        <v/>
       </c>
       <c r="E307" t="str">
         <v>1920</v>
       </c>
       <c r="F307" t="str">
-        <v>1080</v>
+        <v>1439</v>
       </c>
       <c r="G307" t="str">
         <v>横</v>
@@ -9978,16 +10015,16 @@
         <v>misc6</v>
       </c>
       <c r="C308" t="str">
-        <v>IMG_8354.jpg</v>
+        <v>IMG_8277.jpg</v>
       </c>
       <c r="D308" t="str">
-        <v>2023:02:23 01:28:15</v>
+        <v/>
       </c>
       <c r="E308" t="str">
         <v>1920</v>
       </c>
       <c r="F308" t="str">
-        <v>1080</v>
+        <v>1439</v>
       </c>
       <c r="G308" t="str">
         <v>横</v>
@@ -10001,16 +10038,16 @@
         <v>misc6</v>
       </c>
       <c r="C309" t="str">
-        <v>IMG_8360.jpg</v>
+        <v>IMG_8346.jpg</v>
       </c>
       <c r="D309" t="str">
-        <v/>
+        <v>2023:02:23 01:10:15</v>
       </c>
       <c r="E309" t="str">
         <v>1920</v>
       </c>
       <c r="F309" t="str">
-        <v>1439</v>
+        <v>1080</v>
       </c>
       <c r="G309" t="str">
         <v>横</v>
@@ -10024,16 +10061,16 @@
         <v>misc6</v>
       </c>
       <c r="C310" t="str">
-        <v>IMG_8614.jpg</v>
+        <v>IMG_8348.jpg</v>
       </c>
       <c r="D310" t="str">
-        <v>2023:03:22 22:48:47</v>
+        <v>2023:02:23 01:17:34</v>
       </c>
       <c r="E310" t="str">
         <v>1920</v>
       </c>
       <c r="F310" t="str">
-        <v>1440</v>
+        <v>1080</v>
       </c>
       <c r="G310" t="str">
         <v>横</v>
@@ -10047,16 +10084,16 @@
         <v>misc6</v>
       </c>
       <c r="C311" t="str">
-        <v>IMG_8826.jpg</v>
+        <v>IMG_8354.jpg</v>
       </c>
       <c r="D311" t="str">
-        <v>2023:06:30 06:24:25</v>
+        <v>2023:02:23 01:28:15</v>
       </c>
       <c r="E311" t="str">
         <v>1920</v>
       </c>
       <c r="F311" t="str">
-        <v>1440</v>
+        <v>1080</v>
       </c>
       <c r="G311" t="str">
         <v>横</v>
@@ -10070,16 +10107,16 @@
         <v>misc6</v>
       </c>
       <c r="C312" t="str">
-        <v>IMG_8831.jpg</v>
+        <v>IMG_8360.jpg</v>
       </c>
       <c r="D312" t="str">
-        <v>2023:06:30 06:24:53</v>
+        <v/>
       </c>
       <c r="E312" t="str">
         <v>1920</v>
       </c>
       <c r="F312" t="str">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="G312" t="str">
         <v>横</v>
@@ -10093,10 +10130,10 @@
         <v>misc6</v>
       </c>
       <c r="C313" t="str">
-        <v>IMG_8833.jpg</v>
+        <v>IMG_8614.jpg</v>
       </c>
       <c r="D313" t="str">
-        <v>2023:06:30 06:25:07</v>
+        <v>2023:03:22 22:48:47</v>
       </c>
       <c r="E313" t="str">
         <v>1920</v>
@@ -10116,10 +10153,10 @@
         <v>misc6</v>
       </c>
       <c r="C314" t="str">
-        <v>IMG_8838.jpg</v>
+        <v>IMG_8826.jpg</v>
       </c>
       <c r="D314" t="str">
-        <v>2023:06:30 06:39:49</v>
+        <v>2023:06:30 06:24:25</v>
       </c>
       <c r="E314" t="str">
         <v>1920</v>
@@ -10139,16 +10176,16 @@
         <v>misc6</v>
       </c>
       <c r="C315" t="str">
-        <v>IMG_8842.jpg</v>
+        <v>IMG_8831.jpg</v>
       </c>
       <c r="D315" t="str">
-        <v/>
+        <v>2023:06:30 06:24:53</v>
       </c>
       <c r="E315" t="str">
         <v>1920</v>
       </c>
       <c r="F315" t="str">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="G315" t="str">
         <v>横</v>
@@ -10162,16 +10199,16 @@
         <v>misc6</v>
       </c>
       <c r="C316" t="str">
-        <v>IMG_9753.jpg</v>
+        <v>IMG_8833.jpg</v>
       </c>
       <c r="D316" t="str">
-        <v/>
+        <v>2023:06:30 06:25:07</v>
       </c>
       <c r="E316" t="str">
         <v>1920</v>
       </c>
       <c r="F316" t="str">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="G316" t="str">
         <v>横</v>
@@ -10185,16 +10222,16 @@
         <v>misc6</v>
       </c>
       <c r="C317" t="str">
-        <v>IMG_9810.jpg</v>
+        <v>IMG_8838.jpg</v>
       </c>
       <c r="D317" t="str">
-        <v/>
+        <v>2023:06:30 06:39:49</v>
       </c>
       <c r="E317" t="str">
         <v>1920</v>
       </c>
       <c r="F317" t="str">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="G317" t="str">
         <v>横</v>
@@ -10208,7 +10245,7 @@
         <v>misc6</v>
       </c>
       <c r="C318" t="str">
-        <v>IMG_9908.jpg</v>
+        <v>IMG_8842.jpg</v>
       </c>
       <c r="D318" t="str">
         <v/>
@@ -10231,7 +10268,7 @@
         <v>misc6</v>
       </c>
       <c r="C319" t="str">
-        <v>IMG_9965.jpg</v>
+        <v>IMG_9753.jpg</v>
       </c>
       <c r="D319" t="str">
         <v/>
@@ -10251,22 +10288,22 @@
         <v/>
       </c>
       <c r="B320" t="str">
-        <v>misc8</v>
+        <v>misc6</v>
       </c>
       <c r="C320" t="str">
-        <v>IMG_0424.jpg</v>
+        <v>IMG_9810.jpg</v>
       </c>
       <c r="D320" t="str">
         <v/>
       </c>
       <c r="E320" t="str">
+        <v>1920</v>
+      </c>
+      <c r="F320" t="str">
         <v>1439</v>
       </c>
-      <c r="F320" t="str">
-        <v>1920</v>
-      </c>
       <c r="G320" t="str">
-        <v>縦</v>
+        <v>横</v>
       </c>
     </row>
     <row r="321">
@@ -10274,10 +10311,10 @@
         <v/>
       </c>
       <c r="B321" t="str">
-        <v>misc8</v>
+        <v>misc6</v>
       </c>
       <c r="C321" t="str">
-        <v>IMG_0874.jpg</v>
+        <v>IMG_9908.jpg</v>
       </c>
       <c r="D321" t="str">
         <v/>
@@ -10297,10 +10334,10 @@
         <v/>
       </c>
       <c r="B322" t="str">
-        <v>misc8</v>
+        <v>misc6</v>
       </c>
       <c r="C322" t="str">
-        <v>IMG_3650.jpg</v>
+        <v>IMG_9965.jpg</v>
       </c>
       <c r="D322" t="str">
         <v/>
@@ -10309,7 +10346,7 @@
         <v>1920</v>
       </c>
       <c r="F322" t="str">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="G322" t="str">
         <v>横</v>
@@ -10323,19 +10360,19 @@
         <v>misc8</v>
       </c>
       <c r="C323" t="str">
-        <v>IMG_3652.jpg</v>
+        <v>IMG_0424.jpg</v>
       </c>
       <c r="D323" t="str">
         <v/>
       </c>
       <c r="E323" t="str">
-        <v>1920</v>
+        <v>1439</v>
       </c>
       <c r="F323" t="str">
-        <v>1440</v>
+        <v>1920</v>
       </c>
       <c r="G323" t="str">
-        <v>横</v>
+        <v>縦</v>
       </c>
     </row>
     <row r="324">
@@ -10346,16 +10383,16 @@
         <v>misc8</v>
       </c>
       <c r="C324" t="str">
-        <v>IMG_6265.jpg</v>
+        <v>IMG_0874.jpg</v>
       </c>
       <c r="D324" t="str">
-        <v>2025:07:25 23:25:23</v>
+        <v/>
       </c>
       <c r="E324" t="str">
         <v>1920</v>
       </c>
       <c r="F324" t="str">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="G324" t="str">
         <v>横</v>
@@ -10369,7 +10406,7 @@
         <v>misc8</v>
       </c>
       <c r="C325" t="str">
-        <v>IMG_6268.jpg</v>
+        <v>IMG_3650.jpg</v>
       </c>
       <c r="D325" t="str">
         <v/>
@@ -10392,19 +10429,19 @@
         <v>misc8</v>
       </c>
       <c r="C326" t="str">
-        <v>IMG_7779.jpg</v>
+        <v>IMG_3652.jpg</v>
       </c>
       <c r="D326" t="str">
         <v/>
       </c>
       <c r="E326" t="str">
-        <v>1080</v>
+        <v>1920</v>
       </c>
       <c r="F326" t="str">
-        <v>1920</v>
+        <v>1440</v>
       </c>
       <c r="G326" t="str">
-        <v>縦</v>
+        <v>横</v>
       </c>
     </row>
     <row r="327">
@@ -10412,22 +10449,22 @@
         <v/>
       </c>
       <c r="B327" t="str">
-        <v>or</v>
+        <v>misc8</v>
       </c>
       <c r="C327" t="str">
-        <v>69de880f-808f-46ef-9255-ad70caa4c671.jpg</v>
+        <v>IMG_6265.jpg</v>
       </c>
       <c r="D327" t="str">
-        <v/>
+        <v>2025:07:25 23:25:23</v>
       </c>
       <c r="E327" t="str">
-        <v>1440</v>
+        <v>1920</v>
       </c>
       <c r="F327" t="str">
-        <v>1920</v>
+        <v>1440</v>
       </c>
       <c r="G327" t="str">
-        <v>縦</v>
+        <v>横</v>
       </c>
     </row>
     <row r="328">
@@ -10435,13 +10472,13 @@
         <v/>
       </c>
       <c r="B328" t="str">
-        <v>or</v>
+        <v>misc8</v>
       </c>
       <c r="C328" t="str">
-        <v>IMG_0090.jpg</v>
+        <v>IMG_6268.jpg</v>
       </c>
       <c r="D328" t="str">
-        <v>2025:03:05 17:51:26</v>
+        <v/>
       </c>
       <c r="E328" t="str">
         <v>1920</v>
@@ -10458,22 +10495,22 @@
         <v/>
       </c>
       <c r="B329" t="str">
-        <v>or</v>
+        <v>misc8</v>
       </c>
       <c r="C329" t="str">
-        <v>IMG_0256.jpg</v>
+        <v>IMG_7779.jpg</v>
       </c>
       <c r="D329" t="str">
-        <v>2021:06:21 17:30:37</v>
+        <v/>
       </c>
       <c r="E329" t="str">
-        <v>1920</v>
+        <v>1080</v>
       </c>
       <c r="F329" t="str">
-        <v>1440</v>
+        <v>1920</v>
       </c>
       <c r="G329" t="str">
-        <v>横</v>
+        <v>縦</v>
       </c>
     </row>
     <row r="330">
@@ -10484,19 +10521,19 @@
         <v>or</v>
       </c>
       <c r="C330" t="str">
-        <v>IMG_0419.jpg</v>
+        <v>69de880f-808f-46ef-9255-ad70caa4c671.jpg</v>
       </c>
       <c r="D330" t="str">
-        <v>2021:04:02 12:36:40</v>
+        <v/>
       </c>
       <c r="E330" t="str">
-        <v>1920</v>
+        <v>1440</v>
       </c>
       <c r="F330" t="str">
-        <v>1440</v>
+        <v>1920</v>
       </c>
       <c r="G330" t="str">
-        <v>横</v>
+        <v>縦</v>
       </c>
     </row>
     <row r="331">
@@ -10507,10 +10544,10 @@
         <v>or</v>
       </c>
       <c r="C331" t="str">
-        <v>IMG_0883.jpg</v>
+        <v>IMG_0090.jpg</v>
       </c>
       <c r="D331" t="str">
-        <v>2021:06:11 13:38:08</v>
+        <v>2025:03:05 17:51:26</v>
       </c>
       <c r="E331" t="str">
         <v>1920</v>
@@ -10530,10 +10567,10 @@
         <v>or</v>
       </c>
       <c r="C332" t="str">
-        <v>IMG_0994.jpg</v>
+        <v>IMG_0256.jpg</v>
       </c>
       <c r="D332" t="str">
-        <v>2021:07:02 14:58:49</v>
+        <v>2021:06:21 17:30:37</v>
       </c>
       <c r="E332" t="str">
         <v>1920</v>
@@ -10553,10 +10590,10 @@
         <v>or</v>
       </c>
       <c r="C333" t="str">
-        <v>IMG_1080.jpg</v>
+        <v>IMG_0419.jpg</v>
       </c>
       <c r="D333" t="str">
-        <v>2021:07:30 14:04:29</v>
+        <v>2021:04:02 12:36:40</v>
       </c>
       <c r="E333" t="str">
         <v>1920</v>
@@ -10576,10 +10613,10 @@
         <v>or</v>
       </c>
       <c r="C334" t="str">
-        <v>IMG_1139.jpg</v>
+        <v>IMG_0883.jpg</v>
       </c>
       <c r="D334" t="str">
-        <v>2021:08:13 18:05:10</v>
+        <v>2021:06:11 13:38:08</v>
       </c>
       <c r="E334" t="str">
         <v>1920</v>
@@ -10599,10 +10636,10 @@
         <v>or</v>
       </c>
       <c r="C335" t="str">
-        <v>IMG_2676.jpg</v>
+        <v>IMG_0994.jpg</v>
       </c>
       <c r="D335" t="str">
-        <v/>
+        <v>2021:07:02 14:58:49</v>
       </c>
       <c r="E335" t="str">
         <v>1920</v>
@@ -10615,17 +10652,17 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336">
-        <v>22</v>
+      <c r="A336" t="str">
+        <v/>
       </c>
       <c r="B336" t="str">
         <v>or</v>
       </c>
       <c r="C336" t="str">
-        <v>IMG_2953.jpg</v>
+        <v>IMG_1080.jpg</v>
       </c>
       <c r="D336" t="str">
-        <v>2019:03:29 15:31:13</v>
+        <v>2021:07:30 14:04:29</v>
       </c>
       <c r="E336" t="str">
         <v>1920</v>
@@ -10645,16 +10682,16 @@
         <v>or</v>
       </c>
       <c r="C337" t="str">
-        <v>IMG_8373.jpg</v>
+        <v>IMG_1139.jpg</v>
       </c>
       <c r="D337" t="str">
-        <v/>
+        <v>2021:08:13 18:05:10</v>
       </c>
       <c r="E337" t="str">
         <v>1920</v>
       </c>
       <c r="F337" t="str">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="G337" t="str">
         <v>横</v>
@@ -10668,7 +10705,7 @@
         <v>or</v>
       </c>
       <c r="C338" t="str">
-        <v>IMG_8394.jpg</v>
+        <v>IMG_2676.jpg</v>
       </c>
       <c r="D338" t="str">
         <v/>
@@ -10684,17 +10721,17 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" t="str">
-        <v/>
+      <c r="A339">
+        <v>22</v>
       </c>
       <c r="B339" t="str">
         <v>or</v>
       </c>
       <c r="C339" t="str">
-        <v>IMG_8610.jpg</v>
+        <v>IMG_2953.jpg</v>
       </c>
       <c r="D339" t="str">
-        <v>2024:04:12 14:24:24</v>
+        <v>2019:03:29 15:31:13</v>
       </c>
       <c r="E339" t="str">
         <v>1920</v>
@@ -10714,33 +10751,33 @@
         <v>or</v>
       </c>
       <c r="C340" t="str">
-        <v>IMG_8611.jpg</v>
+        <v>IMG_8373.jpg</v>
       </c>
       <c r="D340" t="str">
-        <v>2024:04:12 15:34:36</v>
+        <v/>
       </c>
       <c r="E340" t="str">
         <v>1920</v>
       </c>
       <c r="F340" t="str">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="G340" t="str">
         <v>横</v>
       </c>
     </row>
     <row r="341">
-      <c r="A341">
-        <v>23</v>
+      <c r="A341" t="str">
+        <v/>
       </c>
       <c r="B341" t="str">
         <v>or</v>
       </c>
       <c r="C341" t="str">
-        <v>IMG_8659.jpg</v>
+        <v>IMG_8394.jpg</v>
       </c>
       <c r="D341" t="str">
-        <v>2024:05:24 12:10:01</v>
+        <v/>
       </c>
       <c r="E341" t="str">
         <v>1920</v>
@@ -10760,19 +10797,19 @@
         <v>or</v>
       </c>
       <c r="C342" t="str">
-        <v>IMG_8789.jpg</v>
+        <v>IMG_8610.jpg</v>
       </c>
       <c r="D342" t="str">
-        <v/>
+        <v>2024:04:12 14:24:24</v>
       </c>
       <c r="E342" t="str">
-        <v>1440</v>
+        <v>1920</v>
       </c>
       <c r="F342" t="str">
-        <v>1920</v>
+        <v>1440</v>
       </c>
       <c r="G342" t="str">
-        <v>縦</v>
+        <v>横</v>
       </c>
     </row>
     <row r="343">
@@ -10783,10 +10820,10 @@
         <v>or</v>
       </c>
       <c r="C343" t="str">
-        <v>IMG_9067.jpg</v>
+        <v>IMG_8611.jpg</v>
       </c>
       <c r="D343" t="str">
-        <v>2024:05:22 10:01:10</v>
+        <v>2024:04:12 15:34:36</v>
       </c>
       <c r="E343" t="str">
         <v>1920</v>
@@ -10799,17 +10836,17 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" t="str">
-        <v/>
+      <c r="A344">
+        <v>23</v>
       </c>
       <c r="B344" t="str">
         <v>or</v>
       </c>
       <c r="C344" t="str">
-        <v>IMG_9120.jpg</v>
+        <v>IMG_8659.jpg</v>
       </c>
       <c r="D344" t="str">
-        <v>2024:08:05 10:10:24</v>
+        <v>2024:05:24 12:10:01</v>
       </c>
       <c r="E344" t="str">
         <v>1920</v>
@@ -10829,33 +10866,33 @@
         <v>or</v>
       </c>
       <c r="C345" t="str">
-        <v>IMG_9214.jpg</v>
+        <v>IMG_8789.jpg</v>
       </c>
       <c r="D345" t="str">
-        <v>2024:08:26 14:14:55</v>
+        <v/>
       </c>
       <c r="E345" t="str">
-        <v>1920</v>
+        <v>1440</v>
       </c>
       <c r="F345" t="str">
-        <v>1440</v>
+        <v>1920</v>
       </c>
       <c r="G345" t="str">
-        <v>横</v>
+        <v>縦</v>
       </c>
     </row>
     <row r="346">
-      <c r="A346">
-        <v>24</v>
+      <c r="A346" t="str">
+        <v/>
       </c>
       <c r="B346" t="str">
         <v>or</v>
       </c>
       <c r="C346" t="str">
-        <v>IMG_9883.jpg</v>
+        <v>IMG_9067.jpg</v>
       </c>
       <c r="D346" t="str">
-        <v>2025:01:06 11:58:25</v>
+        <v>2024:05:22 10:01:10</v>
       </c>
       <c r="E346" t="str">
         <v>1920</v>
@@ -10875,10 +10912,10 @@
         <v>or</v>
       </c>
       <c r="C347" t="str">
-        <v>IMG_9957.jpg</v>
+        <v>IMG_9120.jpg</v>
       </c>
       <c r="D347" t="str">
-        <v>2025:01:27 13:24:25</v>
+        <v>2024:08:05 10:10:24</v>
       </c>
       <c r="E347" t="str">
         <v>1920</v>
@@ -10898,10 +10935,10 @@
         <v>or</v>
       </c>
       <c r="C348" t="str">
-        <v>IMG_9988.jpg</v>
+        <v>IMG_9214.jpg</v>
       </c>
       <c r="D348" t="str">
-        <v>2025:02:03 10:38:27</v>
+        <v>2024:08:26 14:14:55</v>
       </c>
       <c r="E348" t="str">
         <v>1920</v>
@@ -10914,17 +10951,17 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" t="str">
-        <v/>
+      <c r="A349">
+        <v>24</v>
       </c>
       <c r="B349" t="str">
         <v>or</v>
       </c>
       <c r="C349" t="str">
-        <v>cache_Messagep8461.jpg</v>
+        <v>IMG_9883.jpg</v>
       </c>
       <c r="D349" t="str">
-        <v>2021:08:13 18:15:55</v>
+        <v>2025:01:06 11:58:25</v>
       </c>
       <c r="E349" t="str">
         <v>1920</v>
@@ -10937,17 +10974,17 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350">
-        <v>20</v>
+      <c r="A350" t="str">
+        <v/>
       </c>
       <c r="B350" t="str">
         <v>or</v>
       </c>
       <c r="C350" t="str">
-        <v>cache_Messagep8464.jpg</v>
+        <v>IMG_9957.jpg</v>
       </c>
       <c r="D350" t="str">
-        <v>2021:08:13 16:24:10</v>
+        <v>2025:01:27 13:24:25</v>
       </c>
       <c r="E350" t="str">
         <v>1920</v>
@@ -10964,13 +11001,13 @@
         <v/>
       </c>
       <c r="B351" t="str">
-        <v>rehab</v>
+        <v>or</v>
       </c>
       <c r="C351" t="str">
-        <v>7F793CFB-7E3D-427D-A2B9-7F48876F8894.jpg</v>
+        <v>IMG_9988.jpg</v>
       </c>
       <c r="D351" t="str">
-        <v/>
+        <v>2025:02:03 10:38:27</v>
       </c>
       <c r="E351" t="str">
         <v>1920</v>
@@ -10987,13 +11024,13 @@
         <v/>
       </c>
       <c r="B352" t="str">
-        <v>rehab</v>
+        <v>or</v>
       </c>
       <c r="C352" t="str">
-        <v>IMG_3850.jpg</v>
+        <v>cache_Messagep8461.jpg</v>
       </c>
       <c r="D352" t="str">
-        <v>2024:10:07 22:07:38</v>
+        <v>2021:08:13 18:15:55</v>
       </c>
       <c r="E352" t="str">
         <v>1920</v>
@@ -11006,17 +11043,17 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" t="str">
-        <v/>
+      <c r="A353">
+        <v>20</v>
       </c>
       <c r="B353" t="str">
-        <v>rehab</v>
+        <v>or</v>
       </c>
       <c r="C353" t="str">
-        <v>IMG_9499.jpg</v>
+        <v>cache_Messagep8464.jpg</v>
       </c>
       <c r="D353" t="str">
-        <v>2024:10:08 07:48:13</v>
+        <v>2021:08:13 16:24:10</v>
       </c>
       <c r="E353" t="str">
         <v>1920</v>
@@ -11036,10 +11073,10 @@
         <v>rehab</v>
       </c>
       <c r="C354" t="str">
-        <v>IMG_9500.jpg</v>
+        <v>7F793CFB-7E3D-427D-A2B9-7F48876F8894.jpg</v>
       </c>
       <c r="D354" t="str">
-        <v>2024:10:08 07:49:00</v>
+        <v/>
       </c>
       <c r="E354" t="str">
         <v>1920</v>
@@ -11059,10 +11096,10 @@
         <v>rehab</v>
       </c>
       <c r="C355" t="str">
-        <v>IMG_9502.jpg</v>
+        <v>IMG_3850.jpg</v>
       </c>
       <c r="D355" t="str">
-        <v>2024:10:08 07:49:42</v>
+        <v>2024:10:07 22:07:38</v>
       </c>
       <c r="E355" t="str">
         <v>1920</v>
@@ -11079,13 +11116,13 @@
         <v/>
       </c>
       <c r="B356" t="str">
-        <v>running</v>
+        <v>rehab</v>
       </c>
       <c r="C356" t="str">
-        <v>F801B87B-17FD-45E8-8E78-660A40CC1D66.jpg</v>
+        <v>IMG_9499.jpg</v>
       </c>
       <c r="D356" t="str">
-        <v/>
+        <v>2024:10:08 07:48:13</v>
       </c>
       <c r="E356" t="str">
         <v>1920</v>
@@ -11102,13 +11139,13 @@
         <v/>
       </c>
       <c r="B357" t="str">
-        <v>running</v>
+        <v>rehab</v>
       </c>
       <c r="C357" t="str">
-        <v>IMG_0014.jpg</v>
+        <v>IMG_9500.jpg</v>
       </c>
       <c r="D357" t="str">
-        <v/>
+        <v>2024:10:08 07:49:00</v>
       </c>
       <c r="E357" t="str">
         <v>1920</v>
@@ -11121,17 +11158,17 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358">
-        <v>32</v>
+      <c r="A358" t="str">
+        <v/>
       </c>
       <c r="B358" t="str">
-        <v>running</v>
+        <v>rehab</v>
       </c>
       <c r="C358" t="str">
-        <v>IMG_0015.jpg</v>
+        <v>IMG_9502.jpg</v>
       </c>
       <c r="D358" t="str">
-        <v/>
+        <v>2024:10:08 07:49:42</v>
       </c>
       <c r="E358" t="str">
         <v>1920</v>
@@ -11151,7 +11188,7 @@
         <v>running</v>
       </c>
       <c r="C359" t="str">
-        <v>IMG_0021.jpg</v>
+        <v>F801B87B-17FD-45E8-8E78-660A40CC1D66.jpg</v>
       </c>
       <c r="D359" t="str">
         <v/>
@@ -11171,13 +11208,13 @@
         <v/>
       </c>
       <c r="B360" t="str">
-        <v>ryugaku</v>
+        <v>running</v>
       </c>
       <c r="C360" t="str">
-        <v>IMG_0005.jpg</v>
+        <v>IMG_0014.jpg</v>
       </c>
       <c r="D360" t="str">
-        <v>2023:09:19 10:08:25</v>
+        <v/>
       </c>
       <c r="E360" t="str">
         <v>1920</v>
@@ -11190,17 +11227,17 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" t="str">
-        <v/>
+      <c r="A361">
+        <v>32</v>
       </c>
       <c r="B361" t="str">
-        <v>ryugaku</v>
+        <v>running</v>
       </c>
       <c r="C361" t="str">
-        <v>IMG_0066.jpg</v>
+        <v>IMG_0015.jpg</v>
       </c>
       <c r="D361" t="str">
-        <v>2023:09:20 20:43:40</v>
+        <v/>
       </c>
       <c r="E361" t="str">
         <v>1920</v>
@@ -11217,13 +11254,13 @@
         <v/>
       </c>
       <c r="B362" t="str">
-        <v>ryugaku</v>
+        <v>running</v>
       </c>
       <c r="C362" t="str">
-        <v>IMG_6563.jpg</v>
+        <v>IMG_0021.jpg</v>
       </c>
       <c r="D362" t="str">
-        <v>2023:09:20 14:31:34</v>
+        <v/>
       </c>
       <c r="E362" t="str">
         <v>1920</v>
@@ -11243,10 +11280,10 @@
         <v>ryugaku</v>
       </c>
       <c r="C363" t="str">
-        <v>IMG_6580.jpg</v>
+        <v>IMG_0005.jpg</v>
       </c>
       <c r="D363" t="str">
-        <v>2023:09:21 11:49:50</v>
+        <v>2023:09:19 10:08:25</v>
       </c>
       <c r="E363" t="str">
         <v>1920</v>
@@ -11266,19 +11303,19 @@
         <v>ryugaku</v>
       </c>
       <c r="C364" t="str">
-        <v>IMG_7694.jpg</v>
+        <v>IMG_0066.jpg</v>
       </c>
       <c r="D364" t="str">
-        <v/>
+        <v>2023:09:20 20:43:40</v>
       </c>
       <c r="E364" t="str">
-        <v>1440</v>
+        <v>1920</v>
       </c>
       <c r="F364" t="str">
-        <v>1920</v>
+        <v>1440</v>
       </c>
       <c r="G364" t="str">
-        <v>縦</v>
+        <v>横</v>
       </c>
     </row>
     <row r="365">
@@ -11286,13 +11323,13 @@
         <v/>
       </c>
       <c r="B365" t="str">
-        <v>sakai</v>
+        <v>ryugaku</v>
       </c>
       <c r="C365" t="str">
-        <v>IMG_1203.jpg</v>
+        <v>IMG_6563.jpg</v>
       </c>
       <c r="D365" t="str">
-        <v>2020:03:31 11:46:26</v>
+        <v>2023:09:20 14:31:34</v>
       </c>
       <c r="E365" t="str">
         <v>1920</v>
@@ -11305,23 +11342,23 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366">
-        <v>31</v>
+      <c r="A366" t="str">
+        <v/>
       </c>
       <c r="B366" t="str">
-        <v>sakai</v>
+        <v>ryugaku</v>
       </c>
       <c r="C366" t="str">
-        <v>IMG_2675.jpg</v>
+        <v>IMG_6580.jpg</v>
       </c>
       <c r="D366" t="str">
-        <v/>
+        <v>2023:09:21 11:49:50</v>
       </c>
       <c r="E366" t="str">
         <v>1920</v>
       </c>
       <c r="F366" t="str">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="G366" t="str">
         <v>横</v>
@@ -11332,22 +11369,22 @@
         <v/>
       </c>
       <c r="B367" t="str">
-        <v>uchida-party</v>
+        <v>ryugaku</v>
       </c>
       <c r="C367" t="str">
-        <v>IMG_0418.jpg</v>
+        <v>IMG_7694.jpg</v>
       </c>
       <c r="D367" t="str">
-        <v>2021:04:02 12:36:34</v>
+        <v/>
       </c>
       <c r="E367" t="str">
-        <v>1920</v>
+        <v>1440</v>
       </c>
       <c r="F367" t="str">
-        <v>1440</v>
+        <v>1920</v>
       </c>
       <c r="G367" t="str">
-        <v>横</v>
+        <v>縦</v>
       </c>
     </row>
     <row r="368">
@@ -11355,13 +11392,13 @@
         <v/>
       </c>
       <c r="B368" t="str">
-        <v>uchida-party</v>
+        <v>sakai</v>
       </c>
       <c r="C368" t="str">
-        <v>IMG_0420.jpg</v>
+        <v>IMG_1203.jpg</v>
       </c>
       <c r="D368" t="str">
-        <v>2021:04:02 12:36:53</v>
+        <v>2020:03:31 11:46:26</v>
       </c>
       <c r="E368" t="str">
         <v>1920</v>
@@ -11374,23 +11411,23 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" t="str">
-        <v/>
+      <c r="A369">
+        <v>31</v>
       </c>
       <c r="B369" t="str">
-        <v>uchida-party</v>
+        <v>sakai</v>
       </c>
       <c r="C369" t="str">
-        <v>IMG_0833.jpg</v>
+        <v>IMG_2675.jpg</v>
       </c>
       <c r="D369" t="str">
-        <v>2021:06:04 08:18:35</v>
+        <v/>
       </c>
       <c r="E369" t="str">
         <v>1920</v>
       </c>
       <c r="F369" t="str">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="G369" t="str">
         <v>横</v>
@@ -11404,10 +11441,10 @@
         <v>uchida-party</v>
       </c>
       <c r="C370" t="str">
-        <v>IMG_0889.jpg</v>
+        <v>IMG_0418.jpg</v>
       </c>
       <c r="D370" t="str">
-        <v>2021:06:14 07:39:41</v>
+        <v>2021:04:02 12:36:34</v>
       </c>
       <c r="E370" t="str">
         <v>1920</v>
@@ -11427,10 +11464,10 @@
         <v>uchida-party</v>
       </c>
       <c r="C371" t="str">
-        <v>IMG_1078.jpg</v>
+        <v>IMG_0420.jpg</v>
       </c>
       <c r="D371" t="str">
-        <v>2021:07:30 14:04:05</v>
+        <v>2021:04:02 12:36:53</v>
       </c>
       <c r="E371" t="str">
         <v>1920</v>
@@ -11450,10 +11487,10 @@
         <v>uchida-party</v>
       </c>
       <c r="C372" t="str">
-        <v>IMG_1079.jpg</v>
+        <v>IMG_0833.jpg</v>
       </c>
       <c r="D372" t="str">
-        <v>2021:07:30 14:04:27</v>
+        <v>2021:06:04 08:18:35</v>
       </c>
       <c r="E372" t="str">
         <v>1920</v>
@@ -11473,10 +11510,10 @@
         <v>uchida-party</v>
       </c>
       <c r="C373" t="str">
-        <v>IMG_1131.jpg</v>
+        <v>IMG_0889.jpg</v>
       </c>
       <c r="D373" t="str">
-        <v>2021:08:11 18:54:25</v>
+        <v>2021:06:14 07:39:41</v>
       </c>
       <c r="E373" t="str">
         <v>1920</v>
@@ -11496,10 +11533,10 @@
         <v>uchida-party</v>
       </c>
       <c r="C374" t="str">
-        <v>IMG_1132.jpg</v>
+        <v>IMG_1078.jpg</v>
       </c>
       <c r="D374" t="str">
-        <v>2021:08:11 18:54:16</v>
+        <v>2021:07:30 14:04:05</v>
       </c>
       <c r="E374" t="str">
         <v>1920</v>
@@ -11519,10 +11556,10 @@
         <v>uchida-party</v>
       </c>
       <c r="C375" t="str">
-        <v>IMG_1134.jpg</v>
+        <v>IMG_1079.jpg</v>
       </c>
       <c r="D375" t="str">
-        <v>2021:08:11 18:55:10</v>
+        <v>2021:07:30 14:04:27</v>
       </c>
       <c r="E375" t="str">
         <v>1920</v>
@@ -11542,10 +11579,10 @@
         <v>uchida-party</v>
       </c>
       <c r="C376" t="str">
-        <v>IMG_1140.jpg</v>
+        <v>IMG_1131.jpg</v>
       </c>
       <c r="D376" t="str">
-        <v>2021:08:13 18:05:11</v>
+        <v>2021:08:11 18:54:25</v>
       </c>
       <c r="E376" t="str">
         <v>1920</v>
@@ -11565,10 +11602,10 @@
         <v>uchida-party</v>
       </c>
       <c r="C377" t="str">
-        <v>IMG_1158.jpg</v>
+        <v>IMG_1132.jpg</v>
       </c>
       <c r="D377" t="str">
-        <v>2021:08:21 07:00:31</v>
+        <v>2021:08:11 18:54:16</v>
       </c>
       <c r="E377" t="str">
         <v>1920</v>
@@ -11588,16 +11625,16 @@
         <v>uchida-party</v>
       </c>
       <c r="C378" t="str">
-        <v>IMG_1554.jpg</v>
+        <v>IMG_1134.jpg</v>
       </c>
       <c r="D378" t="str">
-        <v/>
+        <v>2021:08:11 18:55:10</v>
       </c>
       <c r="E378" t="str">
         <v>1920</v>
       </c>
       <c r="F378" t="str">
-        <v>1080</v>
+        <v>1440</v>
       </c>
       <c r="G378" t="str">
         <v>横</v>
@@ -11611,19 +11648,19 @@
         <v>uchida-party</v>
       </c>
       <c r="C379" t="str">
-        <v>IMG_2618.jpg</v>
+        <v>IMG_1140.jpg</v>
       </c>
       <c r="D379" t="str">
-        <v/>
+        <v>2021:08:13 18:05:11</v>
       </c>
       <c r="E379" t="str">
-        <v>1440</v>
+        <v>1920</v>
       </c>
       <c r="F379" t="str">
-        <v>1920</v>
+        <v>1440</v>
       </c>
       <c r="G379" t="str">
-        <v>縦</v>
+        <v>横</v>
       </c>
     </row>
     <row r="380">
@@ -11634,10 +11671,10 @@
         <v>uchida-party</v>
       </c>
       <c r="C380" t="str">
-        <v>IMG_2621.jpg</v>
+        <v>IMG_1158.jpg</v>
       </c>
       <c r="D380" t="str">
-        <v/>
+        <v>2021:08:21 07:00:31</v>
       </c>
       <c r="E380" t="str">
         <v>1920</v>
@@ -11657,7 +11694,7 @@
         <v>uchida-party</v>
       </c>
       <c r="C381" t="str">
-        <v>IMG_2622.jpg</v>
+        <v>IMG_1554.jpg</v>
       </c>
       <c r="D381" t="str">
         <v/>
@@ -11666,7 +11703,7 @@
         <v>1920</v>
       </c>
       <c r="F381" t="str">
-        <v>1440</v>
+        <v>1080</v>
       </c>
       <c r="G381" t="str">
         <v>横</v>
@@ -11680,19 +11717,19 @@
         <v>uchida-party</v>
       </c>
       <c r="C382" t="str">
-        <v>IMG_2624.jpg</v>
+        <v>IMG_2618.jpg</v>
       </c>
       <c r="D382" t="str">
         <v/>
       </c>
       <c r="E382" t="str">
-        <v>1920</v>
+        <v>1440</v>
       </c>
       <c r="F382" t="str">
-        <v>1440</v>
+        <v>1920</v>
       </c>
       <c r="G382" t="str">
-        <v>横</v>
+        <v>縦</v>
       </c>
     </row>
     <row r="383">
@@ -11703,19 +11740,19 @@
         <v>uchida-party</v>
       </c>
       <c r="C383" t="str">
-        <v>IMG_2625.jpg</v>
+        <v>IMG_2621.jpg</v>
       </c>
       <c r="D383" t="str">
         <v/>
       </c>
       <c r="E383" t="str">
-        <v>1440</v>
+        <v>1920</v>
       </c>
       <c r="F383" t="str">
-        <v>1920</v>
+        <v>1440</v>
       </c>
       <c r="G383" t="str">
-        <v>縦</v>
+        <v>横</v>
       </c>
     </row>
     <row r="384">
@@ -11726,10 +11763,10 @@
         <v>uchida-party</v>
       </c>
       <c r="C384" t="str">
-        <v>IMG_6560.jpg</v>
+        <v>IMG_2622.jpg</v>
       </c>
       <c r="D384" t="str">
-        <v>2023:09:20 14:31:22</v>
+        <v/>
       </c>
       <c r="E384" t="str">
         <v>1920</v>
@@ -11749,10 +11786,10 @@
         <v>uchida-party</v>
       </c>
       <c r="C385" t="str">
-        <v>IMG_6561.jpg</v>
+        <v>IMG_2624.jpg</v>
       </c>
       <c r="D385" t="str">
-        <v>2023:09:20 14:31:31</v>
+        <v/>
       </c>
       <c r="E385" t="str">
         <v>1920</v>
@@ -11772,19 +11809,19 @@
         <v>uchida-party</v>
       </c>
       <c r="C386" t="str">
-        <v>IMG_8352.jpg</v>
+        <v>IMG_2625.jpg</v>
       </c>
       <c r="D386" t="str">
         <v/>
       </c>
       <c r="E386" t="str">
-        <v>1920</v>
+        <v>1440</v>
       </c>
       <c r="F386" t="str">
-        <v>1080</v>
+        <v>1920</v>
       </c>
       <c r="G386" t="str">
-        <v>横</v>
+        <v>縦</v>
       </c>
     </row>
     <row r="387">
@@ -11795,10 +11832,10 @@
         <v>uchida-party</v>
       </c>
       <c r="C387" t="str">
-        <v>IMG_8576.jpg</v>
+        <v>IMG_6560.jpg</v>
       </c>
       <c r="D387" t="str">
-        <v/>
+        <v>2023:09:20 14:31:22</v>
       </c>
       <c r="E387" t="str">
         <v>1920</v>
@@ -11818,10 +11855,10 @@
         <v>uchida-party</v>
       </c>
       <c r="C388" t="str">
-        <v>IMG_8596.jpg</v>
+        <v>IMG_6561.jpg</v>
       </c>
       <c r="D388" t="str">
-        <v/>
+        <v>2023:09:20 14:31:31</v>
       </c>
       <c r="E388" t="str">
         <v>1920</v>
@@ -11841,16 +11878,16 @@
         <v>uchida-party</v>
       </c>
       <c r="C389" t="str">
-        <v>IMG_8660.jpg</v>
+        <v>IMG_8352.jpg</v>
       </c>
       <c r="D389" t="str">
-        <v>2024:05:24 12:10:11</v>
+        <v/>
       </c>
       <c r="E389" t="str">
         <v>1920</v>
       </c>
       <c r="F389" t="str">
-        <v>1440</v>
+        <v>1080</v>
       </c>
       <c r="G389" t="str">
         <v>横</v>
@@ -11864,19 +11901,19 @@
         <v>uchida-party</v>
       </c>
       <c r="C390" t="str">
-        <v>IMG_8977.jpg</v>
+        <v>IMG_8576.jpg</v>
       </c>
       <c r="D390" t="str">
         <v/>
       </c>
       <c r="E390" t="str">
-        <v>1440</v>
+        <v>1920</v>
       </c>
       <c r="F390" t="str">
-        <v>1920</v>
+        <v>1440</v>
       </c>
       <c r="G390" t="str">
-        <v>縦</v>
+        <v>横</v>
       </c>
     </row>
     <row r="391">
@@ -11887,10 +11924,10 @@
         <v>uchida-party</v>
       </c>
       <c r="C391" t="str">
-        <v>IMG_9063.jpg</v>
+        <v>IMG_8596.jpg</v>
       </c>
       <c r="D391" t="str">
-        <v>2024:05:22 09:57:35</v>
+        <v/>
       </c>
       <c r="E391" t="str">
         <v>1920</v>
@@ -11910,10 +11947,10 @@
         <v>uchida-party</v>
       </c>
       <c r="C392" t="str">
-        <v>IMG_9068.jpg</v>
+        <v>IMG_8660.jpg</v>
       </c>
       <c r="D392" t="str">
-        <v>2024:05:22 10:06:44</v>
+        <v>2024:05:24 12:10:11</v>
       </c>
       <c r="E392" t="str">
         <v>1920</v>
@@ -11933,19 +11970,19 @@
         <v>uchida-party</v>
       </c>
       <c r="C393" t="str">
-        <v>IMG_9134.jpg</v>
+        <v>IMG_8977.jpg</v>
       </c>
       <c r="D393" t="str">
-        <v>2024:08:07 18:15:34</v>
+        <v/>
       </c>
       <c r="E393" t="str">
-        <v>1920</v>
+        <v>1440</v>
       </c>
       <c r="F393" t="str">
-        <v>1440</v>
+        <v>1920</v>
       </c>
       <c r="G393" t="str">
-        <v>横</v>
+        <v>縦</v>
       </c>
     </row>
     <row r="394">
@@ -11956,10 +11993,10 @@
         <v>uchida-party</v>
       </c>
       <c r="C394" t="str">
-        <v>IMG_9218.jpg</v>
+        <v>IMG_9063.jpg</v>
       </c>
       <c r="D394" t="str">
-        <v>2024:08:26 14:41:06</v>
+        <v>2024:05:22 09:57:35</v>
       </c>
       <c r="E394" t="str">
         <v>1920</v>
@@ -11979,10 +12016,10 @@
         <v>uchida-party</v>
       </c>
       <c r="C395" t="str">
-        <v>IMG_9234.jpg</v>
+        <v>IMG_9068.jpg</v>
       </c>
       <c r="D395" t="str">
-        <v>2024:09:02 14:32:47</v>
+        <v>2024:05:22 10:06:44</v>
       </c>
       <c r="E395" t="str">
         <v>1920</v>
@@ -12002,10 +12039,10 @@
         <v>uchida-party</v>
       </c>
       <c r="C396" t="str">
-        <v>IMG_9265.jpg</v>
+        <v>IMG_9134.jpg</v>
       </c>
       <c r="D396" t="str">
-        <v>2024:09:09 10:27:17</v>
+        <v>2024:08:07 18:15:34</v>
       </c>
       <c r="E396" t="str">
         <v>1920</v>
@@ -12025,10 +12062,10 @@
         <v>uchida-party</v>
       </c>
       <c r="C397" t="str">
-        <v>IMG_9425.jpg</v>
+        <v>IMG_9218.jpg</v>
       </c>
       <c r="D397" t="str">
-        <v/>
+        <v>2024:08:26 14:41:06</v>
       </c>
       <c r="E397" t="str">
         <v>1920</v>
@@ -12048,16 +12085,16 @@
         <v>uchida-party</v>
       </c>
       <c r="C398" t="str">
-        <v>IMG_9739.jpg</v>
+        <v>IMG_9234.jpg</v>
       </c>
       <c r="D398" t="str">
-        <v>2024:11:13 08:43:36</v>
+        <v>2024:09:02 14:32:47</v>
       </c>
       <c r="E398" t="str">
         <v>1920</v>
       </c>
       <c r="F398" t="str">
-        <v>1080</v>
+        <v>1440</v>
       </c>
       <c r="G398" t="str">
         <v>横</v>
@@ -12071,10 +12108,10 @@
         <v>uchida-party</v>
       </c>
       <c r="C399" t="str">
-        <v>IMG_9894.jpg</v>
+        <v>IMG_9265.jpg</v>
       </c>
       <c r="D399" t="str">
-        <v>2025:01:06 12:06:57</v>
+        <v>2024:09:09 10:27:17</v>
       </c>
       <c r="E399" t="str">
         <v>1920</v>
@@ -12094,7 +12131,7 @@
         <v>uchida-party</v>
       </c>
       <c r="C400" t="str">
-        <v>IMG_9965.jpg</v>
+        <v>IMG_9425.jpg</v>
       </c>
       <c r="D400" t="str">
         <v/>
@@ -12117,24 +12154,93 @@
         <v>uchida-party</v>
       </c>
       <c r="C401" t="str">
+        <v>IMG_9739.jpg</v>
+      </c>
+      <c r="D401" t="str">
+        <v>2024:11:13 08:43:36</v>
+      </c>
+      <c r="E401" t="str">
+        <v>1920</v>
+      </c>
+      <c r="F401" t="str">
+        <v>1080</v>
+      </c>
+      <c r="G401" t="str">
+        <v>横</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="str">
+        <v/>
+      </c>
+      <c r="B402" t="str">
+        <v>uchida-party</v>
+      </c>
+      <c r="C402" t="str">
+        <v>IMG_9894.jpg</v>
+      </c>
+      <c r="D402" t="str">
+        <v>2025:01:06 12:06:57</v>
+      </c>
+      <c r="E402" t="str">
+        <v>1920</v>
+      </c>
+      <c r="F402" t="str">
+        <v>1440</v>
+      </c>
+      <c r="G402" t="str">
+        <v>横</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="str">
+        <v/>
+      </c>
+      <c r="B403" t="str">
+        <v>uchida-party</v>
+      </c>
+      <c r="C403" t="str">
+        <v>IMG_9965.jpg</v>
+      </c>
+      <c r="D403" t="str">
+        <v/>
+      </c>
+      <c r="E403" t="str">
+        <v>1920</v>
+      </c>
+      <c r="F403" t="str">
+        <v>1440</v>
+      </c>
+      <c r="G403" t="str">
+        <v>横</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="str">
+        <v/>
+      </c>
+      <c r="B404" t="str">
+        <v>uchida-party</v>
+      </c>
+      <c r="C404" t="str">
         <v>cache_Messagep8463.jpg</v>
       </c>
-      <c r="D401" t="str">
+      <c r="D404" t="str">
         <v>2021:08:13 16:25:12</v>
       </c>
-      <c r="E401" t="str">
-        <v>1920</v>
-      </c>
-      <c r="F401" t="str">
-        <v>1440</v>
-      </c>
-      <c r="G401" t="str">
+      <c r="E404" t="str">
+        <v>1920</v>
+      </c>
+      <c r="F404" t="str">
+        <v>1440</v>
+      </c>
+      <c r="G404" t="str">
         <v>横</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G401"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G404"/>
   </ignoredErrors>
 </worksheet>
 </file>